--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -11328,7 +11328,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/23/2026 2:21:13 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/23/2026 6:46:19 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 7/23/2016 to 7/23/2026</t>
+          <t xml:space="preserve">WARNs Received: 7/24/2016 to 7/24/2026</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/23/2026 6:46:19 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/24/2026 6:37:56 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -11328,7 +11328,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/24/2026 6:37:56 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/24/2026 6:55:44 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 7/24/2016 to 7/24/2026</t>
+          <t xml:space="preserve">WARNs Received: 7/25/2016 to 7/25/2026</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/24/2026 6:55:44 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/25/2026 6:23:51 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -11328,7 +11328,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/25/2026 6:23:51 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/25/2026 7:08:24 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 7/25/2016 to 7/25/2026</t>
+          <t xml:space="preserve">WARNs Received: 7/26/2016 to 7/26/2026</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/25/2026 7:08:24 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/26/2026 6:23:56 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -11328,7 +11328,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/26/2026 6:23:56 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/26/2026 7:16:39 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 7/26/2016 to 7/26/2026</t>
+          <t xml:space="preserve">WARNs Received: 7/27/2016 to 7/27/2026</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/26/2026 7:16:39 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/27/2026 8:07:06 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10429,891 +10429,116 @@
     <row r="328" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">6991</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">The Coca -Cola Company Odwalla's - Port</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C328">
         <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D328">
-        <v>44074</v>
-      </c>
-      <c s="11" r="E328">
-        <v>30</v>
-      </c>
+          <t xml:space="preserve">ELGIN                         </t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D328"/>
+      <c s="13" t="str" r="E328"/>
       <c s="9" t="inlineStr" r="F328">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G328">
-        <v>44012</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">6987</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">Levy Premium Foodservice...LLC</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C329">
         <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D329">
-        <v>44044</v>
-      </c>
-      <c s="11" r="E329">
-        <v>54</v>
-      </c>
+          <t xml:space="preserve">Mesa, AZ</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D329"/>
+      <c s="13" t="str" r="E329"/>
       <c s="9" t="inlineStr" r="F329">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G329">
-        <v>44006</v>
+        <v>45125</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">6967</t>
+          <t xml:space="preserve">9324</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">Hyatt Regency - Portland</t>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C330">
         <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D330">
-        <v>44209</v>
-      </c>
-      <c s="11" r="E330">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D330"/>
+      <c s="13" t="str" r="E330"/>
       <c s="9" t="inlineStr" r="F330">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G330">
-        <v>44001</v>
-      </c>
-    </row>
-    <row r="331" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A331">
-        <is>
-          <t xml:space="preserve">6967</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B331">
-        <is>
-          <t xml:space="preserve">Hyatt Regency - Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C331">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D331">
-        <v>44136</v>
-      </c>
-      <c s="11" r="E331">
-        <v>1</v>
-      </c>
-      <c s="9" t="inlineStr" r="F331">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G331">
-        <v>44001</v>
-      </c>
-    </row>
-    <row r="332" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A332">
-        <is>
-          <t xml:space="preserve">6967</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B332">
-        <is>
-          <t xml:space="preserve">Hyatt Regency - Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C332">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D332">
-        <v>44134</v>
-      </c>
-      <c s="11" r="E332">
-        <v>4</v>
-      </c>
-      <c s="9" t="inlineStr" r="F332">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G332">
-        <v>44001</v>
-      </c>
-    </row>
-    <row r="333" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A333">
-        <is>
-          <t xml:space="preserve">6967</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B333">
-        <is>
-          <t xml:space="preserve">Hyatt Regency - Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C333">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D333">
-        <v>44078</v>
-      </c>
-      <c s="11" r="E333">
-        <v>8</v>
-      </c>
-      <c s="9" t="inlineStr" r="F333">
-        <is>
-          <t xml:space="preserve">Temporary Layoff</t>
-        </is>
-      </c>
-      <c s="12" r="G333">
-        <v>44001</v>
-      </c>
-    </row>
-    <row r="334" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A334">
-        <is>
-          <t xml:space="preserve">6967</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B334">
-        <is>
-          <t xml:space="preserve">Hyatt Regency - Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C334">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D334">
-        <v>43910</v>
-      </c>
-      <c s="11" r="E334">
-        <v>181</v>
-      </c>
-      <c s="9" t="inlineStr" r="F334">
-        <is>
-          <t xml:space="preserve">Temporary Layoff</t>
-        </is>
-      </c>
-      <c s="12" r="G334">
-        <v>44001</v>
-      </c>
-    </row>
-    <row r="335" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A335">
-        <is>
-          <t xml:space="preserve">6964</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B335">
-        <is>
-          <t xml:space="preserve">The Bay Company - Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C335">
-        <is>
-          <t xml:space="preserve">Tigard</t>
-        </is>
-      </c>
-      <c s="10" r="D335">
-        <v>44103</v>
-      </c>
-      <c s="11" r="E335">
-        <v>125</v>
-      </c>
-      <c s="9" t="inlineStr" r="F335">
-        <is>
-          <t xml:space="preserve">Other</t>
-        </is>
-      </c>
-      <c s="12" r="G335">
-        <v>43991</v>
-      </c>
-    </row>
-    <row r="336" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A336">
-        <is>
-          <t xml:space="preserve">6964</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B336">
-        <is>
-          <t xml:space="preserve">The Bay Company - Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C336">
-        <is>
-          <t xml:space="preserve">Tigard</t>
-        </is>
-      </c>
-      <c s="10" r="D336">
-        <v>43936</v>
-      </c>
-      <c s="11" r="E336">
-        <v>289</v>
-      </c>
-      <c s="9" t="inlineStr" r="F336">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G336">
-        <v>43991</v>
-      </c>
-    </row>
-    <row r="337" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A337">
-        <is>
-          <t xml:space="preserve">6963</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B337">
-        <is>
-          <t xml:space="preserve">Kimpton Hotel Monaco Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C337">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D337">
-        <v>43903</v>
-      </c>
-      <c s="11" r="E337">
-        <v>147</v>
-      </c>
-      <c s="9" t="inlineStr" r="F337">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G337">
-        <v>43994</v>
-      </c>
-    </row>
-    <row r="338" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A338">
-        <is>
-          <t xml:space="preserve">6963</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B338">
-        <is>
-          <t xml:space="preserve">Kimpton Riverplace Hotel</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C338">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D338">
-        <v>43903</v>
-      </c>
-      <c s="11" r="E338">
-        <v>79</v>
-      </c>
-      <c s="9" t="inlineStr" r="F338">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G338">
-        <v>43994</v>
-      </c>
-    </row>
-    <row r="339" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A339">
-        <is>
-          <t xml:space="preserve">6963</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B339">
-        <is>
-          <t xml:space="preserve">Kimpton Hotel Vintage Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C339">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D339">
-        <v>43891</v>
-      </c>
-      <c s="11" r="E339">
-        <v>94</v>
-      </c>
-      <c s="9" t="inlineStr" r="F339">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G339">
-        <v>43994</v>
-      </c>
-    </row>
-    <row r="340" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A340">
-        <is>
-          <t xml:space="preserve">6935</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B340">
-        <is>
-          <t xml:space="preserve">ATI Albany Operations</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C340">
-        <is>
-          <t xml:space="preserve">Albany</t>
-        </is>
-      </c>
-      <c s="10" r="D340">
-        <v>44172</v>
-      </c>
-      <c s="11" r="E340">
-        <v>76</v>
-      </c>
-      <c s="9" t="inlineStr" r="F340">
-        <is>
-          <t xml:space="preserve">Permanent closure</t>
-        </is>
-      </c>
-      <c s="12" r="G340">
-        <v>43992</v>
-      </c>
-    </row>
-    <row r="341" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A341">
-        <is>
-          <t xml:space="preserve">6935</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B341">
-        <is>
-          <t xml:space="preserve">ATI Albany Operations</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C341">
-        <is>
-          <t xml:space="preserve">Albany</t>
-        </is>
-      </c>
-      <c s="10" r="D341">
-        <v>44130</v>
-      </c>
-      <c s="11" r="E341">
-        <v>135</v>
-      </c>
-      <c s="9" t="inlineStr" r="F341">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G341">
-        <v>43992</v>
-      </c>
-    </row>
-    <row r="342" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A342">
-        <is>
-          <t xml:space="preserve">6903</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B342">
-        <is>
-          <t xml:space="preserve">PCC Structurals - Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C342">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D342">
-        <v>44036</v>
-      </c>
-      <c s="11" r="E342">
-        <v>94</v>
-      </c>
-      <c s="9" t="inlineStr" r="F342">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G342">
-        <v>43986</v>
-      </c>
-    </row>
-    <row r="343" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A343">
-        <is>
-          <t xml:space="preserve">6903</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B343">
-        <is>
-          <t xml:space="preserve">PCC Structurals - Clackamas</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C343">
-        <is>
-          <t xml:space="preserve">Clackamas</t>
-        </is>
-      </c>
-      <c s="10" r="D343">
-        <v>43936</v>
-      </c>
-      <c s="11" r="E343">
-        <v>170</v>
-      </c>
-      <c s="9" t="inlineStr" r="F343">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G343">
-        <v>43986</v>
-      </c>
-    </row>
-    <row r="344" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A344">
-        <is>
-          <t xml:space="preserve">6903</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B344">
-        <is>
-          <t xml:space="preserve">PCC Structurals - Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C344">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D344">
-        <v>43936</v>
-      </c>
-      <c s="11" r="E344">
-        <v>547</v>
-      </c>
-      <c s="9" t="inlineStr" r="F344">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G344">
-        <v>43986</v>
-      </c>
-    </row>
-    <row r="345" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A345">
-        <is>
-          <t xml:space="preserve">6903</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B345">
-        <is>
-          <t xml:space="preserve">PCC Structurals - Redmond</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C345">
-        <is>
-          <t xml:space="preserve">Redmond</t>
-        </is>
-      </c>
-      <c s="10" r="D345">
-        <v>43934</v>
-      </c>
-      <c s="11" r="E345">
-        <v>175</v>
-      </c>
-      <c s="9" t="inlineStr" r="F345">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G345">
-        <v>43986</v>
-      </c>
-    </row>
-    <row r="346" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A346">
-        <is>
-          <t xml:space="preserve">6875</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B346">
-        <is>
-          <t xml:space="preserve">Continuum Global Solutions, LLC</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C346">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D346">
-        <v>44055</v>
-      </c>
-      <c s="11" r="E346">
-        <v>255</v>
-      </c>
-      <c s="9" t="inlineStr" r="F346">
-        <is>
-          <t xml:space="preserve">Permanent closure</t>
-        </is>
-      </c>
-      <c s="12" r="G346">
-        <v>43992</v>
-      </c>
-    </row>
-    <row r="347" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A347">
-        <is>
-          <t xml:space="preserve">6874</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B347">
-        <is>
-          <t xml:space="preserve">EVRAZ - Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C347">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D347">
-        <v>43990</v>
-      </c>
-      <c s="11" r="E347">
-        <v>65</v>
-      </c>
-      <c s="9" t="inlineStr" r="F347">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G347">
-        <v>43990</v>
-      </c>
-    </row>
-    <row r="348" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A348">
-        <is>
-          <t xml:space="preserve">6867</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B348">
-        <is>
-          <t xml:space="preserve">Marriott Portland Downtown Waterfront </t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C348">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D348">
-        <v>44141</v>
-      </c>
-      <c s="11" r="E348">
-        <v>145</v>
-      </c>
-      <c s="9" t="inlineStr" r="F348">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G348">
-        <v>43987</v>
-      </c>
-    </row>
-    <row r="349" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A349">
-        <is>
-          <t xml:space="preserve">6867</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B349">
-        <is>
-          <t xml:space="preserve">Marriott Portland Downtown Waterfront </t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C349">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D349">
-        <v>43911</v>
-      </c>
-      <c s="11" r="E349">
-        <v>248</v>
-      </c>
-      <c s="9" t="inlineStr" r="F349">
-        <is>
-          <t xml:space="preserve">Temporary Layoff</t>
-        </is>
-      </c>
-      <c s="12" r="G349">
-        <v>43987</v>
-      </c>
-    </row>
-    <row r="350" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A350">
-        <is>
-          <t xml:space="preserve">6847</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B350">
-        <is>
-          <t xml:space="preserve">Benson Hotel</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C350">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D350">
-        <v>43983</v>
-      </c>
-      <c s="11" r="E350">
-        <v>81</v>
-      </c>
-      <c s="9" t="inlineStr" r="F350">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G350">
-        <v>43983</v>
-      </c>
-    </row>
-    <row r="351" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A351">
-        <is>
-          <t xml:space="preserve">6846</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B351">
-        <is>
-          <t xml:space="preserve">Embassy Suites - Portland - Wash Sq </t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C351">
-        <is>
-          <t xml:space="preserve">Tigard</t>
-        </is>
-      </c>
-      <c s="10" r="D351">
-        <v>43983</v>
-      </c>
-      <c s="11" r="E351">
-        <v>7</v>
-      </c>
-      <c s="9" t="inlineStr" r="F351">
-        <is>
-          <t xml:space="preserve">Temporary Layoff</t>
-        </is>
-      </c>
-      <c s="12" r="G351">
-        <v>43982</v>
-      </c>
-    </row>
-    <row r="352" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A352">
-        <is>
-          <t xml:space="preserve">6846</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B352">
-        <is>
-          <t xml:space="preserve">Embassy Suites - Portland - Wash Sq </t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C352">
-        <is>
-          <t xml:space="preserve">Tigard</t>
-        </is>
-      </c>
-      <c s="10" r="D352">
-        <v>43919</v>
-      </c>
-      <c s="11" r="E352">
-        <v>81</v>
-      </c>
-      <c s="9" t="inlineStr" r="F352">
-        <is>
-          <t xml:space="preserve">Temporary Layoff</t>
-        </is>
-      </c>
-      <c s="12" r="G352">
-        <v>43982</v>
-      </c>
-    </row>
-    <row r="353" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A353">
-        <is>
-          <t xml:space="preserve">8470</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B353">
-        <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C353">
-        <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D353"/>
-      <c s="13" t="str" r="E353"/>
-      <c s="9" t="inlineStr" r="F353">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G353">
-        <v>44909</v>
-      </c>
-    </row>
-    <row r="354" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A354">
-        <is>
-          <t xml:space="preserve">8592</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B354">
-        <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C354">
-        <is>
-          <t xml:space="preserve">Mesa, AZ</t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D354"/>
-      <c s="13" t="str" r="E354"/>
-      <c s="9" t="inlineStr" r="F354">
-        <is>
-          <t xml:space="preserve">Permanent closure</t>
-        </is>
-      </c>
-      <c s="12" r="G354">
-        <v>45125</v>
-      </c>
-    </row>
-    <row r="355" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A355">
-        <is>
-          <t xml:space="preserve">9324</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B355">
-        <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C355">
-        <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D355"/>
-      <c s="13" t="str" r="E355"/>
-      <c s="9" t="inlineStr" r="F355">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G355">
         <v>45887</v>
       </c>
     </row>
-    <row r="356" ht="3.6" customHeight="0">
-      <c s="14" t="inlineStr" r="A356">
+    <row r="331" ht="3.6" customHeight="0">
+      <c s="14" t="inlineStr" r="A331">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B356">
+      <c s="14" t="inlineStr" r="B331">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C356">
+      <c s="14" t="inlineStr" r="C331">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D356">
+      <c s="14" t="inlineStr" r="D331">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E356">
+      <c s="14" t="inlineStr" r="E331">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F356">
+      <c s="14" t="inlineStr" r="F331">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G356">
+      <c s="14" t="inlineStr" r="G331">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -11328,7 +10553,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/27/2026 8:07:06 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/27/2026 6:50:50 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 7/27/2016 to 7/27/2026</t>
+          <t xml:space="preserve">WARNs Received: 7/28/2016 to 7/28/2026</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/27/2026 6:50:50 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/28/2026 6:50:48 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10553,7 +10553,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/28/2026 6:50:48 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/28/2026 6:49:56 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 7/28/2016 to 7/28/2026</t>
+          <t xml:space="preserve">WARNs Received: 7/29/2016 to 7/29/2026</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/28/2026 6:49:56 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/29/2026 7:08:13 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10553,7 +10553,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/29/2026 7:08:13 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/29/2026 6:46:02 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 7/29/2016 to 7/29/2026</t>
+          <t xml:space="preserve">WARNs Received: 7/30/2016 to 7/30/2026</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/29/2026 6:46:02 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/30/2026 6:46:17 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10553,7 +10553,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/30/2026 6:46:17 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/30/2026 7:12:22 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 7/30/2016 to 7/30/2026</t>
+          <t xml:space="preserve">WARNs Received: 7/31/2016 to 7/31/2026</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/30/2026 7:12:22 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/31/2026 6:53:02 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -385,63 +385,63 @@
     <row r="4" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">9534</t>
+          <t xml:space="preserve">9549</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
+          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D4">
-        <v>46262</v>
+        <v>46325</v>
       </c>
       <c s="11" r="E4">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c s="9" t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G4">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">Adventist Health Tillamook</t>
+          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D5">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c s="11" r="E5">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c s="9" t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G5">
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="0">
@@ -452,19 +452,19 @@
       </c>
       <c s="9" t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">Adventist Health Portland</t>
+          <t xml:space="preserve">Adventist Health Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">Portland, </t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D6">
         <v>46206</v>
       </c>
       <c s="11" r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F6">
         <is>
@@ -483,19 +483,19 @@
       </c>
       <c s="9" t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
+          <t xml:space="preserve">Adventist Health Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">The Dalles</t>
+          <t xml:space="preserve">Portland, </t>
         </is>
       </c>
       <c s="10" r="D7">
         <v>46206</v>
       </c>
       <c s="11" r="E7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F7">
         <is>
@@ -509,32 +509,32 @@
     <row r="8" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">PacificSource</t>
+          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">The Dalles</t>
         </is>
       </c>
       <c s="10" r="D8">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E8">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G8">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="0">
@@ -545,23 +545,23 @@
       </c>
       <c s="9" t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">PacificSource - Bend</t>
+          <t xml:space="preserve">PacificSource</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D9">
         <v>46234</v>
       </c>
       <c s="11" r="E9">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F9">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G9">
@@ -576,19 +576,19 @@
       </c>
       <c s="9" t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">PacificSource - Portland</t>
+          <t xml:space="preserve">PacificSource - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D10">
         <v>46234</v>
       </c>
       <c s="11" r="E10">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F10">
         <is>
@@ -607,12 +607,12 @@
       </c>
       <c s="9" t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">PacificSource - Salem</t>
+          <t xml:space="preserve">PacificSource - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D11">
@@ -638,19 +638,19 @@
       </c>
       <c s="9" t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">PacificSource Hood River</t>
+          <t xml:space="preserve">PacificSource - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D12">
         <v>46234</v>
       </c>
       <c s="11" r="E12">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F12">
         <is>
@@ -664,63 +664,63 @@
     <row r="13" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">9511</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
+          <t xml:space="preserve">PacificSource Hood River</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D13">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E13">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F13">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9511</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D14">
-        <v>46234</v>
+        <v>46228</v>
       </c>
       <c s="11" r="E14">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F14">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G14">
-        <v>46160</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="0">
@@ -731,19 +731,19 @@
       </c>
       <c s="9" t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D15">
         <v>46234</v>
       </c>
       <c s="11" r="E15">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F15">
         <is>
@@ -762,19 +762,19 @@
       </c>
       <c s="9" t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D16">
         <v>46234</v>
       </c>
       <c s="11" r="E16">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F16">
         <is>
@@ -793,19 +793,19 @@
       </c>
       <c s="9" t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C17">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D17">
         <v>46234</v>
       </c>
       <c s="11" r="E17">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F17">
         <is>
@@ -824,19 +824,19 @@
       </c>
       <c s="9" t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D18">
         <v>46234</v>
       </c>
       <c s="11" r="E18">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c s="9" t="inlineStr" r="F18">
         <is>
@@ -850,86 +850,86 @@
     <row r="19" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D19">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E19">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G19">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D20">
-        <v>46201</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E20">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G20">
-        <v>46141</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D21">
-        <v>46295</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E21">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F21">
         <is>
@@ -937,49 +937,49 @@
         </is>
       </c>
       <c s="12" r="G21">
-        <v>46114</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D22">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E22">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G22">
-        <v>46108</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C23">
@@ -988,18 +988,18 @@
         </is>
       </c>
       <c s="10" r="D23">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E23">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G23">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="0">
@@ -1010,7 +1010,7 @@
       </c>
       <c s="9" t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C24">
@@ -1036,24 +1036,24 @@
     <row r="25" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D25">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E25">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F25">
         <is>
@@ -1061,38 +1061,38 @@
         </is>
       </c>
       <c s="12" r="G25">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D26">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E26">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G26">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="0">
@@ -1103,19 +1103,19 @@
       </c>
       <c s="9" t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D27">
         <v>46131</v>
       </c>
       <c s="11" r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F27">
         <is>
@@ -1129,63 +1129,63 @@
     <row r="28" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D28">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E28">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F28">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G28">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D29">
         <v>46117</v>
       </c>
       <c s="11" r="E29">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G29">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="0">
@@ -1196,19 +1196,19 @@
       </c>
       <c s="9" t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D30">
         <v>46117</v>
       </c>
       <c s="11" r="E30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F30">
         <is>
@@ -1227,12 +1227,12 @@
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D31">
@@ -1258,12 +1258,12 @@
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D32">
@@ -1289,12 +1289,12 @@
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D33">
@@ -1320,12 +1320,12 @@
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D34">
@@ -1351,12 +1351,12 @@
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D35">
@@ -1382,12 +1382,12 @@
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D36">
@@ -1413,7 +1413,7 @@
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
@@ -1444,7 +1444,7 @@
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
@@ -1475,12 +1475,12 @@
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D39">
@@ -1506,12 +1506,12 @@
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D40">
@@ -1537,12 +1537,12 @@
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D41">
@@ -1568,7 +1568,7 @@
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
@@ -1599,19 +1599,19 @@
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D43">
         <v>46117</v>
       </c>
       <c s="11" r="E43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F43">
         <is>
@@ -1630,19 +1630,19 @@
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D44">
         <v>46117</v>
       </c>
       <c s="11" r="E44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F44">
         <is>
@@ -1661,19 +1661,19 @@
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D45">
         <v>46117</v>
       </c>
       <c s="11" r="E45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F45">
         <is>
@@ -1692,12 +1692,12 @@
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D46">
@@ -1723,12 +1723,12 @@
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D47">
@@ -1749,24 +1749,24 @@
     <row r="48" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D48">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E48">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F48">
         <is>
@@ -1785,19 +1785,19 @@
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D49">
         <v>46112</v>
       </c>
       <c s="11" r="E49">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F49">
         <is>
@@ -1816,19 +1816,19 @@
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D50">
         <v>46112</v>
       </c>
       <c s="11" r="E50">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F50">
         <is>
@@ -1842,24 +1842,24 @@
     <row r="51" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D51">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E51">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F51">
         <is>
@@ -1867,30 +1867,30 @@
         </is>
       </c>
       <c s="12" r="G51">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D52">
-        <v>46142</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E52">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F52">
         <is>
@@ -1898,30 +1898,30 @@
         </is>
       </c>
       <c s="12" r="G52">
-        <v>46020</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D53">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E53">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F53">
         <is>
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c s="12" r="G53">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="0">
@@ -1940,7 +1940,7 @@
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
@@ -1952,7 +1952,7 @@
         <v>46014</v>
       </c>
       <c s="11" r="E54">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F54">
         <is>
@@ -1971,19 +1971,19 @@
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D55">
         <v>46014</v>
       </c>
       <c s="11" r="E55">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F55">
         <is>
@@ -1997,43 +1997,43 @@
     <row r="56" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D56">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E56">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F56">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G56">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
@@ -2042,29 +2042,29 @@
         </is>
       </c>
       <c s="10" r="D57">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E57">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F57">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G57">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c s="10" r="D58">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E58">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F58">
         <is>
@@ -2090,63 +2090,63 @@
     <row r="59" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D59">
         <v>46054</v>
       </c>
       <c s="11" r="E59">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F59">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G59">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D60">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E60">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F60">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G60">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="0">
@@ -2157,19 +2157,19 @@
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D61">
         <v>45916</v>
       </c>
       <c s="11" r="E61">
-        <v>510</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F61">
         <is>
@@ -2188,7 +2188,7 @@
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
@@ -2200,7 +2200,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E62">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F62">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
@@ -2231,7 +2231,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E63">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F63">
         <is>
@@ -2245,24 +2245,24 @@
     <row r="64" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D64">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E64">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F64">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c s="12" r="G64">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="0">
@@ -2281,23 +2281,23 @@
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D65">
         <v>46022</v>
       </c>
       <c s="11" r="E65">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F65">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G65">
@@ -2312,19 +2312,19 @@
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D66">
         <v>46022</v>
       </c>
       <c s="11" r="E66">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F66">
         <is>
@@ -2343,19 +2343,19 @@
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D67">
         <v>46022</v>
       </c>
       <c s="11" r="E67">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F67">
         <is>
@@ -2374,19 +2374,19 @@
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D68">
         <v>46022</v>
       </c>
       <c s="11" r="E68">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F68">
         <is>
@@ -2400,55 +2400,55 @@
     <row r="69" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D69">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E69">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F69">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G69">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D70">
         <v>46017</v>
       </c>
       <c s="11" r="E70">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F70">
         <is>
@@ -2462,28 +2462,28 @@
     <row r="71" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D71">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E71">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F71">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G71">
@@ -2507,14 +2507,14 @@
         </is>
       </c>
       <c s="10" r="D72">
-        <v>46017</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E72">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G72">
@@ -2524,86 +2524,86 @@
     <row r="73" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C73">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D73">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E73">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G73">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D74">
-        <v>46022</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E74">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F74">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G74">
-        <v>45917</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D75">
-        <v>45978</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E75">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F75">
         <is>
@@ -2611,18 +2611,18 @@
         </is>
       </c>
       <c s="12" r="G75">
-        <v>45943</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c s="10" r="D76">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E76">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F76">
         <is>
@@ -2642,38 +2642,38 @@
         </is>
       </c>
       <c s="12" r="G76">
-        <v>45930</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D77">
-        <v>45940</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E77">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G77">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="0">
@@ -2693,14 +2693,14 @@
         </is>
       </c>
       <c s="10" r="D78">
-        <v>45925</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E78">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G78">
@@ -2710,24 +2710,24 @@
     <row r="79" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C79">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D79">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E79">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
@@ -2735,34 +2735,34 @@
         </is>
       </c>
       <c s="12" r="G79">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C80">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D80">
         <v>45976</v>
       </c>
       <c s="11" r="E80">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G80">
@@ -2772,63 +2772,63 @@
     <row r="81" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D81">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E81">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G81">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C82">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D82">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E82">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G82">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="0">
@@ -2839,7 +2839,7 @@
       </c>
       <c s="9" t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C83">
@@ -2851,7 +2851,7 @@
         <v>45949</v>
       </c>
       <c s="11" r="E83">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
@@ -2865,12 +2865,12 @@
     <row r="84" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
@@ -2879,41 +2879,41 @@
         </is>
       </c>
       <c s="10" r="D84">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E84">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G84">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D85">
-        <v>45874</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E85">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
@@ -2921,18 +2921,18 @@
         </is>
       </c>
       <c s="12" r="G85">
-        <v>45867</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
@@ -2941,49 +2941,49 @@
         </is>
       </c>
       <c s="10" r="D86">
-        <v>45920</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E86">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G86">
-        <v>45854</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D87">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E87">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G87">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="0">
@@ -2994,19 +2994,19 @@
       </c>
       <c s="9" t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D88">
         <v>45912</v>
       </c>
       <c s="11" r="E88">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
@@ -3020,63 +3020,63 @@
     <row r="89" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C89">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D89">
         <v>45912</v>
       </c>
       <c s="11" r="E89">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G89">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C90">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D90">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E90">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G90">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="0">
@@ -3087,19 +3087,19 @@
       </c>
       <c s="9" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C91">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D91">
         <v>45853</v>
       </c>
       <c s="11" r="E91">
-        <v>1544</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
@@ -3118,7 +3118,7 @@
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
@@ -3130,7 +3130,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E92">
-        <v>174</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
@@ -3161,7 +3161,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E93">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
@@ -3175,86 +3175,86 @@
     <row r="94" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D94">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E94">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G94">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C95">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D95">
-        <v>45901</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E95">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G95">
-        <v>45839</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D96">
-        <v>45982</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E96">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c s="12" r="G96">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="0">
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c s="10" r="D97">
-        <v>45968</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E97">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c s="10" r="D98">
-        <v>45894</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E98">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
@@ -3330,24 +3330,24 @@
     <row r="99" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D99">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E99">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
@@ -3355,30 +3355,30 @@
         </is>
       </c>
       <c s="12" r="G99">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C100">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D100">
         <v>45838</v>
       </c>
       <c s="11" r="E100">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
@@ -3392,94 +3392,94 @@
     <row r="101" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C101">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D101">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E101">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G101">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D102">
-        <v>45807</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E102">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G102">
-        <v>45804</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D103">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E103">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G103">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="0">
@@ -3490,19 +3490,19 @@
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D104">
         <v>45866</v>
       </c>
       <c s="11" r="E104">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
@@ -3516,55 +3516,55 @@
     <row r="105" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D105">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E105">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G105">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D106">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E106">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
@@ -3572,85 +3572,85 @@
         </is>
       </c>
       <c s="12" r="G106">
-        <v>45778</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D107">
-        <v>45769</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E107">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G107">
-        <v>45769</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D108">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E108">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G108">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D109">
@@ -3661,69 +3661,69 @@
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G109">
-        <v>45763</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D110">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E110">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G110">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D111">
-        <v>45810</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E111">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G111">
@@ -3733,43 +3733,43 @@
     <row r="112" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D112">
-        <v>45808</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E112">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G112">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
@@ -3778,103 +3778,103 @@
         </is>
       </c>
       <c s="10" r="D113">
-        <v>45834</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E113">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G113">
-        <v>45774</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C114">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D114">
-        <v>45838</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E114">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G114">
-        <v>45744</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C115">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D115">
-        <v>45706</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E115">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G115">
-        <v>45706</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D116">
-        <v>45734</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E116">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
@@ -3882,38 +3882,38 @@
         </is>
       </c>
       <c s="12" r="G116">
-        <v>45666</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D117">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E117">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G117">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="0">
@@ -3924,19 +3924,19 @@
       </c>
       <c s="9" t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D118">
         <v>45707</v>
       </c>
       <c s="11" r="E118">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
@@ -3950,63 +3950,63 @@
     <row r="119" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D119">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E119">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G119">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D120">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E120">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G120">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="0">
@@ -4017,19 +4017,19 @@
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D121">
         <v>45696</v>
       </c>
       <c s="11" r="E121">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
@@ -4043,86 +4043,86 @@
     <row r="122" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D122">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E122">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G122">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D123">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E123">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G123">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D124">
         <v>45931</v>
       </c>
       <c s="11" r="E124">
-        <v>221</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
@@ -4136,43 +4136,43 @@
     <row r="125" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D125">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E125">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G125">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C126">
@@ -4181,18 +4181,18 @@
         </is>
       </c>
       <c s="10" r="D126">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E126">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G126">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="0">
@@ -4203,19 +4203,19 @@
       </c>
       <c s="9" t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D127">
         <v>45726</v>
       </c>
       <c s="11" r="E127">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
@@ -4234,19 +4234,19 @@
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D128">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E128">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
@@ -4265,19 +4265,19 @@
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D129">
         <v>45725</v>
       </c>
       <c s="11" r="E129">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
@@ -4296,19 +4296,19 @@
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D130">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E130">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
@@ -4327,12 +4327,12 @@
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D131">
@@ -4358,12 +4358,12 @@
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D132">
@@ -4389,7 +4389,7 @@
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c s="10" r="D133">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E133">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F133">
         <is>
@@ -4420,19 +4420,19 @@
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D134">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E134">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F134">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c s="10" r="D135">
-        <v>45703</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E135">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
@@ -4482,19 +4482,19 @@
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D136">
-        <v>45690</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E136">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
@@ -4508,12 +4508,12 @@
     <row r="137" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
@@ -4522,72 +4522,72 @@
         </is>
       </c>
       <c s="10" r="D137">
-        <v>45657</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E137">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G137">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D138">
-        <v>45640</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E138">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G138">
-        <v>45580</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D139">
-        <v>45657</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E139">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
@@ -4595,100 +4595,100 @@
         </is>
       </c>
       <c s="12" r="G139">
-        <v>45595</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D140">
-        <v>45584</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E140">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G140">
-        <v>45584</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D141">
-        <v>45664</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E141">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F141">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G141">
-        <v>45582</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D142">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E142">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F142">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G142">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="0">
@@ -4699,19 +4699,19 @@
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D143">
         <v>45611</v>
       </c>
       <c s="11" r="E143">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F143">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
@@ -4742,7 +4742,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E144">
-        <v>124</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
@@ -4761,7 +4761,7 @@
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
@@ -4773,7 +4773,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E145">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
@@ -4787,28 +4787,28 @@
     <row r="146" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D146">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E146">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G146">
@@ -4818,24 +4818,24 @@
     <row r="147" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D147">
-        <v>45621</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E147">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
@@ -4843,38 +4843,38 @@
         </is>
       </c>
       <c s="12" r="G147">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D148">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E148">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F148">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G148">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="0">
@@ -4885,23 +4885,23 @@
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D149">
         <v>45544</v>
       </c>
       <c s="11" r="E149">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F149">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G149">
@@ -4911,55 +4911,55 @@
     <row r="150" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D150">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E150">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F150">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G150">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D151">
-        <v>45654</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E151">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F151">
         <is>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c s="12" r="G151">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="0">
@@ -4987,10 +4987,10 @@
         </is>
       </c>
       <c s="10" r="D152">
-        <v>45612</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E152">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F152">
         <is>
@@ -5018,14 +5018,14 @@
         </is>
       </c>
       <c s="10" r="D153">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E153">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G153">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c s="10" r="D154">
-        <v>45569</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F154">
         <is>
@@ -5080,14 +5080,14 @@
         </is>
       </c>
       <c s="10" r="D155">
-        <v>45555</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E155">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G155">
@@ -5097,24 +5097,24 @@
     <row r="156" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C156">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D156">
-        <v>45653</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E156">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c s="12" r="G156">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="0">
@@ -5142,14 +5142,14 @@
         </is>
       </c>
       <c s="10" r="D157">
-        <v>45505</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E157">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G157">
@@ -5159,24 +5159,24 @@
     <row r="158" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D158">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E158">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c s="12" r="G158">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B159">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c s="10" r="D159">
-        <v>45513</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E159">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F159">
         <is>
@@ -5215,18 +5215,18 @@
         </is>
       </c>
       <c s="12" r="G159">
-        <v>45450</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C160">
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c s="10" r="D160">
-        <v>45504</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E160">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F160">
         <is>
@@ -5246,30 +5246,30 @@
         </is>
       </c>
       <c s="12" r="G160">
-        <v>45441</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C161">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D161">
-        <v>46229</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E161">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F161">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c s="12" r="G161">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="0">
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c s="10" r="D162">
-        <v>45688</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E162">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c s="10" r="D163">
-        <v>45506</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E163">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
@@ -5345,32 +5345,32 @@
     <row r="164" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C164">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D164">
-        <v>45483</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E164">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G164">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="0">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c s="10" r="D165">
-        <v>45401</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E165">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c s="10" r="D166">
-        <v>45366</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
@@ -5438,43 +5438,43 @@
     <row r="167" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C167">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D167">
-        <v>45473</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E167">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G167">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C168">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c s="10" r="D168">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E168">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
@@ -5494,111 +5494,111 @@
         </is>
       </c>
       <c s="12" r="G168">
-        <v>45404</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C169">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D169">
         <v>45471</v>
       </c>
       <c s="11" r="E169">
-        <v>740</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G169">
-        <v>45401</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C170">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D170">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E170">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G170">
-        <v>45384</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C171">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D171">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E171">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G171">
-        <v>45380</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C172">
@@ -5607,134 +5607,134 @@
         </is>
       </c>
       <c s="10" r="D172">
-        <v>45439</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E172">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G172">
-        <v>45379</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C173">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D173">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E173">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G173">
-        <v>45372</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C174">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D174">
-        <v>45433</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E174">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G174">
-        <v>45373</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C175">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E175">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G175">
-        <v>45358</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C176">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45352</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E176">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
@@ -5742,18 +5742,18 @@
         </is>
       </c>
       <c s="12" r="G176">
-        <v>45345</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C177">
@@ -5762,41 +5762,41 @@
         </is>
       </c>
       <c s="10" r="D177">
-        <v>45401</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E177">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G177">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C178">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D178">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E178">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c s="12" r="G178">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="0">
@@ -5815,7 +5815,7 @@
       </c>
       <c s="9" t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C179">
@@ -5827,7 +5827,7 @@
         <v>45337</v>
       </c>
       <c s="11" r="E179">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
@@ -5841,24 +5841,24 @@
     <row r="180" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C180">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D180">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E180">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
@@ -5866,34 +5866,34 @@
         </is>
       </c>
       <c s="12" r="G180">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C181">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D181">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E181">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G181">
@@ -5908,19 +5908,19 @@
       </c>
       <c s="9" t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C182">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D182">
         <v>45382</v>
       </c>
       <c s="11" r="E182">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
@@ -5939,19 +5939,19 @@
       </c>
       <c s="9" t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C183">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D183">
         <v>45382</v>
       </c>
       <c s="11" r="E183">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c s="9" t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C184">
@@ -5982,7 +5982,7 @@
         <v>45382</v>
       </c>
       <c s="11" r="E184">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
@@ -6001,12 +6001,12 @@
       </c>
       <c s="9" t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C185">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D185">
@@ -6027,32 +6027,32 @@
     <row r="186" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C186">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D186">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E186">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F186">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G186">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="0">
@@ -6063,23 +6063,23 @@
       </c>
       <c s="9" t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C187">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D187">
         <v>45366</v>
       </c>
       <c s="11" r="E187">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F187">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G187">
@@ -6089,55 +6089,55 @@
     <row r="188" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C188">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D188">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E188">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G188">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D189">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E189">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c s="12" r="G189">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="0">
@@ -6156,19 +6156,19 @@
       </c>
       <c s="9" t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C190">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D190">
         <v>45275</v>
       </c>
       <c s="11" r="E190">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
@@ -6187,19 +6187,19 @@
       </c>
       <c s="9" t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C191">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D191">
         <v>45275</v>
       </c>
       <c s="11" r="E191">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
@@ -6218,19 +6218,19 @@
       </c>
       <c s="9" t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C192">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D192">
         <v>45275</v>
       </c>
       <c s="11" r="E192">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
@@ -6244,24 +6244,24 @@
     <row r="193" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C193">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D193">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E193">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
@@ -6269,30 +6269,30 @@
         </is>
       </c>
       <c s="12" r="G193">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C194">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D194">
-        <v>45294</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E194">
-        <v>136</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
@@ -6300,30 +6300,30 @@
         </is>
       </c>
       <c s="12" r="G194">
-        <v>45217</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C195">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D195">
-        <v>45473</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E195">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F195">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c s="12" r="G195">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="0">
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c s="10" r="D196">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E196">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F196">
         <is>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c s="10" r="D197">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E197">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
@@ -6399,24 +6399,24 @@
     <row r="198" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C198">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D198">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E198">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
@@ -6424,18 +6424,18 @@
         </is>
       </c>
       <c s="12" r="G198">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C199">
@@ -6447,7 +6447,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E199">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
@@ -6461,12 +6461,12 @@
     <row r="200" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
@@ -6478,7 +6478,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E200">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
@@ -6492,24 +6492,24 @@
     <row r="201" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D201">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E201">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
@@ -6517,61 +6517,61 @@
         </is>
       </c>
       <c s="12" r="G201">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D202">
-        <v>45237</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E202">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F202">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G202">
-        <v>45176</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D203">
-        <v>45387</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E203">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F203">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c s="12" r="G203">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="0">
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c s="10" r="D204">
-        <v>45317</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E204">
         <v>2</v>
@@ -6630,14 +6630,14 @@
         </is>
       </c>
       <c s="10" r="D205">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E205">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F205">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G205">
@@ -6652,7 +6652,7 @@
       </c>
       <c s="9" t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C206">
@@ -6664,11 +6664,11 @@
         <v>45303</v>
       </c>
       <c s="11" r="E206">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F206">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G206">
@@ -6683,7 +6683,7 @@
       </c>
       <c s="9" t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C207">
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c s="10" r="D207">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E207">
         <v>3</v>
@@ -6714,7 +6714,7 @@
       </c>
       <c s="9" t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C208">
@@ -6726,7 +6726,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F208">
         <is>
@@ -6745,7 +6745,7 @@
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c s="10" r="D209">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E209">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F209">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c s="10" r="D210">
-        <v>45247</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E210">
         <v>1</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c s="9" t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C211">
@@ -6816,14 +6816,14 @@
         </is>
       </c>
       <c s="10" r="D211">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E211">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F211">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G211">
@@ -6838,7 +6838,7 @@
       </c>
       <c s="9" t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C212">
@@ -6850,7 +6850,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E212">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F212">
         <is>
@@ -6864,86 +6864,86 @@
     <row r="213" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C213">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D213">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E213">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F213">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G213">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C214">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D214">
-        <v>45199</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E214">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F214">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G214">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C215">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D215">
-        <v>45213</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E215">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F215">
         <is>
@@ -6957,24 +6957,24 @@
     <row r="216" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C216">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D216">
-        <v>45283</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E216">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c s="12" r="G216">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="0">
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c s="10" r="D217">
-        <v>45192</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E217">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
@@ -7019,24 +7019,24 @@
     <row r="218" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C218">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D218">
-        <v>45137</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E218">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c s="12" r="G218">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="0">
@@ -7055,19 +7055,19 @@
       </c>
       <c s="9" t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C219">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D219">
-        <v>45107</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E219">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
@@ -7081,32 +7081,32 @@
     <row r="220" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C220">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D220">
-        <v>45233</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E220">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F220">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G220">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="0">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c s="10" r="D221">
-        <v>45205</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E221">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F221">
         <is>
@@ -7143,24 +7143,24 @@
     <row r="222" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C222">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D222">
-        <v>45175</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E222">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F222">
         <is>
@@ -7168,30 +7168,30 @@
         </is>
       </c>
       <c s="12" r="G222">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C223">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D223">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E223">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F223">
         <is>
@@ -7199,123 +7199,123 @@
         </is>
       </c>
       <c s="12" r="G223">
-        <v>45091</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C224">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D224">
-        <v>45128</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E224">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G224">
-        <v>45090</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C225">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D225">
-        <v>45170</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E225">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G225">
-        <v>45085</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C226">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D226">
-        <v>45106</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E226">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G226">
-        <v>45083</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C227">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D227">
-        <v>45107</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E227">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
@@ -7323,30 +7323,30 @@
         </is>
       </c>
       <c s="12" r="G227">
-        <v>45070</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C228">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D228">
-        <v>45115</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E228">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F228">
         <is>
@@ -7354,61 +7354,61 @@
         </is>
       </c>
       <c s="12" r="G228">
-        <v>45055</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C229">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D229">
-        <v>45105</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E229">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F229">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G229">
-        <v>45044</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D230">
-        <v>45135</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E230">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
@@ -7416,30 +7416,30 @@
         </is>
       </c>
       <c s="12" r="G230">
-        <v>45041</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D231">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E231">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c s="12" r="G231">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="0">
@@ -7458,12 +7458,12 @@
       </c>
       <c s="9" t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C232">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D232">
@@ -7489,12 +7489,12 @@
       </c>
       <c s="9" t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D233">
@@ -7520,12 +7520,12 @@
       </c>
       <c s="9" t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C234">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D234">
@@ -7551,12 +7551,12 @@
       </c>
       <c s="9" t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C235">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D235">
@@ -7577,86 +7577,86 @@
     <row r="236" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C236">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D236">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E236">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F236">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G236">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D237">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E237">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F237">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G237">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C238">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45058</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E238">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F238">
         <is>
@@ -7670,24 +7670,24 @@
     <row r="239" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E239">
-        <v>379</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F239">
         <is>
@@ -7695,30 +7695,30 @@
         </is>
       </c>
       <c s="12" r="G239">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D240">
         <v>45079</v>
       </c>
       <c s="11" r="E240">
-        <v>201</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
@@ -7732,12 +7732,12 @@
     <row r="241" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
@@ -7746,103 +7746,103 @@
         </is>
       </c>
       <c s="10" r="D241">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E241">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G241">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D242">
-        <v>44939</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E242">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F242">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G242">
-        <v>44937</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D243">
-        <v>44890</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E243">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F243">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G243">
-        <v>44827</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D244">
-        <v>44907</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E244">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F244">
         <is>
@@ -7850,30 +7850,30 @@
         </is>
       </c>
       <c s="12" r="G244">
-        <v>44846</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C245">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D245">
-        <v>44911</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E245">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F245">
         <is>
@@ -7881,80 +7881,80 @@
         </is>
       </c>
       <c s="12" r="G245">
-        <v>44845</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C246">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D246">
-        <v>44869</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E246">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F246">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G246">
-        <v>44812</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>44866</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E247">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G247">
-        <v>44803</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
@@ -7963,41 +7963,41 @@
         </is>
       </c>
       <c s="10" r="D248">
-        <v>44856</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E248">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G248">
-        <v>44795</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C249">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D249">
-        <v>44815</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E249">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F249">
         <is>
@@ -8005,30 +8005,30 @@
         </is>
       </c>
       <c s="12" r="G249">
-        <v>44755</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C250">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D250">
-        <v>44802</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E250">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F250">
         <is>
@@ -8036,30 +8036,30 @@
         </is>
       </c>
       <c s="12" r="G250">
-        <v>44741</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D251">
-        <v>44865</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E251">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F251">
         <is>
@@ -8067,7 +8067,7 @@
         </is>
       </c>
       <c s="12" r="G251">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="0">
@@ -8087,10 +8087,10 @@
         </is>
       </c>
       <c s="10" r="D252">
-        <v>44805</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E252">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F252">
         <is>
@@ -8104,74 +8104,74 @@
     <row r="253" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C253">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D253">
-        <v>44712</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E253">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F253">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G253">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C254">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D254">
-        <v>44600</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E254">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F254">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G254">
-        <v>44600</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
@@ -8180,10 +8180,10 @@
         </is>
       </c>
       <c s="10" r="D255">
-        <v>44652</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E255">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F255">
         <is>
@@ -8191,30 +8191,30 @@
         </is>
       </c>
       <c s="12" r="G255">
-        <v>44578</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D256">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E256">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
@@ -8222,7 +8222,7 @@
         </is>
       </c>
       <c s="12" r="G256">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="0">
@@ -8245,7 +8245,7 @@
         <v>44620</v>
       </c>
       <c s="11" r="E257">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
@@ -8259,24 +8259,24 @@
     <row r="258" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C258">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D258">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E258">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
@@ -8284,30 +8284,30 @@
         </is>
       </c>
       <c s="12" r="G258">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C259">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D259">
-        <v>44531</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E259">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
@@ -8315,30 +8315,30 @@
         </is>
       </c>
       <c s="12" r="G259">
-        <v>44470</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D260">
-        <v>44799</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E260">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F260">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c s="12" r="G260">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="0">
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c s="10" r="D261">
-        <v>44743</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E261">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F261">
         <is>
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c s="10" r="D262">
-        <v>44680</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E262">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F262">
         <is>
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c s="10" r="D263">
-        <v>44652</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E263">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F263">
         <is>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c s="10" r="D264">
-        <v>44575</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E264">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F264">
         <is>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c s="10" r="D265">
-        <v>44512</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E265">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
@@ -8507,12 +8507,12 @@
     <row r="266" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C266">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c s="10" r="D266">
-        <v>44469</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E266">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
@@ -8532,30 +8532,30 @@
         </is>
       </c>
       <c s="12" r="G266">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C267">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D267">
-        <v>44482</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E267">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
@@ -8563,30 +8563,30 @@
         </is>
       </c>
       <c s="12" r="G267">
-        <v>44421</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C268">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D268">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E268">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c s="12" r="G268">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="0">
@@ -8605,7 +8605,7 @@
       </c>
       <c s="9" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C269">
@@ -8617,7 +8617,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E269">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
@@ -8636,19 +8636,19 @@
       </c>
       <c s="9" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C270">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D270">
         <v>44469</v>
       </c>
       <c s="11" r="E270">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
@@ -8662,24 +8662,24 @@
     <row r="271" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C271">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D271">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E271">
-        <v>402</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
@@ -8687,30 +8687,30 @@
         </is>
       </c>
       <c s="12" r="G271">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C272">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D272">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E272">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
@@ -8718,18 +8718,18 @@
         </is>
       </c>
       <c s="12" r="G272">
-        <v>44383</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C273">
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44348</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E273">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
@@ -8749,18 +8749,18 @@
         </is>
       </c>
       <c s="12" r="G273">
-        <v>44308</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C274">
@@ -8769,49 +8769,49 @@
         </is>
       </c>
       <c s="10" r="D274">
-        <v>44347</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E274">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G274">
-        <v>44291</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C275">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D275">
-        <v>44311</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E275">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G275">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="0">
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c s="10" r="D276">
-        <v>44256</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E276">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
@@ -8848,32 +8848,32 @@
     <row r="277" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C277">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44358</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E277">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G277">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="0">
@@ -8893,10 +8893,10 @@
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44330</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E278">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c s="10" r="D279">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E279">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c s="10" r="D280">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E280">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8972,12 +8972,12 @@
     <row r="281" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C281">
@@ -8989,7 +8989,7 @@
         <v>44288</v>
       </c>
       <c s="11" r="E281">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
@@ -9003,24 +9003,24 @@
     <row r="282" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C282">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D282">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E282">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c s="12" r="G282">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="0">
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c s="10" r="D283">
-        <v>44264</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E283">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
@@ -9065,24 +9065,24 @@
     <row r="284" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C284">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44242</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E284">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
@@ -9090,100 +9090,100 @@
         </is>
       </c>
       <c s="12" r="G284">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C285">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D285">
-        <v>44270</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E285">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G285">
-        <v>44168</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C286">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D286">
-        <v>44214</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E286">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G286">
-        <v>44160</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C287">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D287">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E287">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G287">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="0">
@@ -9206,11 +9206,11 @@
         <v>44211</v>
       </c>
       <c s="11" r="E288">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G288">
@@ -9220,12 +9220,12 @@
     <row r="289" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C289">
@@ -9234,29 +9234,29 @@
         </is>
       </c>
       <c s="10" r="D289">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E289">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G289">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C290">
@@ -9265,69 +9265,69 @@
         </is>
       </c>
       <c s="10" r="D290">
-        <v>44214</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E290">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G290">
-        <v>44151</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C291">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D291">
-        <v>44186</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E291">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G291">
-        <v>44127</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C292">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D292">
-        <v>44104</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E292">
         <v>59</v>
@@ -9338,100 +9338,100 @@
         </is>
       </c>
       <c s="12" r="G292">
-        <v>44104</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C293">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44197</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E293">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F293">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G293">
-        <v>44151</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">7241</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">SP+</t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C294">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Elgin</t>
         </is>
       </c>
       <c s="10" r="D294">
-        <v>43914</v>
+        <v>44197</v>
       </c>
       <c s="11" r="E294">
-        <v>89</v>
+        <v>229</v>
       </c>
       <c s="9" t="inlineStr" r="F294">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G294">
-        <v>44099</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">7218</t>
+          <t xml:space="preserve">7241</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
+          <t xml:space="preserve">SP+</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C295">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D295">
-        <v>43903</v>
+        <v>43914</v>
       </c>
       <c s="11" r="E295">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G295">
-        <v>44091</v>
+        <v>44099</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="0">
@@ -9442,19 +9442,19 @@
       </c>
       <c s="9" t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
+          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C296">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D296">
         <v>43903</v>
       </c>
       <c s="11" r="E296">
-        <v>358</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
@@ -9473,19 +9473,19 @@
       </c>
       <c s="9" t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">Sodexo - Medford SD</t>
+          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C297">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D297">
         <v>43903</v>
       </c>
       <c s="11" r="E297">
-        <v>111</v>
+        <v>358</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
@@ -9499,32 +9499,32 @@
     <row r="298" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">7217</t>
+          <t xml:space="preserve">7218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">PF Chang's</t>
+          <t xml:space="preserve">Sodexo - Medford SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C298">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D298">
-        <v>44092</v>
+        <v>43903</v>
       </c>
       <c s="11" r="E298">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G298">
-        <v>44092</v>
+        <v>44091</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="0">
@@ -9535,12 +9535,12 @@
       </c>
       <c s="9" t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">PF Chang's - Eugene</t>
+          <t xml:space="preserve">PF Chang's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C299">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D299">
@@ -9561,32 +9561,32 @@
     <row r="300" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">7215</t>
+          <t xml:space="preserve">7217</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Salem</t>
+          <t xml:space="preserve">PF Chang's - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C300">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D300">
-        <v>44137</v>
+        <v>44092</v>
       </c>
       <c s="11" r="E300">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F300">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G300">
-        <v>44077</v>
+        <v>44092</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="0">
@@ -9597,19 +9597,19 @@
       </c>
       <c s="9" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Portland</t>
+          <t xml:space="preserve">LAGS Medical Center - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C301">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D301">
         <v>44137</v>
       </c>
       <c s="11" r="E301">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F301">
         <is>
@@ -9623,12 +9623,12 @@
     <row r="302" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">7211</t>
+          <t xml:space="preserve">7215</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">Bon Appetit</t>
+          <t xml:space="preserve">LAGS Medical Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C302">
@@ -9637,18 +9637,18 @@
         </is>
       </c>
       <c s="10" r="D302">
-        <v>44104</v>
+        <v>44137</v>
       </c>
       <c s="11" r="E302">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F302">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G302">
-        <v>44075</v>
+        <v>44077</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="0">
@@ -9671,11 +9671,11 @@
         <v>44104</v>
       </c>
       <c s="11" r="E303">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c s="9" t="inlineStr" r="F303">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G303">
@@ -9685,24 +9685,24 @@
     <row r="304" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">7209</t>
+          <t xml:space="preserve">7211</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">Dave &amp; Buster's</t>
+          <t xml:space="preserve">Bon Appetit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C304">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D304">
-        <v>44143</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E304">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
@@ -9710,123 +9710,123 @@
         </is>
       </c>
       <c s="12" r="G304">
-        <v>44082</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">7207</t>
+          <t xml:space="preserve">7209</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">PGE - Boardman</t>
+          <t xml:space="preserve">Dave &amp; Buster's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C305">
         <is>
-          <t xml:space="preserve">Boardman</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D305">
-        <v>44140</v>
+        <v>44143</v>
       </c>
       <c s="11" r="E305">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G305">
-        <v>44075</v>
+        <v>44082</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">7199</t>
+          <t xml:space="preserve">7207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">LAIKA</t>
+          <t xml:space="preserve">PGE - Boardman</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C306">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Boardman</t>
         </is>
       </c>
       <c s="10" r="D306">
+        <v>44140</v>
+      </c>
+      <c s="11" r="E306">
+        <v>22</v>
+      </c>
+      <c s="9" t="inlineStr" r="F306">
+        <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G306">
         <v>44075</v>
-      </c>
-      <c s="11" r="E306">
-        <v>50</v>
-      </c>
-      <c s="9" t="inlineStr" r="F306">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G306">
-        <v>44057</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">7192</t>
+          <t xml:space="preserve">7199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">HMSHost</t>
+          <t xml:space="preserve">LAIKA</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C307">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D307">
-        <v>44119</v>
+        <v>44075</v>
       </c>
       <c s="11" r="E307">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F307">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G307">
-        <v>44054</v>
+        <v>44057</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">7186</t>
+          <t xml:space="preserve">7192</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">HMSHost</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C308">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D308">
-        <v>44124</v>
+        <v>44119</v>
       </c>
       <c s="11" r="E308">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F308">
         <is>
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c s="12" r="G308">
-        <v>44032</v>
+        <v>44054</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="0">
@@ -9845,19 +9845,19 @@
       </c>
       <c s="9" t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C309">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D309">
-        <v>44099</v>
+        <v>44124</v>
       </c>
       <c s="11" r="E309">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F309">
         <is>
@@ -9876,19 +9876,19 @@
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D310">
         <v>44099</v>
       </c>
       <c s="11" r="E310">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F310">
         <is>
@@ -9902,24 +9902,24 @@
     <row r="311" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">7185</t>
+          <t xml:space="preserve">7186</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C311">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D311">
-        <v>44105</v>
+        <v>44099</v>
       </c>
       <c s="11" r="E311">
-        <v>277</v>
+        <v>355</v>
       </c>
       <c s="9" t="inlineStr" r="F311">
         <is>
@@ -9927,18 +9927,18 @@
         </is>
       </c>
       <c s="12" r="G311">
-        <v>44041</v>
+        <v>44032</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">7184</t>
+          <t xml:space="preserve">7185</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
+          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C312">
@@ -9947,29 +9947,29 @@
         </is>
       </c>
       <c s="10" r="D312">
-        <v>43910</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E312">
-        <v>70</v>
+        <v>277</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G312">
-        <v>44043</v>
+        <v>44041</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">7171</t>
+          <t xml:space="preserve">7184</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
+          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
@@ -9978,10 +9978,10 @@
         </is>
       </c>
       <c s="10" r="D313">
-        <v>44105</v>
+        <v>43910</v>
       </c>
       <c s="11" r="E313">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
@@ -9995,32 +9995,32 @@
     <row r="314" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">7162</t>
+          <t xml:space="preserve">7171</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">Nike - Childcare  </t>
+          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D314">
         <v>44105</v>
       </c>
       <c s="11" r="E314">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c s="9" t="inlineStr" r="F314">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G314">
-        <v>44035</v>
+        <v>44043</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="0">
@@ -10031,7 +10031,7 @@
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">Nike</t>
+          <t xml:space="preserve">Nike - Childcare  </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
@@ -10043,7 +10043,7 @@
         <v>44105</v>
       </c>
       <c s="11" r="E315">
-        <v>308</v>
+        <v>192</v>
       </c>
       <c s="9" t="inlineStr" r="F315">
         <is>
@@ -10071,10 +10071,10 @@
         </is>
       </c>
       <c s="10" r="D316">
-        <v>44035</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E316">
-        <v>700</v>
+        <v>308</v>
       </c>
       <c s="9" t="inlineStr" r="F316">
         <is>
@@ -10088,59 +10088,59 @@
     <row r="317" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">7151</t>
+          <t xml:space="preserve">7162</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">American Queen Steamboat Company </t>
+          <t xml:space="preserve">Nike</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C317">
         <is>
-          <t xml:space="preserve">New Albany, IN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D317">
-        <v>44098</v>
+        <v>44035</v>
       </c>
       <c s="11" r="E317">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c s="9" t="inlineStr" r="F317">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G317">
-        <v>44034</v>
+        <v>44035</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">7135</t>
+          <t xml:space="preserve">7151</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">Vesta </t>
+          <t xml:space="preserve">American Queen Steamboat Company </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C318">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">New Albany, IN</t>
         </is>
       </c>
       <c s="10" r="D318">
-        <v>44034</v>
+        <v>44098</v>
       </c>
       <c s="11" r="E318">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c s="9" t="inlineStr" r="F318">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G318">
@@ -10150,24 +10150,24 @@
     <row r="319" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">7134</t>
+          <t xml:space="preserve">7135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">Pioneer Pacific College</t>
+          <t xml:space="preserve">Vesta </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C319">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D319">
-        <v>44043</v>
+        <v>44034</v>
       </c>
       <c s="11" r="E319">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F319">
         <is>
@@ -10175,7 +10175,7 @@
         </is>
       </c>
       <c s="12" r="G319">
-        <v>44033</v>
+        <v>44034</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="0">
@@ -10186,19 +10186,19 @@
       </c>
       <c s="9" t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">Pioneer Pacific College - Beaverton</t>
+          <t xml:space="preserve">Pioneer Pacific College</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C320">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D320">
         <v>44043</v>
       </c>
       <c s="11" r="E320">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F320">
         <is>
@@ -10217,19 +10217,19 @@
       </c>
       <c s="9" t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">Pioneer Pacific College - Springfield</t>
+          <t xml:space="preserve">Pioneer Pacific College - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C321">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D321">
         <v>44043</v>
       </c>
       <c s="11" r="E321">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F321">
         <is>
@@ -10243,32 +10243,32 @@
     <row r="322" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">7071</t>
+          <t xml:space="preserve">7134</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">United - PDX</t>
+          <t xml:space="preserve">Pioneer Pacific College - Springfield</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C322">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D322">
-        <v>44105</v>
+        <v>44043</v>
       </c>
       <c s="11" r="E322">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F322">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G322">
-        <v>44020</v>
+        <v>44033</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="0">
@@ -10291,7 +10291,7 @@
         <v>44105</v>
       </c>
       <c s="11" r="E323">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c s="9" t="inlineStr" r="F323">
         <is>
@@ -10305,24 +10305,24 @@
     <row r="324" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">7070</t>
+          <t xml:space="preserve">7071</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">arauco - Albany </t>
+          <t xml:space="preserve">United - PDX</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C324">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D324">
-        <v>44018</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E324">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F324">
         <is>
@@ -10330,30 +10330,30 @@
         </is>
       </c>
       <c s="12" r="G324">
-        <v>44018</v>
+        <v>44020</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">7057</t>
+          <t xml:space="preserve">7070</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">Hampton Inn &amp; Suites - Portland</t>
+          <t xml:space="preserve">arauco - Albany </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C325">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D325">
-        <v>44012</v>
+        <v>44018</v>
       </c>
       <c s="11" r="E325">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F325">
         <is>
@@ -10367,12 +10367,12 @@
     <row r="326" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">7056</t>
+          <t xml:space="preserve">7057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">Atrium Hospitality - Portland Embassy S</t>
+          <t xml:space="preserve">Hampton Inn &amp; Suites - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C326">
@@ -10381,29 +10381,29 @@
         </is>
       </c>
       <c s="10" r="D326">
-        <v>43902</v>
+        <v>44012</v>
       </c>
       <c s="11" r="E326">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F326">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G326">
-        <v>43964</v>
+        <v>44018</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">7052</t>
+          <t xml:space="preserve">7056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">Hilton Portland Downtown</t>
+          <t xml:space="preserve">Atrium Hospitality - Portland Embassy S</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C327">
@@ -10412,10 +10412,10 @@
         </is>
       </c>
       <c s="10" r="D327">
-        <v>43912</v>
+        <v>43902</v>
       </c>
       <c s="11" r="E327">
-        <v>330</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F327">
         <is>
@@ -10423,127 +10423,159 @@
         </is>
       </c>
       <c s="12" r="G327">
-        <v>44012</v>
+        <v>43964</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7052</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Hilton Portland Downtown</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C328">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D328"/>
-      <c s="13" t="str" r="E328"/>
+          <t xml:space="preserve">Portland</t>
+        </is>
+      </c>
+      <c s="10" r="D328">
+        <v>43912</v>
+      </c>
+      <c s="11" r="E328">
+        <v>330</v>
+      </c>
       <c s="9" t="inlineStr" r="F328">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G328">
-        <v>44909</v>
+        <v>44012</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C329">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D329"/>
       <c s="13" t="str" r="E329"/>
       <c s="9" t="inlineStr" r="F329">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G329">
-        <v>45125</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C330">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">Mesa, AZ</t>
         </is>
       </c>
       <c s="9" t="str" r="D330"/>
       <c s="13" t="str" r="E330"/>
       <c s="9" t="inlineStr" r="F330">
         <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G330">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="331" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A331">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B331">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C331">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D331"/>
+      <c s="13" t="str" r="E331"/>
+      <c s="9" t="inlineStr" r="F331">
+        <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
-      <c s="12" r="G330">
+      <c s="12" r="G331">
         <v>45887</v>
       </c>
     </row>
-    <row r="331" ht="3.6" customHeight="0">
-      <c s="14" t="inlineStr" r="A331">
+    <row r="332" ht="3.55" customHeight="0">
+      <c s="14" t="inlineStr" r="A332">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B331">
+      <c s="14" t="inlineStr" r="B332">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C331">
+      <c s="14" t="inlineStr" r="C332">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D331">
+      <c s="14" t="inlineStr" r="D332">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E331">
+      <c s="14" t="inlineStr" r="E332">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F331">
+      <c s="14" t="inlineStr" r="F332">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G331">
+      <c s="14" t="inlineStr" r="G332">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
+    <row r="333" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:A2"/>
@@ -10553,7 +10585,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/31/2026 6:53:02 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/31/2026 7:10:28 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 7/31/2016 to 7/31/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/1/2016 to 8/1/2026</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10585,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 7/31/2026 7:10:28 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/1/2026 6:16:47 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10585,7 +10585,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/1/2026 6:16:47 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/1/2026 7:15:34 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/1/2016 to 8/1/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/2/2016 to 8/2/2026</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10585,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/1/2026 7:15:34 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/2/2026 6:24:22 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10585,7 +10585,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/2/2026 6:24:22 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/2/2026 6:54:08 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/2/2016 to 8/2/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/3/2016 to 8/3/2026</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10585,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/2/2026 6:54:08 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/3/2026 7:36:02 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10585,7 +10585,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/3/2026 7:36:02 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/3/2026 6:46:38 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/3/2016 to 8/3/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/4/2016 to 8/4/2026</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10585,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/3/2026 6:46:38 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/4/2026 7:07:49 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -385,94 +385,94 @@
     <row r="4" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">9549</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
+          <t xml:space="preserve">Avamere Health Services, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tigard</t>
         </is>
       </c>
       <c s="10" r="D4">
-        <v>46325</v>
+        <v>46266</v>
       </c>
       <c s="11" r="E4">
-        <v>387</v>
+        <v>129</v>
       </c>
       <c s="9" t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G4">
-        <v>46233</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">9534</t>
+          <t xml:space="preserve">9549</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
+          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D5">
-        <v>46262</v>
+        <v>46325</v>
       </c>
       <c s="11" r="E5">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c s="9" t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G5">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">Adventist Health Tillamook</t>
+          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D6">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c s="11" r="E6">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c s="9" t="inlineStr" r="F6">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G6">
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="0">
@@ -483,19 +483,19 @@
       </c>
       <c s="9" t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">Adventist Health Portland</t>
+          <t xml:space="preserve">Adventist Health Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">Portland, </t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D7">
         <v>46206</v>
       </c>
       <c s="11" r="E7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F7">
         <is>
@@ -514,19 +514,19 @@
       </c>
       <c s="9" t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
+          <t xml:space="preserve">Adventist Health Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">The Dalles</t>
+          <t xml:space="preserve">Portland, </t>
         </is>
       </c>
       <c s="10" r="D8">
         <v>46206</v>
       </c>
       <c s="11" r="E8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F8">
         <is>
@@ -540,32 +540,32 @@
     <row r="9" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">PacificSource</t>
+          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">The Dalles</t>
         </is>
       </c>
       <c s="10" r="D9">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E9">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F9">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G9">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="0">
@@ -576,23 +576,23 @@
       </c>
       <c s="9" t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">PacificSource - Bend</t>
+          <t xml:space="preserve">PacificSource</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D10">
         <v>46234</v>
       </c>
       <c s="11" r="E10">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G10">
@@ -607,19 +607,19 @@
       </c>
       <c s="9" t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">PacificSource - Portland</t>
+          <t xml:space="preserve">PacificSource - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D11">
         <v>46234</v>
       </c>
       <c s="11" r="E11">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F11">
         <is>
@@ -638,12 +638,12 @@
       </c>
       <c s="9" t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">PacificSource - Salem</t>
+          <t xml:space="preserve">PacificSource - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D12">
@@ -669,19 +669,19 @@
       </c>
       <c s="9" t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">PacificSource Hood River</t>
+          <t xml:space="preserve">PacificSource - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D13">
         <v>46234</v>
       </c>
       <c s="11" r="E13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F13">
         <is>
@@ -695,63 +695,63 @@
     <row r="14" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">9511</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
+          <t xml:space="preserve">PacificSource Hood River</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D14">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E14">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F14">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G14">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9511</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D15">
-        <v>46234</v>
+        <v>46228</v>
       </c>
       <c s="11" r="E15">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G15">
-        <v>46160</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="0">
@@ -762,19 +762,19 @@
       </c>
       <c s="9" t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D16">
         <v>46234</v>
       </c>
       <c s="11" r="E16">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F16">
         <is>
@@ -793,19 +793,19 @@
       </c>
       <c s="9" t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C17">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D17">
         <v>46234</v>
       </c>
       <c s="11" r="E17">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F17">
         <is>
@@ -824,19 +824,19 @@
       </c>
       <c s="9" t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D18">
         <v>46234</v>
       </c>
       <c s="11" r="E18">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F18">
         <is>
@@ -855,19 +855,19 @@
       </c>
       <c s="9" t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D19">
         <v>46234</v>
       </c>
       <c s="11" r="E19">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c s="9" t="inlineStr" r="F19">
         <is>
@@ -881,86 +881,86 @@
     <row r="20" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D20">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E20">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G20">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D21">
-        <v>46201</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E21">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G21">
-        <v>46141</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D22">
-        <v>46295</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E22">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F22">
         <is>
@@ -968,49 +968,49 @@
         </is>
       </c>
       <c s="12" r="G22">
-        <v>46114</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D23">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E23">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G23">
-        <v>46108</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C24">
@@ -1019,18 +1019,18 @@
         </is>
       </c>
       <c s="10" r="D24">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E24">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G24">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="0">
@@ -1041,7 +1041,7 @@
       </c>
       <c s="9" t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C25">
@@ -1067,24 +1067,24 @@
     <row r="26" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D26">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E26">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F26">
         <is>
@@ -1092,38 +1092,38 @@
         </is>
       </c>
       <c s="12" r="G26">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D27">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E27">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G27">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="0">
@@ -1134,19 +1134,19 @@
       </c>
       <c s="9" t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D28">
         <v>46131</v>
       </c>
       <c s="11" r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F28">
         <is>
@@ -1160,63 +1160,63 @@
     <row r="29" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D29">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E29">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G29">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D30">
         <v>46117</v>
       </c>
       <c s="11" r="E30">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G30">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="0">
@@ -1227,19 +1227,19 @@
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D31">
         <v>46117</v>
       </c>
       <c s="11" r="E31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F31">
         <is>
@@ -1258,12 +1258,12 @@
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D32">
@@ -1289,12 +1289,12 @@
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D33">
@@ -1320,12 +1320,12 @@
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D34">
@@ -1351,12 +1351,12 @@
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D35">
@@ -1382,12 +1382,12 @@
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D36">
@@ -1413,12 +1413,12 @@
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D37">
@@ -1444,7 +1444,7 @@
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
@@ -1475,7 +1475,7 @@
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
@@ -1506,12 +1506,12 @@
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D40">
@@ -1537,12 +1537,12 @@
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D41">
@@ -1568,12 +1568,12 @@
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D42">
@@ -1599,7 +1599,7 @@
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
@@ -1630,19 +1630,19 @@
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D44">
         <v>46117</v>
       </c>
       <c s="11" r="E44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F44">
         <is>
@@ -1661,19 +1661,19 @@
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D45">
         <v>46117</v>
       </c>
       <c s="11" r="E45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F45">
         <is>
@@ -1692,19 +1692,19 @@
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D46">
         <v>46117</v>
       </c>
       <c s="11" r="E46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F46">
         <is>
@@ -1723,12 +1723,12 @@
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D47">
@@ -1754,12 +1754,12 @@
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D48">
@@ -1780,24 +1780,24 @@
     <row r="49" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D49">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E49">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F49">
         <is>
@@ -1816,19 +1816,19 @@
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D50">
         <v>46112</v>
       </c>
       <c s="11" r="E50">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F50">
         <is>
@@ -1847,19 +1847,19 @@
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D51">
         <v>46112</v>
       </c>
       <c s="11" r="E51">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F51">
         <is>
@@ -1873,24 +1873,24 @@
     <row r="52" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D52">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E52">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F52">
         <is>
@@ -1898,30 +1898,30 @@
         </is>
       </c>
       <c s="12" r="G52">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D53">
-        <v>46142</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E53">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F53">
         <is>
@@ -1929,30 +1929,30 @@
         </is>
       </c>
       <c s="12" r="G53">
-        <v>46020</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D54">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E54">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F54">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c s="12" r="G54">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="0">
@@ -1971,7 +1971,7 @@
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
@@ -1983,7 +1983,7 @@
         <v>46014</v>
       </c>
       <c s="11" r="E55">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F55">
         <is>
@@ -2002,19 +2002,19 @@
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D56">
         <v>46014</v>
       </c>
       <c s="11" r="E56">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F56">
         <is>
@@ -2028,43 +2028,43 @@
     <row r="57" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D57">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E57">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F57">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G57">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
@@ -2073,29 +2073,29 @@
         </is>
       </c>
       <c s="10" r="D58">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E58">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F58">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G58">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c s="10" r="D59">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E59">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F59">
         <is>
@@ -2121,63 +2121,63 @@
     <row r="60" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D60">
         <v>46054</v>
       </c>
       <c s="11" r="E60">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F60">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G60">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D61">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E61">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F61">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G61">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="0">
@@ -2188,19 +2188,19 @@
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D62">
         <v>45916</v>
       </c>
       <c s="11" r="E62">
-        <v>510</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F62">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
@@ -2231,7 +2231,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E63">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F63">
         <is>
@@ -2250,7 +2250,7 @@
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
@@ -2262,7 +2262,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E64">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F64">
         <is>
@@ -2276,24 +2276,24 @@
     <row r="65" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D65">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E65">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F65">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c s="12" r="G65">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="0">
@@ -2312,23 +2312,23 @@
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D66">
         <v>46022</v>
       </c>
       <c s="11" r="E66">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F66">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G66">
@@ -2343,19 +2343,19 @@
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D67">
         <v>46022</v>
       </c>
       <c s="11" r="E67">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F67">
         <is>
@@ -2374,19 +2374,19 @@
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D68">
         <v>46022</v>
       </c>
       <c s="11" r="E68">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F68">
         <is>
@@ -2405,19 +2405,19 @@
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D69">
         <v>46022</v>
       </c>
       <c s="11" r="E69">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F69">
         <is>
@@ -2431,55 +2431,55 @@
     <row r="70" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D70">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E70">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F70">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G70">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D71">
         <v>46017</v>
       </c>
       <c s="11" r="E71">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F71">
         <is>
@@ -2493,28 +2493,28 @@
     <row r="72" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C72">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D72">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E72">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G72">
@@ -2538,14 +2538,14 @@
         </is>
       </c>
       <c s="10" r="D73">
-        <v>46017</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E73">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G73">
@@ -2555,86 +2555,86 @@
     <row r="74" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D74">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E74">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F74">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G74">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D75">
-        <v>46022</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E75">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F75">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G75">
-        <v>45917</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D76">
-        <v>45978</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E76">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F76">
         <is>
@@ -2642,18 +2642,18 @@
         </is>
       </c>
       <c s="12" r="G76">
-        <v>45943</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c s="10" r="D77">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E77">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
@@ -2673,38 +2673,38 @@
         </is>
       </c>
       <c s="12" r="G77">
-        <v>45930</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C78">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D78">
-        <v>45940</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E78">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G78">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="0">
@@ -2724,14 +2724,14 @@
         </is>
       </c>
       <c s="10" r="D79">
-        <v>45925</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E79">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G79">
@@ -2741,24 +2741,24 @@
     <row r="80" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C80">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D80">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E80">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
@@ -2766,34 +2766,34 @@
         </is>
       </c>
       <c s="12" r="G80">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D81">
         <v>45976</v>
       </c>
       <c s="11" r="E81">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G81">
@@ -2803,63 +2803,63 @@
     <row r="82" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C82">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D82">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E82">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G82">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C83">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D83">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E83">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G83">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="0">
@@ -2870,7 +2870,7 @@
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
@@ -2882,7 +2882,7 @@
         <v>45949</v>
       </c>
       <c s="11" r="E84">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
@@ -2896,12 +2896,12 @@
     <row r="85" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
@@ -2910,41 +2910,41 @@
         </is>
       </c>
       <c s="10" r="D85">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E85">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G85">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D86">
-        <v>45874</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E86">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
@@ -2952,18 +2952,18 @@
         </is>
       </c>
       <c s="12" r="G86">
-        <v>45867</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
@@ -2972,49 +2972,49 @@
         </is>
       </c>
       <c s="10" r="D87">
-        <v>45920</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E87">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G87">
-        <v>45854</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D88">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E88">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G88">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="0">
@@ -3025,19 +3025,19 @@
       </c>
       <c s="9" t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C89">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D89">
         <v>45912</v>
       </c>
       <c s="11" r="E89">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
@@ -3051,63 +3051,63 @@
     <row r="90" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C90">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D90">
         <v>45912</v>
       </c>
       <c s="11" r="E90">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G90">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C91">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D91">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E91">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G91">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="0">
@@ -3118,19 +3118,19 @@
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D92">
         <v>45853</v>
       </c>
       <c s="11" r="E92">
-        <v>1544</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
@@ -3161,7 +3161,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E93">
-        <v>174</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
@@ -3180,7 +3180,7 @@
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
@@ -3192,7 +3192,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E94">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
@@ -3206,86 +3206,86 @@
     <row r="95" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C95">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D95">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E95">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G95">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D96">
-        <v>45901</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E96">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G96">
-        <v>45839</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C97">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D97">
-        <v>45982</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E97">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c s="12" r="G97">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="0">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c s="10" r="D98">
-        <v>45968</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E98">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c s="10" r="D99">
-        <v>45894</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E99">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
@@ -3361,24 +3361,24 @@
     <row r="100" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C100">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D100">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E100">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
@@ -3386,30 +3386,30 @@
         </is>
       </c>
       <c s="12" r="G100">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C101">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D101">
         <v>45838</v>
       </c>
       <c s="11" r="E101">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
@@ -3423,94 +3423,94 @@
     <row r="102" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D102">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E102">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G102">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D103">
-        <v>45807</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E103">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G103">
-        <v>45804</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D104">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E104">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G104">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="0">
@@ -3521,19 +3521,19 @@
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D105">
         <v>45866</v>
       </c>
       <c s="11" r="E105">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
@@ -3547,55 +3547,55 @@
     <row r="106" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D106">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E106">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G106">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D107">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E107">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
@@ -3603,85 +3603,85 @@
         </is>
       </c>
       <c s="12" r="G107">
-        <v>45778</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D108">
-        <v>45769</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E108">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G108">
-        <v>45769</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D109">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E109">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G109">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D110">
@@ -3692,69 +3692,69 @@
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G110">
-        <v>45763</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D111">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E111">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G111">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D112">
-        <v>45810</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E112">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G112">
@@ -3764,43 +3764,43 @@
     <row r="113" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D113">
-        <v>45808</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E113">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G113">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C114">
@@ -3809,103 +3809,103 @@
         </is>
       </c>
       <c s="10" r="D114">
-        <v>45834</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E114">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G114">
-        <v>45774</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C115">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D115">
-        <v>45838</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E115">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G115">
-        <v>45744</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D116">
-        <v>45706</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E116">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G116">
-        <v>45706</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D117">
-        <v>45734</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E117">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
@@ -3913,38 +3913,38 @@
         </is>
       </c>
       <c s="12" r="G117">
-        <v>45666</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D118">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E118">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G118">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="0">
@@ -3955,19 +3955,19 @@
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D119">
         <v>45707</v>
       </c>
       <c s="11" r="E119">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
@@ -3981,63 +3981,63 @@
     <row r="120" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D120">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E120">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G120">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D121">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E121">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G121">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="0">
@@ -4048,19 +4048,19 @@
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D122">
         <v>45696</v>
       </c>
       <c s="11" r="E122">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
@@ -4074,86 +4074,86 @@
     <row r="123" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D123">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E123">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G123">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D124">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E124">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G124">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D125">
         <v>45931</v>
       </c>
       <c s="11" r="E125">
-        <v>221</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
@@ -4167,43 +4167,43 @@
     <row r="126" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C126">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D126">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E126">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G126">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C127">
@@ -4212,18 +4212,18 @@
         </is>
       </c>
       <c s="10" r="D127">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E127">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G127">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="0">
@@ -4234,19 +4234,19 @@
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D128">
         <v>45726</v>
       </c>
       <c s="11" r="E128">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
@@ -4265,19 +4265,19 @@
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D129">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E129">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
@@ -4296,19 +4296,19 @@
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D130">
         <v>45725</v>
       </c>
       <c s="11" r="E130">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
@@ -4327,19 +4327,19 @@
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D131">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E131">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F131">
         <is>
@@ -4358,12 +4358,12 @@
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D132">
@@ -4389,12 +4389,12 @@
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D133">
@@ -4420,7 +4420,7 @@
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c s="10" r="D134">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E134">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F134">
         <is>
@@ -4451,19 +4451,19 @@
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D135">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E135">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
@@ -4482,7 +4482,7 @@
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c s="10" r="D136">
-        <v>45703</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E136">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
@@ -4513,19 +4513,19 @@
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D137">
-        <v>45690</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E137">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
@@ -4539,12 +4539,12 @@
     <row r="138" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
@@ -4553,72 +4553,72 @@
         </is>
       </c>
       <c s="10" r="D138">
-        <v>45657</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E138">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G138">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D139">
-        <v>45640</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E139">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G139">
-        <v>45580</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D140">
-        <v>45657</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E140">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
@@ -4626,100 +4626,100 @@
         </is>
       </c>
       <c s="12" r="G140">
-        <v>45595</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D141">
-        <v>45584</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E141">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F141">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G141">
-        <v>45584</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D142">
-        <v>45664</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E142">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F142">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G142">
-        <v>45582</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D143">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E143">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F143">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G143">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="0">
@@ -4730,19 +4730,19 @@
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D144">
         <v>45611</v>
       </c>
       <c s="11" r="E144">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
@@ -4761,7 +4761,7 @@
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
@@ -4773,7 +4773,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E145">
-        <v>124</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
@@ -4804,7 +4804,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E146">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
@@ -4818,28 +4818,28 @@
     <row r="147" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D147">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E147">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G147">
@@ -4849,24 +4849,24 @@
     <row r="148" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D148">
-        <v>45621</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E148">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F148">
         <is>
@@ -4874,38 +4874,38 @@
         </is>
       </c>
       <c s="12" r="G148">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D149">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E149">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F149">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G149">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="0">
@@ -4916,23 +4916,23 @@
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D150">
         <v>45544</v>
       </c>
       <c s="11" r="E150">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F150">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G150">
@@ -4942,55 +4942,55 @@
     <row r="151" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D151">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E151">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F151">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G151">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C152">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D152">
-        <v>45654</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E152">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F152">
         <is>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c s="12" r="G152">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="0">
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c s="10" r="D153">
-        <v>45612</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E153">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
@@ -5049,14 +5049,14 @@
         </is>
       </c>
       <c s="10" r="D154">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E154">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F154">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G154">
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c s="10" r="D155">
-        <v>45569</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
@@ -5111,14 +5111,14 @@
         </is>
       </c>
       <c s="10" r="D156">
-        <v>45555</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E156">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G156">
@@ -5128,24 +5128,24 @@
     <row r="157" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C157">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D157">
-        <v>45653</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E157">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c s="12" r="G157">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="0">
@@ -5173,14 +5173,14 @@
         </is>
       </c>
       <c s="10" r="D158">
-        <v>45505</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E158">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G158">
@@ -5190,24 +5190,24 @@
     <row r="159" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D159">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E159">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F159">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c s="12" r="G159">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B160">
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c s="10" r="D160">
-        <v>45513</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E160">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F160">
         <is>
@@ -5246,18 +5246,18 @@
         </is>
       </c>
       <c s="12" r="G160">
-        <v>45450</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C161">
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c s="10" r="D161">
-        <v>45504</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E161">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F161">
         <is>
@@ -5277,30 +5277,30 @@
         </is>
       </c>
       <c s="12" r="G161">
-        <v>45441</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C162">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D162">
-        <v>46229</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E162">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c s="12" r="G162">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="0">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c s="10" r="D163">
-        <v>45688</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E163">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c s="10" r="D164">
-        <v>45506</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E164">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
@@ -5376,32 +5376,32 @@
     <row r="165" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C165">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D165">
-        <v>45483</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E165">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G165">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="0">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c s="10" r="D166">
-        <v>45401</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E166">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c s="10" r="D167">
-        <v>45366</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
@@ -5469,43 +5469,43 @@
     <row r="168" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C168">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D168">
-        <v>45473</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E168">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G168">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C169">
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c s="10" r="D169">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E169">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
@@ -5525,111 +5525,111 @@
         </is>
       </c>
       <c s="12" r="G169">
-        <v>45404</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C170">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D170">
         <v>45471</v>
       </c>
       <c s="11" r="E170">
-        <v>740</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G170">
-        <v>45401</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C171">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D171">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E171">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G171">
-        <v>45384</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C172">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D172">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E172">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G172">
-        <v>45380</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C173">
@@ -5638,134 +5638,134 @@
         </is>
       </c>
       <c s="10" r="D173">
-        <v>45439</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E173">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G173">
-        <v>45379</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C174">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D174">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E174">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G174">
-        <v>45372</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C175">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45433</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E175">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G175">
-        <v>45373</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C176">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E176">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G176">
-        <v>45358</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C177">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D177">
-        <v>45352</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E177">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
@@ -5773,18 +5773,18 @@
         </is>
       </c>
       <c s="12" r="G177">
-        <v>45345</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C178">
@@ -5793,41 +5793,41 @@
         </is>
       </c>
       <c s="10" r="D178">
-        <v>45401</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E178">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G178">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C179">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D179">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E179">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c s="12" r="G179">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="0">
@@ -5846,7 +5846,7 @@
       </c>
       <c s="9" t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C180">
@@ -5858,7 +5858,7 @@
         <v>45337</v>
       </c>
       <c s="11" r="E180">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
@@ -5872,24 +5872,24 @@
     <row r="181" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C181">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D181">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E181">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
@@ -5897,34 +5897,34 @@
         </is>
       </c>
       <c s="12" r="G181">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C182">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D182">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E182">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G182">
@@ -5939,19 +5939,19 @@
       </c>
       <c s="9" t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C183">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D183">
         <v>45382</v>
       </c>
       <c s="11" r="E183">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
@@ -5970,19 +5970,19 @@
       </c>
       <c s="9" t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C184">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D184">
         <v>45382</v>
       </c>
       <c s="11" r="E184">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
@@ -6001,7 +6001,7 @@
       </c>
       <c s="9" t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C185">
@@ -6013,7 +6013,7 @@
         <v>45382</v>
       </c>
       <c s="11" r="E185">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F185">
         <is>
@@ -6032,12 +6032,12 @@
       </c>
       <c s="9" t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C186">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D186">
@@ -6058,32 +6058,32 @@
     <row r="187" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C187">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D187">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E187">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F187">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G187">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="0">
@@ -6094,23 +6094,23 @@
       </c>
       <c s="9" t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C188">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D188">
         <v>45366</v>
       </c>
       <c s="11" r="E188">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G188">
@@ -6120,55 +6120,55 @@
     <row r="189" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D189">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E189">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G189">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C190">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D190">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E190">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c s="12" r="G190">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="0">
@@ -6187,19 +6187,19 @@
       </c>
       <c s="9" t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C191">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D191">
         <v>45275</v>
       </c>
       <c s="11" r="E191">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
@@ -6218,19 +6218,19 @@
       </c>
       <c s="9" t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C192">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D192">
         <v>45275</v>
       </c>
       <c s="11" r="E192">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
@@ -6249,19 +6249,19 @@
       </c>
       <c s="9" t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C193">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D193">
         <v>45275</v>
       </c>
       <c s="11" r="E193">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
@@ -6275,24 +6275,24 @@
     <row r="194" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C194">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D194">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E194">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
@@ -6300,30 +6300,30 @@
         </is>
       </c>
       <c s="12" r="G194">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C195">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D195">
-        <v>45294</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E195">
-        <v>136</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F195">
         <is>
@@ -6331,30 +6331,30 @@
         </is>
       </c>
       <c s="12" r="G195">
-        <v>45217</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C196">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D196">
-        <v>45473</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E196">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F196">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c s="12" r="G196">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="0">
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c s="10" r="D197">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E197">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c s="10" r="D198">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E198">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
@@ -6430,24 +6430,24 @@
     <row r="199" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C199">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D199">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E199">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
@@ -6455,18 +6455,18 @@
         </is>
       </c>
       <c s="12" r="G199">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
@@ -6478,7 +6478,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E200">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
@@ -6492,12 +6492,12 @@
     <row r="201" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
@@ -6509,7 +6509,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E201">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
@@ -6523,24 +6523,24 @@
     <row r="202" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D202">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E202">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F202">
         <is>
@@ -6548,61 +6548,61 @@
         </is>
       </c>
       <c s="12" r="G202">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D203">
-        <v>45237</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E203">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F203">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G203">
-        <v>45176</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D204">
-        <v>45387</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E204">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F204">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c s="12" r="G204">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="0">
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c s="10" r="D205">
-        <v>45317</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E205">
         <v>2</v>
@@ -6661,14 +6661,14 @@
         </is>
       </c>
       <c s="10" r="D206">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E206">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F206">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G206">
@@ -6683,7 +6683,7 @@
       </c>
       <c s="9" t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C207">
@@ -6695,11 +6695,11 @@
         <v>45303</v>
       </c>
       <c s="11" r="E207">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F207">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G207">
@@ -6714,7 +6714,7 @@
       </c>
       <c s="9" t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C208">
@@ -6723,7 +6723,7 @@
         </is>
       </c>
       <c s="10" r="D208">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E208">
         <v>3</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
@@ -6757,7 +6757,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E209">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F209">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c s="9" t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C210">
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c s="10" r="D210">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E210">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F210">
         <is>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c s="10" r="D211">
-        <v>45247</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E211">
         <v>1</v>
@@ -6838,7 +6838,7 @@
       </c>
       <c s="9" t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C212">
@@ -6847,14 +6847,14 @@
         </is>
       </c>
       <c s="10" r="D212">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E212">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F212">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G212">
@@ -6869,7 +6869,7 @@
       </c>
       <c s="9" t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C213">
@@ -6881,7 +6881,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E213">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F213">
         <is>
@@ -6895,86 +6895,86 @@
     <row r="214" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C214">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D214">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E214">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F214">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G214">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C215">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D215">
-        <v>45199</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E215">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F215">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G215">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C216">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D216">
-        <v>45213</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E216">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
@@ -6988,24 +6988,24 @@
     <row r="217" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C217">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D217">
-        <v>45283</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E217">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c s="12" r="G217">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="0">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c s="10" r="D218">
-        <v>45192</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E218">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7050,24 +7050,24 @@
     <row r="219" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C219">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D219">
-        <v>45137</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E219">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c s="12" r="G219">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="0">
@@ -7086,19 +7086,19 @@
       </c>
       <c s="9" t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C220">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D220">
-        <v>45107</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E220">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F220">
         <is>
@@ -7112,32 +7112,32 @@
     <row r="221" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C221">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D221">
-        <v>45233</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E221">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F221">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G221">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="0">
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c s="10" r="D222">
-        <v>45205</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E222">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F222">
         <is>
@@ -7174,24 +7174,24 @@
     <row r="223" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C223">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D223">
-        <v>45175</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E223">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F223">
         <is>
@@ -7199,30 +7199,30 @@
         </is>
       </c>
       <c s="12" r="G223">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C224">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D224">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E224">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
@@ -7230,123 +7230,123 @@
         </is>
       </c>
       <c s="12" r="G224">
-        <v>45091</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C225">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D225">
-        <v>45128</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E225">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G225">
-        <v>45090</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C226">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D226">
-        <v>45170</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E226">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G226">
-        <v>45085</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C227">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D227">
-        <v>45106</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E227">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G227">
-        <v>45083</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C228">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D228">
-        <v>45107</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E228">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F228">
         <is>
@@ -7354,30 +7354,30 @@
         </is>
       </c>
       <c s="12" r="G228">
-        <v>45070</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C229">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D229">
-        <v>45115</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E229">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F229">
         <is>
@@ -7385,61 +7385,61 @@
         </is>
       </c>
       <c s="12" r="G229">
-        <v>45055</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D230">
-        <v>45105</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E230">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G230">
-        <v>45044</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D231">
-        <v>45135</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E231">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
@@ -7447,30 +7447,30 @@
         </is>
       </c>
       <c s="12" r="G231">
-        <v>45041</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C232">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D232">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E232">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F232">
         <is>
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c s="12" r="G232">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="0">
@@ -7489,12 +7489,12 @@
       </c>
       <c s="9" t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D233">
@@ -7520,12 +7520,12 @@
       </c>
       <c s="9" t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C234">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D234">
@@ -7551,12 +7551,12 @@
       </c>
       <c s="9" t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C235">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D235">
@@ -7582,12 +7582,12 @@
       </c>
       <c s="9" t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C236">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D236">
@@ -7608,86 +7608,86 @@
     <row r="237" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D237">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E237">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F237">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G237">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C238">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E238">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F238">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G238">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45058</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E239">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F239">
         <is>
@@ -7701,24 +7701,24 @@
     <row r="240" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D240">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E240">
-        <v>379</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
@@ -7726,30 +7726,30 @@
         </is>
       </c>
       <c s="12" r="G240">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D241">
         <v>45079</v>
       </c>
       <c s="11" r="E241">
-        <v>201</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
@@ -7763,12 +7763,12 @@
     <row r="242" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
@@ -7777,103 +7777,103 @@
         </is>
       </c>
       <c s="10" r="D242">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E242">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F242">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G242">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D243">
-        <v>44939</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E243">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F243">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G243">
-        <v>44937</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D244">
-        <v>44890</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E244">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F244">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G244">
-        <v>44827</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C245">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D245">
-        <v>44907</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E245">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F245">
         <is>
@@ -7881,30 +7881,30 @@
         </is>
       </c>
       <c s="12" r="G245">
-        <v>44846</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C246">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D246">
-        <v>44911</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E246">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F246">
         <is>
@@ -7912,80 +7912,80 @@
         </is>
       </c>
       <c s="12" r="G246">
-        <v>44845</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>44869</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E247">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G247">
-        <v>44812</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D248">
-        <v>44866</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E248">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G248">
-        <v>44803</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C249">
@@ -7994,41 +7994,41 @@
         </is>
       </c>
       <c s="10" r="D249">
-        <v>44856</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E249">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F249">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G249">
-        <v>44795</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C250">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D250">
-        <v>44815</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E250">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F250">
         <is>
@@ -8036,30 +8036,30 @@
         </is>
       </c>
       <c s="12" r="G250">
-        <v>44755</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D251">
-        <v>44802</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E251">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F251">
         <is>
@@ -8067,30 +8067,30 @@
         </is>
       </c>
       <c s="12" r="G251">
-        <v>44741</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C252">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D252">
-        <v>44865</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E252">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F252">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c s="12" r="G252">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="0">
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c s="10" r="D253">
-        <v>44805</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E253">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F253">
         <is>
@@ -8135,74 +8135,74 @@
     <row r="254" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C254">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D254">
-        <v>44712</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E254">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F254">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G254">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D255">
-        <v>44600</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E255">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F255">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G255">
-        <v>44600</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
@@ -8211,10 +8211,10 @@
         </is>
       </c>
       <c s="10" r="D256">
-        <v>44652</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E256">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
@@ -8222,30 +8222,30 @@
         </is>
       </c>
       <c s="12" r="G256">
-        <v>44578</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C257">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D257">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E257">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c s="12" r="G257">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="0">
@@ -8276,7 +8276,7 @@
         <v>44620</v>
       </c>
       <c s="11" r="E258">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
@@ -8290,24 +8290,24 @@
     <row r="259" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C259">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D259">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E259">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
@@ -8315,30 +8315,30 @@
         </is>
       </c>
       <c s="12" r="G259">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D260">
-        <v>44531</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E260">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F260">
         <is>
@@ -8346,30 +8346,30 @@
         </is>
       </c>
       <c s="12" r="G260">
-        <v>44470</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C261">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D261">
-        <v>44799</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E261">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F261">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c s="12" r="G261">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="0">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c s="10" r="D262">
-        <v>44743</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E262">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F262">
         <is>
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c s="10" r="D263">
-        <v>44680</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E263">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F263">
         <is>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c s="10" r="D264">
-        <v>44652</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E264">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F264">
         <is>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c s="10" r="D265">
-        <v>44575</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E265">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c s="10" r="D266">
-        <v>44512</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E266">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
@@ -8538,12 +8538,12 @@
     <row r="267" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C267">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c s="10" r="D267">
-        <v>44469</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E267">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
@@ -8563,30 +8563,30 @@
         </is>
       </c>
       <c s="12" r="G267">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C268">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D268">
-        <v>44482</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E268">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8594,30 +8594,30 @@
         </is>
       </c>
       <c s="12" r="G268">
-        <v>44421</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C269">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D269">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E269">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c s="12" r="G269">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="0">
@@ -8636,7 +8636,7 @@
       </c>
       <c s="9" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C270">
@@ -8648,7 +8648,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E270">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
@@ -8667,19 +8667,19 @@
       </c>
       <c s="9" t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C271">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D271">
         <v>44469</v>
       </c>
       <c s="11" r="E271">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
@@ -8693,24 +8693,24 @@
     <row r="272" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C272">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D272">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E272">
-        <v>402</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
@@ -8718,30 +8718,30 @@
         </is>
       </c>
       <c s="12" r="G272">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C273">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E273">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
@@ -8749,18 +8749,18 @@
         </is>
       </c>
       <c s="12" r="G273">
-        <v>44383</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C274">
@@ -8769,10 +8769,10 @@
         </is>
       </c>
       <c s="10" r="D274">
-        <v>44348</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E274">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
@@ -8780,18 +8780,18 @@
         </is>
       </c>
       <c s="12" r="G274">
-        <v>44308</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C275">
@@ -8800,49 +8800,49 @@
         </is>
       </c>
       <c s="10" r="D275">
-        <v>44347</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E275">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G275">
-        <v>44291</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C276">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D276">
-        <v>44311</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E276">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G276">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="0">
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44256</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E277">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
@@ -8879,32 +8879,32 @@
     <row r="278" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C278">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44358</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E278">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G278">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="0">
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c s="10" r="D279">
-        <v>44330</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E279">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c s="10" r="D280">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E280">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8986,10 +8986,10 @@
         </is>
       </c>
       <c s="10" r="D281">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E281">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
@@ -9003,12 +9003,12 @@
     <row r="282" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C282">
@@ -9020,7 +9020,7 @@
         <v>44288</v>
       </c>
       <c s="11" r="E282">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
@@ -9034,24 +9034,24 @@
     <row r="283" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C283">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D283">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E283">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c s="12" r="G283">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="0">
@@ -9079,10 +9079,10 @@
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44264</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E284">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
@@ -9096,24 +9096,24 @@
     <row r="285" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C285">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D285">
-        <v>44242</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E285">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
@@ -9121,100 +9121,100 @@
         </is>
       </c>
       <c s="12" r="G285">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C286">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D286">
-        <v>44270</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E286">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G286">
-        <v>44168</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C287">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D287">
-        <v>44214</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E287">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G287">
-        <v>44160</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C288">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D288">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E288">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G288">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="0">
@@ -9237,11 +9237,11 @@
         <v>44211</v>
       </c>
       <c s="11" r="E289">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G289">
@@ -9251,12 +9251,12 @@
     <row r="290" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C290">
@@ -9265,29 +9265,29 @@
         </is>
       </c>
       <c s="10" r="D290">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E290">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G290">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C291">
@@ -9296,69 +9296,69 @@
         </is>
       </c>
       <c s="10" r="D291">
-        <v>44214</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E291">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G291">
-        <v>44151</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C292">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D292">
-        <v>44186</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E292">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F292">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G292">
-        <v>44127</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C293">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44104</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E293">
         <v>59</v>
@@ -9369,100 +9369,100 @@
         </is>
       </c>
       <c s="12" r="G293">
-        <v>44104</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C294">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D294">
-        <v>44197</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E294">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F294">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G294">
-        <v>44151</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">7241</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">SP+</t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C295">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Elgin</t>
         </is>
       </c>
       <c s="10" r="D295">
-        <v>43914</v>
+        <v>44197</v>
       </c>
       <c s="11" r="E295">
-        <v>89</v>
+        <v>229</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G295">
-        <v>44099</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">7218</t>
+          <t xml:space="preserve">7241</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
+          <t xml:space="preserve">SP+</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C296">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D296">
-        <v>43903</v>
+        <v>43914</v>
       </c>
       <c s="11" r="E296">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G296">
-        <v>44091</v>
+        <v>44099</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="0">
@@ -9473,19 +9473,19 @@
       </c>
       <c s="9" t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
+          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C297">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D297">
         <v>43903</v>
       </c>
       <c s="11" r="E297">
-        <v>358</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
@@ -9504,19 +9504,19 @@
       </c>
       <c s="9" t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">Sodexo - Medford SD</t>
+          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C298">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D298">
         <v>43903</v>
       </c>
       <c s="11" r="E298">
-        <v>111</v>
+        <v>358</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
@@ -9530,32 +9530,32 @@
     <row r="299" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">7217</t>
+          <t xml:space="preserve">7218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">PF Chang's</t>
+          <t xml:space="preserve">Sodexo - Medford SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C299">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D299">
-        <v>44092</v>
+        <v>43903</v>
       </c>
       <c s="11" r="E299">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F299">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G299">
-        <v>44092</v>
+        <v>44091</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="0">
@@ -9566,12 +9566,12 @@
       </c>
       <c s="9" t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">PF Chang's - Eugene</t>
+          <t xml:space="preserve">PF Chang's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C300">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D300">
@@ -9592,32 +9592,32 @@
     <row r="301" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">7215</t>
+          <t xml:space="preserve">7217</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Salem</t>
+          <t xml:space="preserve">PF Chang's - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C301">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D301">
-        <v>44137</v>
+        <v>44092</v>
       </c>
       <c s="11" r="E301">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F301">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G301">
-        <v>44077</v>
+        <v>44092</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="0">
@@ -9628,19 +9628,19 @@
       </c>
       <c s="9" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Portland</t>
+          <t xml:space="preserve">LAGS Medical Center - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C302">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D302">
         <v>44137</v>
       </c>
       <c s="11" r="E302">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F302">
         <is>
@@ -9654,12 +9654,12 @@
     <row r="303" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">7211</t>
+          <t xml:space="preserve">7215</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">Bon Appetit</t>
+          <t xml:space="preserve">LAGS Medical Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C303">
@@ -9668,18 +9668,18 @@
         </is>
       </c>
       <c s="10" r="D303">
-        <v>44104</v>
+        <v>44137</v>
       </c>
       <c s="11" r="E303">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F303">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G303">
-        <v>44075</v>
+        <v>44077</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="0">
@@ -9702,11 +9702,11 @@
         <v>44104</v>
       </c>
       <c s="11" r="E304">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G304">
@@ -9716,24 +9716,24 @@
     <row r="305" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">7209</t>
+          <t xml:space="preserve">7211</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">Dave &amp; Buster's</t>
+          <t xml:space="preserve">Bon Appetit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C305">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D305">
-        <v>44143</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E305">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
@@ -9741,123 +9741,123 @@
         </is>
       </c>
       <c s="12" r="G305">
-        <v>44082</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">7207</t>
+          <t xml:space="preserve">7209</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">PGE - Boardman</t>
+          <t xml:space="preserve">Dave &amp; Buster's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C306">
         <is>
-          <t xml:space="preserve">Boardman</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D306">
-        <v>44140</v>
+        <v>44143</v>
       </c>
       <c s="11" r="E306">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c s="9" t="inlineStr" r="F306">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G306">
-        <v>44075</v>
+        <v>44082</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">7199</t>
+          <t xml:space="preserve">7207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">LAIKA</t>
+          <t xml:space="preserve">PGE - Boardman</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C307">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Boardman</t>
         </is>
       </c>
       <c s="10" r="D307">
+        <v>44140</v>
+      </c>
+      <c s="11" r="E307">
+        <v>22</v>
+      </c>
+      <c s="9" t="inlineStr" r="F307">
+        <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G307">
         <v>44075</v>
-      </c>
-      <c s="11" r="E307">
-        <v>50</v>
-      </c>
-      <c s="9" t="inlineStr" r="F307">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G307">
-        <v>44057</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">7192</t>
+          <t xml:space="preserve">7199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">HMSHost</t>
+          <t xml:space="preserve">LAIKA</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C308">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D308">
-        <v>44119</v>
+        <v>44075</v>
       </c>
       <c s="11" r="E308">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F308">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G308">
-        <v>44054</v>
+        <v>44057</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">7186</t>
+          <t xml:space="preserve">7192</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">HMSHost</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C309">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D309">
-        <v>44124</v>
+        <v>44119</v>
       </c>
       <c s="11" r="E309">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F309">
         <is>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c s="12" r="G309">
-        <v>44032</v>
+        <v>44054</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="0">
@@ -9876,19 +9876,19 @@
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D310">
-        <v>44099</v>
+        <v>44124</v>
       </c>
       <c s="11" r="E310">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F310">
         <is>
@@ -9907,19 +9907,19 @@
       </c>
       <c s="9" t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C311">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D311">
         <v>44099</v>
       </c>
       <c s="11" r="E311">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F311">
         <is>
@@ -9933,24 +9933,24 @@
     <row r="312" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">7185</t>
+          <t xml:space="preserve">7186</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C312">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D312">
-        <v>44105</v>
+        <v>44099</v>
       </c>
       <c s="11" r="E312">
-        <v>277</v>
+        <v>355</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
@@ -9958,18 +9958,18 @@
         </is>
       </c>
       <c s="12" r="G312">
-        <v>44041</v>
+        <v>44032</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">7184</t>
+          <t xml:space="preserve">7185</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
+          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
@@ -9978,29 +9978,29 @@
         </is>
       </c>
       <c s="10" r="D313">
-        <v>43910</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E313">
-        <v>70</v>
+        <v>277</v>
       </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G313">
-        <v>44043</v>
+        <v>44041</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">7171</t>
+          <t xml:space="preserve">7184</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
+          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c s="10" r="D314">
-        <v>44105</v>
+        <v>43910</v>
       </c>
       <c s="11" r="E314">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F314">
         <is>
@@ -10026,32 +10026,32 @@
     <row r="315" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">7162</t>
+          <t xml:space="preserve">7171</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">Nike - Childcare  </t>
+          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D315">
         <v>44105</v>
       </c>
       <c s="11" r="E315">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c s="9" t="inlineStr" r="F315">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G315">
-        <v>44035</v>
+        <v>44043</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="0">
@@ -10062,7 +10062,7 @@
       </c>
       <c s="9" t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">Nike</t>
+          <t xml:space="preserve">Nike - Childcare  </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C316">
@@ -10074,7 +10074,7 @@
         <v>44105</v>
       </c>
       <c s="11" r="E316">
-        <v>308</v>
+        <v>192</v>
       </c>
       <c s="9" t="inlineStr" r="F316">
         <is>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c s="10" r="D317">
-        <v>44035</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E317">
-        <v>700</v>
+        <v>308</v>
       </c>
       <c s="9" t="inlineStr" r="F317">
         <is>
@@ -10119,59 +10119,59 @@
     <row r="318" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">7151</t>
+          <t xml:space="preserve">7162</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">American Queen Steamboat Company </t>
+          <t xml:space="preserve">Nike</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C318">
         <is>
-          <t xml:space="preserve">New Albany, IN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D318">
-        <v>44098</v>
+        <v>44035</v>
       </c>
       <c s="11" r="E318">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c s="9" t="inlineStr" r="F318">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G318">
-        <v>44034</v>
+        <v>44035</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">7135</t>
+          <t xml:space="preserve">7151</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">Vesta </t>
+          <t xml:space="preserve">American Queen Steamboat Company </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C319">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">New Albany, IN</t>
         </is>
       </c>
       <c s="10" r="D319">
-        <v>44034</v>
+        <v>44098</v>
       </c>
       <c s="11" r="E319">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c s="9" t="inlineStr" r="F319">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G319">
@@ -10181,24 +10181,24 @@
     <row r="320" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">7134</t>
+          <t xml:space="preserve">7135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">Pioneer Pacific College</t>
+          <t xml:space="preserve">Vesta </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C320">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D320">
-        <v>44043</v>
+        <v>44034</v>
       </c>
       <c s="11" r="E320">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F320">
         <is>
@@ -10206,7 +10206,7 @@
         </is>
       </c>
       <c s="12" r="G320">
-        <v>44033</v>
+        <v>44034</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="0">
@@ -10217,19 +10217,19 @@
       </c>
       <c s="9" t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">Pioneer Pacific College - Beaverton</t>
+          <t xml:space="preserve">Pioneer Pacific College</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C321">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D321">
         <v>44043</v>
       </c>
       <c s="11" r="E321">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F321">
         <is>
@@ -10248,19 +10248,19 @@
       </c>
       <c s="9" t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">Pioneer Pacific College - Springfield</t>
+          <t xml:space="preserve">Pioneer Pacific College - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C322">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D322">
         <v>44043</v>
       </c>
       <c s="11" r="E322">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F322">
         <is>
@@ -10274,32 +10274,32 @@
     <row r="323" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">7071</t>
+          <t xml:space="preserve">7134</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">United - PDX</t>
+          <t xml:space="preserve">Pioneer Pacific College - Springfield</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C323">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D323">
-        <v>44105</v>
+        <v>44043</v>
       </c>
       <c s="11" r="E323">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F323">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G323">
-        <v>44020</v>
+        <v>44033</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="0">
@@ -10322,7 +10322,7 @@
         <v>44105</v>
       </c>
       <c s="11" r="E324">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c s="9" t="inlineStr" r="F324">
         <is>
@@ -10336,24 +10336,24 @@
     <row r="325" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">7070</t>
+          <t xml:space="preserve">7071</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">arauco - Albany </t>
+          <t xml:space="preserve">United - PDX</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C325">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D325">
-        <v>44018</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E325">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F325">
         <is>
@@ -10361,30 +10361,30 @@
         </is>
       </c>
       <c s="12" r="G325">
-        <v>44018</v>
+        <v>44020</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">7057</t>
+          <t xml:space="preserve">7070</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">Hampton Inn &amp; Suites - Portland</t>
+          <t xml:space="preserve">arauco - Albany </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C326">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D326">
-        <v>44012</v>
+        <v>44018</v>
       </c>
       <c s="11" r="E326">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F326">
         <is>
@@ -10398,12 +10398,12 @@
     <row r="327" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">7056</t>
+          <t xml:space="preserve">7057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">Atrium Hospitality - Portland Embassy S</t>
+          <t xml:space="preserve">Hampton Inn &amp; Suites - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C327">
@@ -10412,29 +10412,29 @@
         </is>
       </c>
       <c s="10" r="D327">
-        <v>43902</v>
+        <v>44012</v>
       </c>
       <c s="11" r="E327">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F327">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G327">
-        <v>43964</v>
+        <v>44018</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">7052</t>
+          <t xml:space="preserve">7056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">Hilton Portland Downtown</t>
+          <t xml:space="preserve">Atrium Hospitality - Portland Embassy S</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C328">
@@ -10443,10 +10443,10 @@
         </is>
       </c>
       <c s="10" r="D328">
-        <v>43912</v>
+        <v>43902</v>
       </c>
       <c s="11" r="E328">
-        <v>330</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F328">
         <is>
@@ -10454,128 +10454,158 @@
         </is>
       </c>
       <c s="12" r="G328">
-        <v>44012</v>
+        <v>43964</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7052</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Hilton Portland Downtown</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C329">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D329"/>
-      <c s="13" t="str" r="E329"/>
+          <t xml:space="preserve">Portland</t>
+        </is>
+      </c>
+      <c s="10" r="D329">
+        <v>43912</v>
+      </c>
+      <c s="11" r="E329">
+        <v>330</v>
+      </c>
       <c s="9" t="inlineStr" r="F329">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G329">
-        <v>44909</v>
+        <v>44012</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C330">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D330"/>
       <c s="13" t="str" r="E330"/>
       <c s="9" t="inlineStr" r="F330">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G330">
-        <v>45125</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A331">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B331">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C331">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">Mesa, AZ</t>
         </is>
       </c>
       <c s="9" t="str" r="D331"/>
       <c s="13" t="str" r="E331"/>
       <c s="9" t="inlineStr" r="F331">
         <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G331">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="332" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A332">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B332">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C332">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D332"/>
+      <c s="13" t="str" r="E332"/>
+      <c s="9" t="inlineStr" r="F332">
+        <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
-      <c s="12" r="G331">
+      <c s="12" r="G332">
         <v>45887</v>
       </c>
     </row>
-    <row r="332" ht="3.55" customHeight="0">
-      <c s="14" t="inlineStr" r="A332">
+    <row r="333" ht="3.6" customHeight="0">
+      <c s="14" t="inlineStr" r="A333">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B332">
+      <c s="14" t="inlineStr" r="B333">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C332">
+      <c s="14" t="inlineStr" r="C333">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D332">
+      <c s="14" t="inlineStr" r="D333">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E332">
+      <c s="14" t="inlineStr" r="E333">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F332">
+      <c s="14" t="inlineStr" r="F333">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G332">
+      <c s="14" t="inlineStr" r="G333">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="333" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:A2"/>
@@ -10585,7 +10615,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/4/2026 7:07:49 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/4/2026 6:49:50 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/4/2016 to 8/4/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/5/2016 to 8/5/2026</t>
         </is>
       </c>
     </row>
@@ -10615,7 +10615,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/4/2026 6:49:50 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/5/2026 7:01:52 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -385,28 +385,28 @@
     <row r="4" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9553</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">Avamere Health Services, LLC</t>
+          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">Tigard</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D4">
-        <v>46266</v>
+        <v>46298</v>
       </c>
       <c s="11" r="E4">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G4">
@@ -416,94 +416,94 @@
     <row r="5" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">9549</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
+          <t xml:space="preserve">Avamere Health Services, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tigard</t>
         </is>
       </c>
       <c s="10" r="D5">
-        <v>46325</v>
+        <v>46266</v>
       </c>
       <c s="11" r="E5">
-        <v>387</v>
+        <v>129</v>
       </c>
       <c s="9" t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G5">
-        <v>46233</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">9534</t>
+          <t xml:space="preserve">9549</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
+          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D6">
-        <v>46262</v>
+        <v>46325</v>
       </c>
       <c s="11" r="E6">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c s="9" t="inlineStr" r="F6">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G6">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">Adventist Health Tillamook</t>
+          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D7">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c s="11" r="E7">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c s="9" t="inlineStr" r="F7">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G7">
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="0">
@@ -514,19 +514,19 @@
       </c>
       <c s="9" t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">Adventist Health Portland</t>
+          <t xml:space="preserve">Adventist Health Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">Portland, </t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D8">
         <v>46206</v>
       </c>
       <c s="11" r="E8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F8">
         <is>
@@ -545,19 +545,19 @@
       </c>
       <c s="9" t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
+          <t xml:space="preserve">Adventist Health Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">The Dalles</t>
+          <t xml:space="preserve">Portland, </t>
         </is>
       </c>
       <c s="10" r="D9">
         <v>46206</v>
       </c>
       <c s="11" r="E9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F9">
         <is>
@@ -571,32 +571,32 @@
     <row r="10" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">PacificSource</t>
+          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">The Dalles</t>
         </is>
       </c>
       <c s="10" r="D10">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E10">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G10">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="0">
@@ -607,23 +607,23 @@
       </c>
       <c s="9" t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">PacificSource - Bend</t>
+          <t xml:space="preserve">PacificSource</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D11">
         <v>46234</v>
       </c>
       <c s="11" r="E11">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G11">
@@ -638,19 +638,19 @@
       </c>
       <c s="9" t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">PacificSource - Portland</t>
+          <t xml:space="preserve">PacificSource - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D12">
         <v>46234</v>
       </c>
       <c s="11" r="E12">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F12">
         <is>
@@ -669,12 +669,12 @@
       </c>
       <c s="9" t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">PacificSource - Salem</t>
+          <t xml:space="preserve">PacificSource - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D13">
@@ -700,19 +700,19 @@
       </c>
       <c s="9" t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">PacificSource Hood River</t>
+          <t xml:space="preserve">PacificSource - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D14">
         <v>46234</v>
       </c>
       <c s="11" r="E14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F14">
         <is>
@@ -726,63 +726,63 @@
     <row r="15" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">9511</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
+          <t xml:space="preserve">PacificSource Hood River</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D15">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E15">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G15">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9511</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D16">
-        <v>46234</v>
+        <v>46228</v>
       </c>
       <c s="11" r="E16">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F16">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G16">
-        <v>46160</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="0">
@@ -793,19 +793,19 @@
       </c>
       <c s="9" t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C17">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D17">
         <v>46234</v>
       </c>
       <c s="11" r="E17">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F17">
         <is>
@@ -824,19 +824,19 @@
       </c>
       <c s="9" t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D18">
         <v>46234</v>
       </c>
       <c s="11" r="E18">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F18">
         <is>
@@ -855,19 +855,19 @@
       </c>
       <c s="9" t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D19">
         <v>46234</v>
       </c>
       <c s="11" r="E19">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F19">
         <is>
@@ -886,19 +886,19 @@
       </c>
       <c s="9" t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D20">
         <v>46234</v>
       </c>
       <c s="11" r="E20">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c s="9" t="inlineStr" r="F20">
         <is>
@@ -912,86 +912,86 @@
     <row r="21" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D21">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E21">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G21">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D22">
-        <v>46201</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E22">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G22">
-        <v>46141</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D23">
-        <v>46295</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E23">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F23">
         <is>
@@ -999,49 +999,49 @@
         </is>
       </c>
       <c s="12" r="G23">
-        <v>46114</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D24">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E24">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G24">
-        <v>46108</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C25">
@@ -1050,18 +1050,18 @@
         </is>
       </c>
       <c s="10" r="D25">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E25">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G25">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="0">
@@ -1072,7 +1072,7 @@
       </c>
       <c s="9" t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C26">
@@ -1098,24 +1098,24 @@
     <row r="27" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D27">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E27">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F27">
         <is>
@@ -1123,38 +1123,38 @@
         </is>
       </c>
       <c s="12" r="G27">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D28">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E28">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F28">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G28">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="0">
@@ -1165,19 +1165,19 @@
       </c>
       <c s="9" t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D29">
         <v>46131</v>
       </c>
       <c s="11" r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F29">
         <is>
@@ -1191,63 +1191,63 @@
     <row r="30" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D30">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E30">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G30">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D31">
         <v>46117</v>
       </c>
       <c s="11" r="E31">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G31">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="0">
@@ -1258,19 +1258,19 @@
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D32">
         <v>46117</v>
       </c>
       <c s="11" r="E32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F32">
         <is>
@@ -1289,12 +1289,12 @@
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D33">
@@ -1320,12 +1320,12 @@
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D34">
@@ -1351,12 +1351,12 @@
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D35">
@@ -1382,12 +1382,12 @@
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D36">
@@ -1413,12 +1413,12 @@
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D37">
@@ -1444,12 +1444,12 @@
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D38">
@@ -1475,7 +1475,7 @@
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
@@ -1506,7 +1506,7 @@
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
@@ -1537,12 +1537,12 @@
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D41">
@@ -1568,12 +1568,12 @@
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D42">
@@ -1599,12 +1599,12 @@
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D43">
@@ -1630,7 +1630,7 @@
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
@@ -1661,19 +1661,19 @@
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D45">
         <v>46117</v>
       </c>
       <c s="11" r="E45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F45">
         <is>
@@ -1692,19 +1692,19 @@
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D46">
         <v>46117</v>
       </c>
       <c s="11" r="E46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F46">
         <is>
@@ -1723,19 +1723,19 @@
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D47">
         <v>46117</v>
       </c>
       <c s="11" r="E47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F47">
         <is>
@@ -1754,12 +1754,12 @@
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D48">
@@ -1785,12 +1785,12 @@
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D49">
@@ -1811,24 +1811,24 @@
     <row r="50" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D50">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E50">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F50">
         <is>
@@ -1847,19 +1847,19 @@
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D51">
         <v>46112</v>
       </c>
       <c s="11" r="E51">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F51">
         <is>
@@ -1878,19 +1878,19 @@
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D52">
         <v>46112</v>
       </c>
       <c s="11" r="E52">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F52">
         <is>
@@ -1904,24 +1904,24 @@
     <row r="53" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D53">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E53">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F53">
         <is>
@@ -1929,30 +1929,30 @@
         </is>
       </c>
       <c s="12" r="G53">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D54">
-        <v>46142</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E54">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F54">
         <is>
@@ -1960,30 +1960,30 @@
         </is>
       </c>
       <c s="12" r="G54">
-        <v>46020</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D55">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E55">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F55">
         <is>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c s="12" r="G55">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="0">
@@ -2002,7 +2002,7 @@
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
@@ -2014,7 +2014,7 @@
         <v>46014</v>
       </c>
       <c s="11" r="E56">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F56">
         <is>
@@ -2033,19 +2033,19 @@
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D57">
         <v>46014</v>
       </c>
       <c s="11" r="E57">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F57">
         <is>
@@ -2059,43 +2059,43 @@
     <row r="58" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D58">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E58">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F58">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G58">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
@@ -2104,29 +2104,29 @@
         </is>
       </c>
       <c s="10" r="D59">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E59">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F59">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G59">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c s="10" r="D60">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E60">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F60">
         <is>
@@ -2152,63 +2152,63 @@
     <row r="61" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D61">
         <v>46054</v>
       </c>
       <c s="11" r="E61">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F61">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G61">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D62">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E62">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F62">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G62">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="0">
@@ -2219,19 +2219,19 @@
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D63">
         <v>45916</v>
       </c>
       <c s="11" r="E63">
-        <v>510</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F63">
         <is>
@@ -2250,7 +2250,7 @@
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
@@ -2262,7 +2262,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E64">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F64">
         <is>
@@ -2281,7 +2281,7 @@
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
@@ -2293,7 +2293,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E65">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F65">
         <is>
@@ -2307,24 +2307,24 @@
     <row r="66" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D66">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E66">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F66">
         <is>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c s="12" r="G66">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="0">
@@ -2343,23 +2343,23 @@
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D67">
         <v>46022</v>
       </c>
       <c s="11" r="E67">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F67">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G67">
@@ -2374,19 +2374,19 @@
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D68">
         <v>46022</v>
       </c>
       <c s="11" r="E68">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F68">
         <is>
@@ -2405,19 +2405,19 @@
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D69">
         <v>46022</v>
       </c>
       <c s="11" r="E69">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F69">
         <is>
@@ -2436,19 +2436,19 @@
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D70">
         <v>46022</v>
       </c>
       <c s="11" r="E70">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F70">
         <is>
@@ -2462,55 +2462,55 @@
     <row r="71" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D71">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E71">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F71">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G71">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C72">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D72">
         <v>46017</v>
       </c>
       <c s="11" r="E72">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
@@ -2524,28 +2524,28 @@
     <row r="73" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C73">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D73">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E73">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G73">
@@ -2569,14 +2569,14 @@
         </is>
       </c>
       <c s="10" r="D74">
-        <v>46017</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E74">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F74">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G74">
@@ -2586,86 +2586,86 @@
     <row r="75" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D75">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E75">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F75">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G75">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D76">
-        <v>46022</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E76">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F76">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G76">
-        <v>45917</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D77">
-        <v>45978</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E77">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
@@ -2673,18 +2673,18 @@
         </is>
       </c>
       <c s="12" r="G77">
-        <v>45943</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C78">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c s="10" r="D78">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E78">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
@@ -2704,38 +2704,38 @@
         </is>
       </c>
       <c s="12" r="G78">
-        <v>45930</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C79">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D79">
-        <v>45940</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E79">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G79">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="0">
@@ -2755,14 +2755,14 @@
         </is>
       </c>
       <c s="10" r="D80">
-        <v>45925</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E80">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G80">
@@ -2772,24 +2772,24 @@
     <row r="81" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D81">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E81">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
@@ -2797,34 +2797,34 @@
         </is>
       </c>
       <c s="12" r="G81">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C82">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D82">
         <v>45976</v>
       </c>
       <c s="11" r="E82">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G82">
@@ -2834,63 +2834,63 @@
     <row r="83" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C83">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D83">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E83">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G83">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D84">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E84">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G84">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="0">
@@ -2901,7 +2901,7 @@
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
@@ -2913,7 +2913,7 @@
         <v>45949</v>
       </c>
       <c s="11" r="E85">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
@@ -2927,12 +2927,12 @@
     <row r="86" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
@@ -2941,41 +2941,41 @@
         </is>
       </c>
       <c s="10" r="D86">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E86">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G86">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D87">
-        <v>45874</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E87">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
@@ -2983,18 +2983,18 @@
         </is>
       </c>
       <c s="12" r="G87">
-        <v>45867</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C88">
@@ -3003,49 +3003,49 @@
         </is>
       </c>
       <c s="10" r="D88">
-        <v>45920</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E88">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G88">
-        <v>45854</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C89">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D89">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E89">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G89">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="0">
@@ -3056,19 +3056,19 @@
       </c>
       <c s="9" t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C90">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D90">
         <v>45912</v>
       </c>
       <c s="11" r="E90">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
@@ -3082,63 +3082,63 @@
     <row r="91" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C91">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D91">
         <v>45912</v>
       </c>
       <c s="11" r="E91">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G91">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D92">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E92">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G92">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="0">
@@ -3149,19 +3149,19 @@
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D93">
         <v>45853</v>
       </c>
       <c s="11" r="E93">
-        <v>1544</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
@@ -3180,7 +3180,7 @@
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
@@ -3192,7 +3192,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E94">
-        <v>174</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
@@ -3211,7 +3211,7 @@
       </c>
       <c s="9" t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C95">
@@ -3223,7 +3223,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E95">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
@@ -3237,86 +3237,86 @@
     <row r="96" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D96">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E96">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G96">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C97">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D97">
-        <v>45901</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E97">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G97">
-        <v>45839</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D98">
-        <v>45982</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E98">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c s="12" r="G98">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="0">
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c s="10" r="D99">
-        <v>45968</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E99">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c s="10" r="D100">
-        <v>45894</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E100">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
@@ -3392,24 +3392,24 @@
     <row r="101" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C101">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D101">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E101">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
@@ -3417,30 +3417,30 @@
         </is>
       </c>
       <c s="12" r="G101">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D102">
         <v>45838</v>
       </c>
       <c s="11" r="E102">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
@@ -3454,94 +3454,94 @@
     <row r="103" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D103">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E103">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G103">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D104">
-        <v>45807</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E104">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G104">
-        <v>45804</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D105">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E105">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G105">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="0">
@@ -3552,19 +3552,19 @@
       </c>
       <c s="9" t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D106">
         <v>45866</v>
       </c>
       <c s="11" r="E106">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
@@ -3578,55 +3578,55 @@
     <row r="107" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D107">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E107">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G107">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D108">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E108">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
@@ -3634,85 +3634,85 @@
         </is>
       </c>
       <c s="12" r="G108">
-        <v>45778</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D109">
-        <v>45769</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E109">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G109">
-        <v>45769</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D110">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E110">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G110">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D111">
@@ -3723,69 +3723,69 @@
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G111">
-        <v>45763</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D112">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E112">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G112">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D113">
-        <v>45810</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E113">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G113">
@@ -3795,43 +3795,43 @@
     <row r="114" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C114">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D114">
-        <v>45808</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E114">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G114">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C115">
@@ -3840,103 +3840,103 @@
         </is>
       </c>
       <c s="10" r="D115">
-        <v>45834</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E115">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G115">
-        <v>45774</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D116">
-        <v>45838</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E116">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G116">
-        <v>45744</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D117">
-        <v>45706</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E117">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G117">
-        <v>45706</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D118">
-        <v>45734</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E118">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
@@ -3944,38 +3944,38 @@
         </is>
       </c>
       <c s="12" r="G118">
-        <v>45666</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D119">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E119">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G119">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="0">
@@ -3986,19 +3986,19 @@
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D120">
         <v>45707</v>
       </c>
       <c s="11" r="E120">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
@@ -4012,63 +4012,63 @@
     <row r="121" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D121">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E121">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G121">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D122">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E122">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G122">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="0">
@@ -4079,19 +4079,19 @@
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D123">
         <v>45696</v>
       </c>
       <c s="11" r="E123">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
@@ -4105,86 +4105,86 @@
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D124">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E124">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G124">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D125">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E125">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G125">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C126">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D126">
         <v>45931</v>
       </c>
       <c s="11" r="E126">
-        <v>221</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
@@ -4198,43 +4198,43 @@
     <row r="127" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D127">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E127">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G127">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
@@ -4243,18 +4243,18 @@
         </is>
       </c>
       <c s="10" r="D128">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E128">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G128">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="0">
@@ -4265,19 +4265,19 @@
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D129">
         <v>45726</v>
       </c>
       <c s="11" r="E129">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
@@ -4296,19 +4296,19 @@
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D130">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E130">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
@@ -4327,19 +4327,19 @@
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D131">
         <v>45725</v>
       </c>
       <c s="11" r="E131">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F131">
         <is>
@@ -4358,19 +4358,19 @@
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D132">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E132">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F132">
         <is>
@@ -4389,12 +4389,12 @@
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D133">
@@ -4420,12 +4420,12 @@
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D134">
@@ -4451,7 +4451,7 @@
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c s="10" r="D135">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E135">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
@@ -4482,19 +4482,19 @@
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D136">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E136">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
@@ -4513,7 +4513,7 @@
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c s="10" r="D137">
-        <v>45703</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E137">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
@@ -4544,19 +4544,19 @@
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D138">
-        <v>45690</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E138">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
@@ -4570,12 +4570,12 @@
     <row r="139" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
@@ -4584,72 +4584,72 @@
         </is>
       </c>
       <c s="10" r="D139">
-        <v>45657</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E139">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G139">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D140">
-        <v>45640</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E140">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G140">
-        <v>45580</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D141">
-        <v>45657</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E141">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F141">
         <is>
@@ -4657,100 +4657,100 @@
         </is>
       </c>
       <c s="12" r="G141">
-        <v>45595</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D142">
-        <v>45584</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E142">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F142">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G142">
-        <v>45584</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D143">
-        <v>45664</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E143">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F143">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G143">
-        <v>45582</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D144">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E144">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G144">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="0">
@@ -4761,19 +4761,19 @@
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D145">
         <v>45611</v>
       </c>
       <c s="11" r="E145">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
@@ -4804,7 +4804,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E146">
-        <v>124</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
@@ -4823,7 +4823,7 @@
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
@@ -4835,7 +4835,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E147">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
@@ -4849,28 +4849,28 @@
     <row r="148" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D148">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E148">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F148">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G148">
@@ -4880,24 +4880,24 @@
     <row r="149" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D149">
-        <v>45621</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E149">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F149">
         <is>
@@ -4905,38 +4905,38 @@
         </is>
       </c>
       <c s="12" r="G149">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D150">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E150">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F150">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G150">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="0">
@@ -4947,23 +4947,23 @@
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D151">
         <v>45544</v>
       </c>
       <c s="11" r="E151">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F151">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G151">
@@ -4973,55 +4973,55 @@
     <row r="152" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C152">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D152">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E152">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F152">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G152">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C153">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D153">
-        <v>45654</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E153">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c s="12" r="G153">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="0">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c s="10" r="D154">
-        <v>45612</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E154">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F154">
         <is>
@@ -5080,14 +5080,14 @@
         </is>
       </c>
       <c s="10" r="D155">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E155">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G155">
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c s="10" r="D156">
-        <v>45569</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
@@ -5142,14 +5142,14 @@
         </is>
       </c>
       <c s="10" r="D157">
-        <v>45555</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E157">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G157">
@@ -5159,24 +5159,24 @@
     <row r="158" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D158">
-        <v>45653</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E158">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c s="12" r="G158">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="0">
@@ -5204,14 +5204,14 @@
         </is>
       </c>
       <c s="10" r="D159">
-        <v>45505</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E159">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F159">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G159">
@@ -5221,24 +5221,24 @@
     <row r="160" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C160">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D160">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E160">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F160">
         <is>
@@ -5246,13 +5246,13 @@
         </is>
       </c>
       <c s="12" r="G160">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B161">
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c s="10" r="D161">
-        <v>45513</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E161">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F161">
         <is>
@@ -5277,18 +5277,18 @@
         </is>
       </c>
       <c s="12" r="G161">
-        <v>45450</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C162">
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c s="10" r="D162">
-        <v>45504</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E162">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5308,30 +5308,30 @@
         </is>
       </c>
       <c s="12" r="G162">
-        <v>45441</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C163">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D163">
-        <v>46229</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E163">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c s="12" r="G163">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="0">
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c s="10" r="D164">
-        <v>45688</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E164">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c s="10" r="D165">
-        <v>45506</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E165">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
@@ -5407,32 +5407,32 @@
     <row r="166" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C166">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D166">
-        <v>45483</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E166">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G166">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="0">
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c s="10" r="D167">
-        <v>45401</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E167">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c s="10" r="D168">
-        <v>45366</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
@@ -5500,43 +5500,43 @@
     <row r="169" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C169">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D169">
-        <v>45473</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E169">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G169">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C170">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c s="10" r="D170">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E170">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
@@ -5556,111 +5556,111 @@
         </is>
       </c>
       <c s="12" r="G170">
-        <v>45404</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C171">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D171">
         <v>45471</v>
       </c>
       <c s="11" r="E171">
-        <v>740</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G171">
-        <v>45401</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C172">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D172">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E172">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G172">
-        <v>45384</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C173">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D173">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E173">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G173">
-        <v>45380</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C174">
@@ -5669,134 +5669,134 @@
         </is>
       </c>
       <c s="10" r="D174">
-        <v>45439</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E174">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G174">
-        <v>45379</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C175">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E175">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G175">
-        <v>45372</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C176">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45433</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E176">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G176">
-        <v>45373</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C177">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D177">
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E177">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G177">
-        <v>45358</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C178">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D178">
-        <v>45352</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E178">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
@@ -5804,18 +5804,18 @@
         </is>
       </c>
       <c s="12" r="G178">
-        <v>45345</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C179">
@@ -5824,41 +5824,41 @@
         </is>
       </c>
       <c s="10" r="D179">
-        <v>45401</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E179">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G179">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C180">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D180">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E180">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c s="12" r="G180">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="0">
@@ -5877,7 +5877,7 @@
       </c>
       <c s="9" t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C181">
@@ -5889,7 +5889,7 @@
         <v>45337</v>
       </c>
       <c s="11" r="E181">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
@@ -5903,24 +5903,24 @@
     <row r="182" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C182">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D182">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E182">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
@@ -5928,34 +5928,34 @@
         </is>
       </c>
       <c s="12" r="G182">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C183">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D183">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E183">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G183">
@@ -5970,19 +5970,19 @@
       </c>
       <c s="9" t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C184">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D184">
         <v>45382</v>
       </c>
       <c s="11" r="E184">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
@@ -6001,19 +6001,19 @@
       </c>
       <c s="9" t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C185">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D185">
         <v>45382</v>
       </c>
       <c s="11" r="E185">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F185">
         <is>
@@ -6032,7 +6032,7 @@
       </c>
       <c s="9" t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C186">
@@ -6044,7 +6044,7 @@
         <v>45382</v>
       </c>
       <c s="11" r="E186">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F186">
         <is>
@@ -6063,12 +6063,12 @@
       </c>
       <c s="9" t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C187">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D187">
@@ -6089,32 +6089,32 @@
     <row r="188" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C188">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D188">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E188">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G188">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="0">
@@ -6125,23 +6125,23 @@
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D189">
         <v>45366</v>
       </c>
       <c s="11" r="E189">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G189">
@@ -6151,55 +6151,55 @@
     <row r="190" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C190">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D190">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E190">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G190">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C191">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D191">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E191">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c s="12" r="G191">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="0">
@@ -6218,19 +6218,19 @@
       </c>
       <c s="9" t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C192">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D192">
         <v>45275</v>
       </c>
       <c s="11" r="E192">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
@@ -6249,19 +6249,19 @@
       </c>
       <c s="9" t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C193">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D193">
         <v>45275</v>
       </c>
       <c s="11" r="E193">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
@@ -6280,19 +6280,19 @@
       </c>
       <c s="9" t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C194">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D194">
         <v>45275</v>
       </c>
       <c s="11" r="E194">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
@@ -6306,24 +6306,24 @@
     <row r="195" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C195">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D195">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E195">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F195">
         <is>
@@ -6331,30 +6331,30 @@
         </is>
       </c>
       <c s="12" r="G195">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C196">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D196">
-        <v>45294</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E196">
-        <v>136</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F196">
         <is>
@@ -6362,30 +6362,30 @@
         </is>
       </c>
       <c s="12" r="G196">
-        <v>45217</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C197">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D197">
-        <v>45473</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E197">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c s="12" r="G197">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="0">
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c s="10" r="D198">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E198">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
@@ -6444,10 +6444,10 @@
         </is>
       </c>
       <c s="10" r="D199">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E199">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
@@ -6461,24 +6461,24 @@
     <row r="200" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D200">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E200">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
@@ -6486,18 +6486,18 @@
         </is>
       </c>
       <c s="12" r="G200">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
@@ -6509,7 +6509,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E201">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
@@ -6523,12 +6523,12 @@
     <row r="202" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
@@ -6540,7 +6540,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E202">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F202">
         <is>
@@ -6554,24 +6554,24 @@
     <row r="203" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D203">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E203">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F203">
         <is>
@@ -6579,61 +6579,61 @@
         </is>
       </c>
       <c s="12" r="G203">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D204">
-        <v>45237</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E204">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F204">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G204">
-        <v>45176</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C205">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D205">
-        <v>45387</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E205">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F205">
         <is>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c s="12" r="G205">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="0">
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c s="10" r="D206">
-        <v>45317</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E206">
         <v>2</v>
@@ -6692,14 +6692,14 @@
         </is>
       </c>
       <c s="10" r="D207">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E207">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F207">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G207">
@@ -6714,7 +6714,7 @@
       </c>
       <c s="9" t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C208">
@@ -6726,11 +6726,11 @@
         <v>45303</v>
       </c>
       <c s="11" r="E208">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F208">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G208">
@@ -6745,7 +6745,7 @@
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c s="10" r="D209">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E209">
         <v>3</v>
@@ -6776,7 +6776,7 @@
       </c>
       <c s="9" t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C210">
@@ -6788,7 +6788,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E210">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F210">
         <is>
@@ -6807,7 +6807,7 @@
       </c>
       <c s="9" t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C211">
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c s="10" r="D211">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F211">
         <is>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c s="10" r="D212">
-        <v>45247</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E212">
         <v>1</v>
@@ -6869,7 +6869,7 @@
       </c>
       <c s="9" t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C213">
@@ -6878,14 +6878,14 @@
         </is>
       </c>
       <c s="10" r="D213">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E213">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F213">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G213">
@@ -6900,7 +6900,7 @@
       </c>
       <c s="9" t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C214">
@@ -6912,7 +6912,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E214">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F214">
         <is>
@@ -6926,86 +6926,86 @@
     <row r="215" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C215">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D215">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E215">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F215">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G215">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C216">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D216">
-        <v>45199</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E216">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G216">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C217">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D217">
-        <v>45213</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E217">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
@@ -7019,24 +7019,24 @@
     <row r="218" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C218">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D218">
-        <v>45283</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E218">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c s="12" r="G218">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="0">
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c s="10" r="D219">
-        <v>45192</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E219">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
@@ -7081,24 +7081,24 @@
     <row r="220" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C220">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D220">
-        <v>45137</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E220">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F220">
         <is>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c s="12" r="G220">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="0">
@@ -7117,19 +7117,19 @@
       </c>
       <c s="9" t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C221">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D221">
-        <v>45107</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E221">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F221">
         <is>
@@ -7143,32 +7143,32 @@
     <row r="222" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C222">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D222">
-        <v>45233</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E222">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F222">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G222">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="0">
@@ -7188,10 +7188,10 @@
         </is>
       </c>
       <c s="10" r="D223">
-        <v>45205</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E223">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F223">
         <is>
@@ -7205,24 +7205,24 @@
     <row r="224" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C224">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D224">
-        <v>45175</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E224">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
@@ -7230,30 +7230,30 @@
         </is>
       </c>
       <c s="12" r="G224">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C225">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D225">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E225">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
@@ -7261,123 +7261,123 @@
         </is>
       </c>
       <c s="12" r="G225">
-        <v>45091</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C226">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D226">
-        <v>45128</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E226">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G226">
-        <v>45090</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C227">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D227">
-        <v>45170</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E227">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G227">
-        <v>45085</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C228">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D228">
-        <v>45106</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E228">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F228">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G228">
-        <v>45083</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C229">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D229">
-        <v>45107</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E229">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F229">
         <is>
@@ -7385,30 +7385,30 @@
         </is>
       </c>
       <c s="12" r="G229">
-        <v>45070</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D230">
-        <v>45115</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E230">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
@@ -7416,61 +7416,61 @@
         </is>
       </c>
       <c s="12" r="G230">
-        <v>45055</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D231">
-        <v>45105</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E231">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G231">
-        <v>45044</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C232">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D232">
-        <v>45135</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E232">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F232">
         <is>
@@ -7478,30 +7478,30 @@
         </is>
       </c>
       <c s="12" r="G232">
-        <v>45041</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D233">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E233">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F233">
         <is>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c s="12" r="G233">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="0">
@@ -7520,12 +7520,12 @@
       </c>
       <c s="9" t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C234">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D234">
@@ -7551,12 +7551,12 @@
       </c>
       <c s="9" t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C235">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D235">
@@ -7582,12 +7582,12 @@
       </c>
       <c s="9" t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C236">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D236">
@@ -7613,12 +7613,12 @@
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D237">
@@ -7639,86 +7639,86 @@
     <row r="238" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C238">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E238">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F238">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G238">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E239">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F239">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G239">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D240">
-        <v>45058</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E240">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
@@ -7732,24 +7732,24 @@
     <row r="241" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D241">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E241">
-        <v>379</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
@@ -7757,30 +7757,30 @@
         </is>
       </c>
       <c s="12" r="G241">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D242">
         <v>45079</v>
       </c>
       <c s="11" r="E242">
-        <v>201</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F242">
         <is>
@@ -7794,12 +7794,12 @@
     <row r="243" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
@@ -7808,103 +7808,103 @@
         </is>
       </c>
       <c s="10" r="D243">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E243">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F243">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G243">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D244">
-        <v>44939</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E244">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F244">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G244">
-        <v>44937</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C245">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D245">
-        <v>44890</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E245">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F245">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G245">
-        <v>44827</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C246">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D246">
-        <v>44907</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E246">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F246">
         <is>
@@ -7912,30 +7912,30 @@
         </is>
       </c>
       <c s="12" r="G246">
-        <v>44846</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>44911</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E247">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
@@ -7943,80 +7943,80 @@
         </is>
       </c>
       <c s="12" r="G247">
-        <v>44845</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D248">
-        <v>44869</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E248">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G248">
-        <v>44812</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C249">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D249">
-        <v>44866</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E249">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F249">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G249">
-        <v>44803</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C250">
@@ -8025,41 +8025,41 @@
         </is>
       </c>
       <c s="10" r="D250">
-        <v>44856</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E250">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F250">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G250">
-        <v>44795</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D251">
-        <v>44815</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E251">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F251">
         <is>
@@ -8067,30 +8067,30 @@
         </is>
       </c>
       <c s="12" r="G251">
-        <v>44755</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C252">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D252">
-        <v>44802</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E252">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F252">
         <is>
@@ -8098,30 +8098,30 @@
         </is>
       </c>
       <c s="12" r="G252">
-        <v>44741</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C253">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D253">
-        <v>44865</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E253">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F253">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c s="12" r="G253">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="0">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c s="10" r="D254">
-        <v>44805</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E254">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F254">
         <is>
@@ -8166,74 +8166,74 @@
     <row r="255" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D255">
-        <v>44712</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E255">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F255">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G255">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D256">
-        <v>44600</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E256">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G256">
-        <v>44600</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C257">
@@ -8242,10 +8242,10 @@
         </is>
       </c>
       <c s="10" r="D257">
-        <v>44652</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E257">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
@@ -8253,30 +8253,30 @@
         </is>
       </c>
       <c s="12" r="G257">
-        <v>44578</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C258">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D258">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E258">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c s="12" r="G258">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="0">
@@ -8307,7 +8307,7 @@
         <v>44620</v>
       </c>
       <c s="11" r="E259">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
@@ -8321,24 +8321,24 @@
     <row r="260" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D260">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E260">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F260">
         <is>
@@ -8346,30 +8346,30 @@
         </is>
       </c>
       <c s="12" r="G260">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C261">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D261">
-        <v>44531</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E261">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F261">
         <is>
@@ -8377,30 +8377,30 @@
         </is>
       </c>
       <c s="12" r="G261">
-        <v>44470</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C262">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D262">
-        <v>44799</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E262">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F262">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c s="12" r="G262">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="0">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c s="10" r="D263">
-        <v>44743</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E263">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F263">
         <is>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c s="10" r="D264">
-        <v>44680</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E264">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F264">
         <is>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c s="10" r="D265">
-        <v>44652</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E265">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c s="10" r="D266">
-        <v>44575</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E266">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c s="10" r="D267">
-        <v>44512</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E267">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
@@ -8569,12 +8569,12 @@
     <row r="268" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C268">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c s="10" r="D268">
-        <v>44469</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E268">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8594,30 +8594,30 @@
         </is>
       </c>
       <c s="12" r="G268">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C269">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D269">
-        <v>44482</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E269">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
@@ -8625,30 +8625,30 @@
         </is>
       </c>
       <c s="12" r="G269">
-        <v>44421</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C270">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D270">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E270">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c s="12" r="G270">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="0">
@@ -8667,7 +8667,7 @@
       </c>
       <c s="9" t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C271">
@@ -8679,7 +8679,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E271">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
@@ -8698,19 +8698,19 @@
       </c>
       <c s="9" t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C272">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D272">
         <v>44469</v>
       </c>
       <c s="11" r="E272">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
@@ -8724,24 +8724,24 @@
     <row r="273" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C273">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E273">
-        <v>402</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
@@ -8749,30 +8749,30 @@
         </is>
       </c>
       <c s="12" r="G273">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C274">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D274">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E274">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
@@ -8780,18 +8780,18 @@
         </is>
       </c>
       <c s="12" r="G274">
-        <v>44383</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C275">
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c s="10" r="D275">
-        <v>44348</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E275">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
@@ -8811,18 +8811,18 @@
         </is>
       </c>
       <c s="12" r="G275">
-        <v>44308</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C276">
@@ -8831,49 +8831,49 @@
         </is>
       </c>
       <c s="10" r="D276">
-        <v>44347</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E276">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G276">
-        <v>44291</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C277">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44311</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E277">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G277">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="0">
@@ -8893,10 +8893,10 @@
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44256</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E278">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
@@ -8910,32 +8910,32 @@
     <row r="279" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C279">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D279">
-        <v>44358</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E279">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G279">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="0">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c s="10" r="D280">
-        <v>44330</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E280">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8986,10 +8986,10 @@
         </is>
       </c>
       <c s="10" r="D281">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E281">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c s="10" r="D282">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E282">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
@@ -9034,12 +9034,12 @@
     <row r="283" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C283">
@@ -9051,7 +9051,7 @@
         <v>44288</v>
       </c>
       <c s="11" r="E283">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
@@ -9065,24 +9065,24 @@
     <row r="284" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C284">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E284">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c s="12" r="G284">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="0">
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c s="10" r="D285">
-        <v>44264</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E285">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
@@ -9127,24 +9127,24 @@
     <row r="286" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C286">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D286">
-        <v>44242</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E286">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
@@ -9152,100 +9152,100 @@
         </is>
       </c>
       <c s="12" r="G286">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C287">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D287">
-        <v>44270</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E287">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G287">
-        <v>44168</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C288">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D288">
-        <v>44214</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E288">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G288">
-        <v>44160</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C289">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D289">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E289">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G289">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="0">
@@ -9268,11 +9268,11 @@
         <v>44211</v>
       </c>
       <c s="11" r="E290">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G290">
@@ -9282,12 +9282,12 @@
     <row r="291" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C291">
@@ -9296,29 +9296,29 @@
         </is>
       </c>
       <c s="10" r="D291">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E291">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G291">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C292">
@@ -9327,69 +9327,69 @@
         </is>
       </c>
       <c s="10" r="D292">
-        <v>44214</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E292">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F292">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G292">
-        <v>44151</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C293">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44186</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E293">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F293">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G293">
-        <v>44127</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C294">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D294">
-        <v>44104</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E294">
         <v>59</v>
@@ -9400,100 +9400,100 @@
         </is>
       </c>
       <c s="12" r="G294">
-        <v>44104</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C295">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D295">
-        <v>44197</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E295">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G295">
-        <v>44151</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">7241</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">SP+</t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C296">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Elgin</t>
         </is>
       </c>
       <c s="10" r="D296">
-        <v>43914</v>
+        <v>44197</v>
       </c>
       <c s="11" r="E296">
-        <v>89</v>
+        <v>229</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G296">
-        <v>44099</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">7218</t>
+          <t xml:space="preserve">7241</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
+          <t xml:space="preserve">SP+</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C297">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D297">
-        <v>43903</v>
+        <v>43914</v>
       </c>
       <c s="11" r="E297">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G297">
-        <v>44091</v>
+        <v>44099</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="0">
@@ -9504,19 +9504,19 @@
       </c>
       <c s="9" t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
+          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C298">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D298">
         <v>43903</v>
       </c>
       <c s="11" r="E298">
-        <v>358</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
@@ -9535,19 +9535,19 @@
       </c>
       <c s="9" t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">Sodexo - Medford SD</t>
+          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C299">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D299">
         <v>43903</v>
       </c>
       <c s="11" r="E299">
-        <v>111</v>
+        <v>358</v>
       </c>
       <c s="9" t="inlineStr" r="F299">
         <is>
@@ -9561,32 +9561,32 @@
     <row r="300" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">7217</t>
+          <t xml:space="preserve">7218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">PF Chang's</t>
+          <t xml:space="preserve">Sodexo - Medford SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C300">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D300">
-        <v>44092</v>
+        <v>43903</v>
       </c>
       <c s="11" r="E300">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F300">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G300">
-        <v>44092</v>
+        <v>44091</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="0">
@@ -9597,12 +9597,12 @@
       </c>
       <c s="9" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">PF Chang's - Eugene</t>
+          <t xml:space="preserve">PF Chang's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C301">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D301">
@@ -9623,32 +9623,32 @@
     <row r="302" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">7215</t>
+          <t xml:space="preserve">7217</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Salem</t>
+          <t xml:space="preserve">PF Chang's - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C302">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D302">
-        <v>44137</v>
+        <v>44092</v>
       </c>
       <c s="11" r="E302">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F302">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G302">
-        <v>44077</v>
+        <v>44092</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="0">
@@ -9659,19 +9659,19 @@
       </c>
       <c s="9" t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Portland</t>
+          <t xml:space="preserve">LAGS Medical Center - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C303">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D303">
         <v>44137</v>
       </c>
       <c s="11" r="E303">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F303">
         <is>
@@ -9685,12 +9685,12 @@
     <row r="304" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">7211</t>
+          <t xml:space="preserve">7215</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">Bon Appetit</t>
+          <t xml:space="preserve">LAGS Medical Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C304">
@@ -9699,18 +9699,18 @@
         </is>
       </c>
       <c s="10" r="D304">
-        <v>44104</v>
+        <v>44137</v>
       </c>
       <c s="11" r="E304">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G304">
-        <v>44075</v>
+        <v>44077</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="0">
@@ -9733,11 +9733,11 @@
         <v>44104</v>
       </c>
       <c s="11" r="E305">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G305">
@@ -9747,24 +9747,24 @@
     <row r="306" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">7209</t>
+          <t xml:space="preserve">7211</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">Dave &amp; Buster's</t>
+          <t xml:space="preserve">Bon Appetit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C306">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D306">
-        <v>44143</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E306">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F306">
         <is>
@@ -9772,123 +9772,123 @@
         </is>
       </c>
       <c s="12" r="G306">
-        <v>44082</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">7207</t>
+          <t xml:space="preserve">7209</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">PGE - Boardman</t>
+          <t xml:space="preserve">Dave &amp; Buster's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C307">
         <is>
-          <t xml:space="preserve">Boardman</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D307">
-        <v>44140</v>
+        <v>44143</v>
       </c>
       <c s="11" r="E307">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c s="9" t="inlineStr" r="F307">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G307">
-        <v>44075</v>
+        <v>44082</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">7199</t>
+          <t xml:space="preserve">7207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">LAIKA</t>
+          <t xml:space="preserve">PGE - Boardman</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C308">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Boardman</t>
         </is>
       </c>
       <c s="10" r="D308">
+        <v>44140</v>
+      </c>
+      <c s="11" r="E308">
+        <v>22</v>
+      </c>
+      <c s="9" t="inlineStr" r="F308">
+        <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G308">
         <v>44075</v>
-      </c>
-      <c s="11" r="E308">
-        <v>50</v>
-      </c>
-      <c s="9" t="inlineStr" r="F308">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G308">
-        <v>44057</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">7192</t>
+          <t xml:space="preserve">7199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">HMSHost</t>
+          <t xml:space="preserve">LAIKA</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C309">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D309">
-        <v>44119</v>
+        <v>44075</v>
       </c>
       <c s="11" r="E309">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F309">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G309">
-        <v>44054</v>
+        <v>44057</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">7186</t>
+          <t xml:space="preserve">7192</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">HMSHost</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D310">
-        <v>44124</v>
+        <v>44119</v>
       </c>
       <c s="11" r="E310">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F310">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c s="12" r="G310">
-        <v>44032</v>
+        <v>44054</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="0">
@@ -9907,19 +9907,19 @@
       </c>
       <c s="9" t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C311">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D311">
-        <v>44099</v>
+        <v>44124</v>
       </c>
       <c s="11" r="E311">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F311">
         <is>
@@ -9938,19 +9938,19 @@
       </c>
       <c s="9" t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C312">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D312">
         <v>44099</v>
       </c>
       <c s="11" r="E312">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
@@ -9964,24 +9964,24 @@
     <row r="313" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">7185</t>
+          <t xml:space="preserve">7186</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D313">
-        <v>44105</v>
+        <v>44099</v>
       </c>
       <c s="11" r="E313">
-        <v>277</v>
+        <v>355</v>
       </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
@@ -9989,18 +9989,18 @@
         </is>
       </c>
       <c s="12" r="G313">
-        <v>44041</v>
+        <v>44032</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">7184</t>
+          <t xml:space="preserve">7185</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
+          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
@@ -10009,29 +10009,29 @@
         </is>
       </c>
       <c s="10" r="D314">
-        <v>43910</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E314">
-        <v>70</v>
+        <v>277</v>
       </c>
       <c s="9" t="inlineStr" r="F314">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G314">
-        <v>44043</v>
+        <v>44041</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">7171</t>
+          <t xml:space="preserve">7184</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
+          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c s="10" r="D315">
-        <v>44105</v>
+        <v>43910</v>
       </c>
       <c s="11" r="E315">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F315">
         <is>
@@ -10057,32 +10057,32 @@
     <row r="316" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">7162</t>
+          <t xml:space="preserve">7171</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">Nike - Childcare  </t>
+          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C316">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D316">
         <v>44105</v>
       </c>
       <c s="11" r="E316">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c s="9" t="inlineStr" r="F316">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G316">
-        <v>44035</v>
+        <v>44043</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="0">
@@ -10093,7 +10093,7 @@
       </c>
       <c s="9" t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">Nike</t>
+          <t xml:space="preserve">Nike - Childcare  </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C317">
@@ -10105,7 +10105,7 @@
         <v>44105</v>
       </c>
       <c s="11" r="E317">
-        <v>308</v>
+        <v>192</v>
       </c>
       <c s="9" t="inlineStr" r="F317">
         <is>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c s="10" r="D318">
-        <v>44035</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E318">
-        <v>700</v>
+        <v>308</v>
       </c>
       <c s="9" t="inlineStr" r="F318">
         <is>
@@ -10150,59 +10150,59 @@
     <row r="319" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">7151</t>
+          <t xml:space="preserve">7162</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">American Queen Steamboat Company </t>
+          <t xml:space="preserve">Nike</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C319">
         <is>
-          <t xml:space="preserve">New Albany, IN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D319">
-        <v>44098</v>
+        <v>44035</v>
       </c>
       <c s="11" r="E319">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c s="9" t="inlineStr" r="F319">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G319">
-        <v>44034</v>
+        <v>44035</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">7135</t>
+          <t xml:space="preserve">7151</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">Vesta </t>
+          <t xml:space="preserve">American Queen Steamboat Company </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C320">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">New Albany, IN</t>
         </is>
       </c>
       <c s="10" r="D320">
-        <v>44034</v>
+        <v>44098</v>
       </c>
       <c s="11" r="E320">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c s="9" t="inlineStr" r="F320">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G320">
@@ -10212,24 +10212,24 @@
     <row r="321" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">7134</t>
+          <t xml:space="preserve">7135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">Pioneer Pacific College</t>
+          <t xml:space="preserve">Vesta </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C321">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D321">
-        <v>44043</v>
+        <v>44034</v>
       </c>
       <c s="11" r="E321">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F321">
         <is>
@@ -10237,7 +10237,7 @@
         </is>
       </c>
       <c s="12" r="G321">
-        <v>44033</v>
+        <v>44034</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="0">
@@ -10248,19 +10248,19 @@
       </c>
       <c s="9" t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">Pioneer Pacific College - Beaverton</t>
+          <t xml:space="preserve">Pioneer Pacific College</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C322">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D322">
         <v>44043</v>
       </c>
       <c s="11" r="E322">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F322">
         <is>
@@ -10279,19 +10279,19 @@
       </c>
       <c s="9" t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">Pioneer Pacific College - Springfield</t>
+          <t xml:space="preserve">Pioneer Pacific College - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C323">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D323">
         <v>44043</v>
       </c>
       <c s="11" r="E323">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F323">
         <is>
@@ -10305,32 +10305,32 @@
     <row r="324" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">7071</t>
+          <t xml:space="preserve">7134</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">United - PDX</t>
+          <t xml:space="preserve">Pioneer Pacific College - Springfield</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C324">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D324">
-        <v>44105</v>
+        <v>44043</v>
       </c>
       <c s="11" r="E324">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F324">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G324">
-        <v>44020</v>
+        <v>44033</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="0">
@@ -10353,7 +10353,7 @@
         <v>44105</v>
       </c>
       <c s="11" r="E325">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c s="9" t="inlineStr" r="F325">
         <is>
@@ -10367,24 +10367,24 @@
     <row r="326" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">7070</t>
+          <t xml:space="preserve">7071</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">arauco - Albany </t>
+          <t xml:space="preserve">United - PDX</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C326">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D326">
-        <v>44018</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E326">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F326">
         <is>
@@ -10392,30 +10392,30 @@
         </is>
       </c>
       <c s="12" r="G326">
-        <v>44018</v>
+        <v>44020</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">7057</t>
+          <t xml:space="preserve">7070</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">Hampton Inn &amp; Suites - Portland</t>
+          <t xml:space="preserve">arauco - Albany </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C327">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D327">
-        <v>44012</v>
+        <v>44018</v>
       </c>
       <c s="11" r="E327">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F327">
         <is>
@@ -10429,12 +10429,12 @@
     <row r="328" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">7056</t>
+          <t xml:space="preserve">7057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">Atrium Hospitality - Portland Embassy S</t>
+          <t xml:space="preserve">Hampton Inn &amp; Suites - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C328">
@@ -10443,29 +10443,29 @@
         </is>
       </c>
       <c s="10" r="D328">
-        <v>43902</v>
+        <v>44012</v>
       </c>
       <c s="11" r="E328">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F328">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G328">
-        <v>43964</v>
+        <v>44018</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">7052</t>
+          <t xml:space="preserve">7056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">Hilton Portland Downtown</t>
+          <t xml:space="preserve">Atrium Hospitality - Portland Embassy S</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C329">
@@ -10474,10 +10474,10 @@
         </is>
       </c>
       <c s="10" r="D329">
-        <v>43912</v>
+        <v>43902</v>
       </c>
       <c s="11" r="E329">
-        <v>330</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F329">
         <is>
@@ -10485,122 +10485,153 @@
         </is>
       </c>
       <c s="12" r="G329">
-        <v>44012</v>
+        <v>43964</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7052</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Hilton Portland Downtown</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C330">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D330"/>
-      <c s="13" t="str" r="E330"/>
+          <t xml:space="preserve">Portland</t>
+        </is>
+      </c>
+      <c s="10" r="D330">
+        <v>43912</v>
+      </c>
+      <c s="11" r="E330">
+        <v>330</v>
+      </c>
       <c s="9" t="inlineStr" r="F330">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G330">
-        <v>44909</v>
+        <v>44012</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A331">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B331">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C331">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D331"/>
       <c s="13" t="str" r="E331"/>
       <c s="9" t="inlineStr" r="F331">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G331">
-        <v>45125</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A332">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B332">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C332">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">Mesa, AZ</t>
         </is>
       </c>
       <c s="9" t="str" r="D332"/>
       <c s="13" t="str" r="E332"/>
       <c s="9" t="inlineStr" r="F332">
         <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G332">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="333" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A333">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B333">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C333">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D333"/>
+      <c s="13" t="str" r="E333"/>
+      <c s="9" t="inlineStr" r="F333">
+        <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
-      <c s="12" r="G332">
+      <c s="12" r="G333">
         <v>45887</v>
       </c>
     </row>
-    <row r="333" ht="3.6" customHeight="0">
-      <c s="14" t="inlineStr" r="A333">
+    <row r="334" ht="3.6" customHeight="0">
+      <c s="14" t="inlineStr" r="A334">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B333">
+      <c s="14" t="inlineStr" r="B334">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C333">
+      <c s="14" t="inlineStr" r="C334">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D333">
+      <c s="14" t="inlineStr" r="D334">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E333">
+      <c s="14" t="inlineStr" r="E334">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F333">
+      <c s="14" t="inlineStr" r="F334">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G333">
+      <c s="14" t="inlineStr" r="G334">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -10615,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/5/2026 7:01:52 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/5/2026 6:47:18 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/5/2016 to 8/5/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/6/2016 to 8/6/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/5/2026 6:47:18 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/6/2026 7:00:15 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/6/2026 7:00:15 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/6/2026 9:20:31 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/6/2016 to 8/6/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/7/2016 to 8/7/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/6/2026 9:20:31 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/7/2026 6:00:01 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/7/2016 to 8/7/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/8/2016 to 8/8/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/7/2026 6:09:00 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/8/2026 5:45:30 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/8/2026 5:45:30 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/8/2026 6:14:51 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/8/2016 to 8/8/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/9/2016 to 8/9/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/8/2026 6:14:51 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/9/2026 5:50:28 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/9/2026 5:50:28 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/9/2026 6:14:16 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/9/2016 to 8/9/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/10/2016 to 8/10/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/9/2026 6:14:16 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/10/2026 6:05:16 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/10/2026 6:05:16 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/10/2026 6:15:28 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/10/2016 to 8/10/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/11/2016 to 8/11/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/10/2026 6:15:28 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/11/2026 6:02:28 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/11/2016 to 8/11/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/12/2016 to 8/12/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/11/2026 6:20:09 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/12/2026 6:02:33 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/12/2026 6:02:33 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/12/2026 6:12:41 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/12/2016 to 8/12/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/13/2016 to 8/13/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/12/2026 6:12:41 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/13/2026 6:04:24 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/13/2026 6:04:24 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/13/2026 6:24:50 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/13/2016 to 8/13/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/14/2016 to 8/14/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/13/2026 6:24:50 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/14/2026 6:00:09 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/14/2026 6:00:09 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/14/2026 5:57:05 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/14/2016 to 8/14/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/15/2016 to 8/15/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/14/2026 5:57:05 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/15/2026 5:40:17 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/15/2026 5:40:17 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/15/2026 5:58:30 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/15/2016 to 8/15/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/16/2016 to 8/16/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/15/2026 5:58:30 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/16/2026 5:38:20 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/16/2026 5:38:20 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/16/2026 5:58:47 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/16/2016 to 8/16/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/17/2016 to 8/17/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/16/2026 5:58:47 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/17/2026 5:41:12 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/17/2026 5:41:12 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/17/2026 6:02:30 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/17/2016 to 8/17/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/18/2016 to 8/18/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/17/2026 6:02:30 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/18/2026 5:46:47 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/18/2026 5:46:47 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/18/2026 5:57:30 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/18/2016 to 8/18/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/19/2016 to 8/19/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/18/2026 5:57:30 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/19/2026 5:44:20 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/19/2026 5:44:20 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/19/2026 5:56:45 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/19/2016 to 8/19/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/20/2016 to 8/20/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/19/2026 5:56:45 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/20/2026 5:45:16 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/20/2026 5:45:16 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/20/2026 6:02:10 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/20/2016 to 8/20/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/21/2016 to 8/21/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/20/2026 6:02:10 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/21/2026 5:47:20 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/21/2026 5:47:20 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/21/2026 5:58:56 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/21/2016 to 8/21/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/22/2016 to 8/22/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/21/2026 5:58:56 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/22/2026 5:39:44 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/22/2026 5:39:44 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/22/2026 6:00:00 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/22/2016 to 8/22/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/23/2016 to 8/23/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/22/2026 6:00:00 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/23/2026 5:40:48 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/23/2026 5:40:48 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/23/2026 5:58:41 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/23/2016 to 8/23/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/24/2016 to 8/24/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/23/2026 5:58:41 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/24/2026 5:46:15 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/24/2026 5:46:15 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/24/2026 5:59:17 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/24/2016 to 8/24/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/25/2016 to 8/25/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/24/2026 5:59:17 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/25/2026 5:48:16 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -385,32 +385,32 @@
     <row r="4" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">9556</t>
+          <t xml:space="preserve">9588</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">JeniusBank</t>
+          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">New York, NY</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D4">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c s="11" r="E4">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c s="9" t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G4">
-        <v>46244</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="0">
@@ -421,19 +421,19 @@
       </c>
       <c s="9" t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">JeniusBank</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">New York, NY</t>
         </is>
       </c>
       <c s="10" r="D5">
         <v>46304</v>
       </c>
       <c s="11" r="E5">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F5">
         <is>
@@ -447,21 +447,21 @@
     <row r="6" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">9555</t>
+          <t xml:space="preserve">9556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">Bowtech, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D6">
-        <v>46446</v>
+        <v>46304</v>
       </c>
       <c s="11" r="E6">
         <v>1</v>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c s="12" r="G6">
-        <v>46230</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="0">
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c s="10" r="D7">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c s="11" r="E7">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F7">
         <is>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c s="10" r="D8">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F8">
         <is>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c s="10" r="D9">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F9">
         <is>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c s="10" r="D10">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E10">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F10">
         <is>
@@ -602,24 +602,24 @@
     <row r="11" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">9553</t>
+          <t xml:space="preserve">9555</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
+          <t xml:space="preserve">Bowtech, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D11">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E11">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F11">
         <is>
@@ -627,34 +627,34 @@
         </is>
       </c>
       <c s="12" r="G11">
-        <v>46237</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9553</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">Avamere Health Services, LLC</t>
+          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">Tigard</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D12">
-        <v>46266</v>
+        <v>46298</v>
       </c>
       <c s="11" r="E12">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G12">
@@ -664,94 +664,94 @@
     <row r="13" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">9549</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
+          <t xml:space="preserve">Avamere Health Services, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tigard</t>
         </is>
       </c>
       <c s="10" r="D13">
-        <v>46325</v>
+        <v>46266</v>
       </c>
       <c s="11" r="E13">
-        <v>387</v>
+        <v>129</v>
       </c>
       <c s="9" t="inlineStr" r="F13">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G13">
-        <v>46233</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">9534</t>
+          <t xml:space="preserve">9549</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
+          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D14">
-        <v>46262</v>
+        <v>46325</v>
       </c>
       <c s="11" r="E14">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c s="9" t="inlineStr" r="F14">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G14">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">Adventist Health Tillamook</t>
+          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D15">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c s="11" r="E15">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c s="9" t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G15">
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="0">
@@ -762,19 +762,19 @@
       </c>
       <c s="9" t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">Adventist Health Portland</t>
+          <t xml:space="preserve">Adventist Health Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">Portland, </t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D16">
         <v>46206</v>
       </c>
       <c s="11" r="E16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F16">
         <is>
@@ -793,19 +793,19 @@
       </c>
       <c s="9" t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
+          <t xml:space="preserve">Adventist Health Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C17">
         <is>
-          <t xml:space="preserve">The Dalles</t>
+          <t xml:space="preserve">Portland, </t>
         </is>
       </c>
       <c s="10" r="D17">
         <v>46206</v>
       </c>
       <c s="11" r="E17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F17">
         <is>
@@ -819,32 +819,32 @@
     <row r="18" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">PacificSource</t>
+          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">The Dalles</t>
         </is>
       </c>
       <c s="10" r="D18">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E18">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F18">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G18">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="0">
@@ -855,23 +855,23 @@
       </c>
       <c s="9" t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">PacificSource - Bend</t>
+          <t xml:space="preserve">PacificSource</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D19">
         <v>46234</v>
       </c>
       <c s="11" r="E19">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G19">
@@ -886,19 +886,19 @@
       </c>
       <c s="9" t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">PacificSource - Portland</t>
+          <t xml:space="preserve">PacificSource - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D20">
         <v>46234</v>
       </c>
       <c s="11" r="E20">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F20">
         <is>
@@ -917,12 +917,12 @@
       </c>
       <c s="9" t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">PacificSource - Salem</t>
+          <t xml:space="preserve">PacificSource - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D21">
@@ -948,19 +948,19 @@
       </c>
       <c s="9" t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">PacificSource Hood River</t>
+          <t xml:space="preserve">PacificSource - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D22">
         <v>46234</v>
       </c>
       <c s="11" r="E22">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F22">
         <is>
@@ -974,63 +974,63 @@
     <row r="23" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">9511</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
+          <t xml:space="preserve">PacificSource Hood River</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D23">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E23">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G23">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9511</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D24">
-        <v>46234</v>
+        <v>46228</v>
       </c>
       <c s="11" r="E24">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G24">
-        <v>46160</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="0">
@@ -1041,19 +1041,19 @@
       </c>
       <c s="9" t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D25">
         <v>46234</v>
       </c>
       <c s="11" r="E25">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F25">
         <is>
@@ -1072,19 +1072,19 @@
       </c>
       <c s="9" t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D26">
         <v>46234</v>
       </c>
       <c s="11" r="E26">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F26">
         <is>
@@ -1103,19 +1103,19 @@
       </c>
       <c s="9" t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D27">
         <v>46234</v>
       </c>
       <c s="11" r="E27">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F27">
         <is>
@@ -1134,19 +1134,19 @@
       </c>
       <c s="9" t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D28">
         <v>46234</v>
       </c>
       <c s="11" r="E28">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c s="9" t="inlineStr" r="F28">
         <is>
@@ -1160,86 +1160,86 @@
     <row r="29" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D29">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E29">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G29">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D30">
-        <v>46201</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E30">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G30">
-        <v>46141</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D31">
-        <v>46295</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E31">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F31">
         <is>
@@ -1247,49 +1247,49 @@
         </is>
       </c>
       <c s="12" r="G31">
-        <v>46114</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D32">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E32">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G32">
-        <v>46108</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
@@ -1298,18 +1298,18 @@
         </is>
       </c>
       <c s="10" r="D33">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E33">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G33">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="0">
@@ -1320,7 +1320,7 @@
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
@@ -1346,24 +1346,24 @@
     <row r="35" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D35">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E35">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F35">
         <is>
@@ -1371,38 +1371,38 @@
         </is>
       </c>
       <c s="12" r="G35">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D36">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E36">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G36">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="0">
@@ -1413,19 +1413,19 @@
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D37">
         <v>46131</v>
       </c>
       <c s="11" r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F37">
         <is>
@@ -1439,63 +1439,63 @@
     <row r="38" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D38">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E38">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G38">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D39">
         <v>46117</v>
       </c>
       <c s="11" r="E39">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G39">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="0">
@@ -1506,19 +1506,19 @@
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D40">
         <v>46117</v>
       </c>
       <c s="11" r="E40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F40">
         <is>
@@ -1537,12 +1537,12 @@
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D41">
@@ -1568,12 +1568,12 @@
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D42">
@@ -1599,12 +1599,12 @@
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D43">
@@ -1630,12 +1630,12 @@
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D44">
@@ -1661,12 +1661,12 @@
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D45">
@@ -1692,12 +1692,12 @@
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D46">
@@ -1723,7 +1723,7 @@
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
@@ -1754,7 +1754,7 @@
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
@@ -1785,12 +1785,12 @@
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D49">
@@ -1816,12 +1816,12 @@
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D50">
@@ -1847,12 +1847,12 @@
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D51">
@@ -1878,7 +1878,7 @@
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
@@ -1909,19 +1909,19 @@
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D53">
         <v>46117</v>
       </c>
       <c s="11" r="E53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F53">
         <is>
@@ -1940,19 +1940,19 @@
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D54">
         <v>46117</v>
       </c>
       <c s="11" r="E54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F54">
         <is>
@@ -1971,19 +1971,19 @@
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D55">
         <v>46117</v>
       </c>
       <c s="11" r="E55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F55">
         <is>
@@ -2002,12 +2002,12 @@
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D56">
@@ -2033,12 +2033,12 @@
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D57">
@@ -2059,24 +2059,24 @@
     <row r="58" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D58">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E58">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F58">
         <is>
@@ -2095,19 +2095,19 @@
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D59">
         <v>46112</v>
       </c>
       <c s="11" r="E59">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F59">
         <is>
@@ -2126,19 +2126,19 @@
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D60">
         <v>46112</v>
       </c>
       <c s="11" r="E60">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F60">
         <is>
@@ -2152,24 +2152,24 @@
     <row r="61" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D61">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E61">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F61">
         <is>
@@ -2177,30 +2177,30 @@
         </is>
       </c>
       <c s="12" r="G61">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D62">
-        <v>46142</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E62">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F62">
         <is>
@@ -2208,30 +2208,30 @@
         </is>
       </c>
       <c s="12" r="G62">
-        <v>46020</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D63">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E63">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F63">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c s="12" r="G63">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="0">
@@ -2250,7 +2250,7 @@
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
@@ -2262,7 +2262,7 @@
         <v>46014</v>
       </c>
       <c s="11" r="E64">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F64">
         <is>
@@ -2281,19 +2281,19 @@
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D65">
         <v>46014</v>
       </c>
       <c s="11" r="E65">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F65">
         <is>
@@ -2307,43 +2307,43 @@
     <row r="66" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D66">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E66">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F66">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G66">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
@@ -2352,29 +2352,29 @@
         </is>
       </c>
       <c s="10" r="D67">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E67">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F67">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G67">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c s="10" r="D68">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E68">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F68">
         <is>
@@ -2400,63 +2400,63 @@
     <row r="69" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D69">
         <v>46054</v>
       </c>
       <c s="11" r="E69">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F69">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G69">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D70">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E70">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F70">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G70">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="0">
@@ -2467,19 +2467,19 @@
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D71">
         <v>45916</v>
       </c>
       <c s="11" r="E71">
-        <v>510</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F71">
         <is>
@@ -2498,7 +2498,7 @@
       </c>
       <c s="9" t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C72">
@@ -2510,7 +2510,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E72">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c s="9" t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C73">
@@ -2541,7 +2541,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E73">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
@@ -2555,24 +2555,24 @@
     <row r="74" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D74">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E74">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F74">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c s="12" r="G74">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="0">
@@ -2591,23 +2591,23 @@
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D75">
         <v>46022</v>
       </c>
       <c s="11" r="E75">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F75">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G75">
@@ -2622,19 +2622,19 @@
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D76">
         <v>46022</v>
       </c>
       <c s="11" r="E76">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F76">
         <is>
@@ -2653,19 +2653,19 @@
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D77">
         <v>46022</v>
       </c>
       <c s="11" r="E77">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
@@ -2684,19 +2684,19 @@
       </c>
       <c s="9" t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C78">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D78">
         <v>46022</v>
       </c>
       <c s="11" r="E78">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
@@ -2710,55 +2710,55 @@
     <row r="79" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C79">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D79">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E79">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G79">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C80">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D80">
         <v>46017</v>
       </c>
       <c s="11" r="E80">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
@@ -2772,28 +2772,28 @@
     <row r="81" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D81">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E81">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G81">
@@ -2817,14 +2817,14 @@
         </is>
       </c>
       <c s="10" r="D82">
-        <v>46017</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E82">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G82">
@@ -2834,86 +2834,86 @@
     <row r="83" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C83">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D83">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E83">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G83">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D84">
-        <v>46022</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E84">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G84">
-        <v>45917</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D85">
-        <v>45978</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E85">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
@@ -2921,18 +2921,18 @@
         </is>
       </c>
       <c s="12" r="G85">
-        <v>45943</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c s="10" r="D86">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E86">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
@@ -2952,38 +2952,38 @@
         </is>
       </c>
       <c s="12" r="G86">
-        <v>45930</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D87">
-        <v>45940</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E87">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G87">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="0">
@@ -3003,14 +3003,14 @@
         </is>
       </c>
       <c s="10" r="D88">
-        <v>45925</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E88">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G88">
@@ -3020,24 +3020,24 @@
     <row r="89" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C89">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D89">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E89">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
@@ -3045,34 +3045,34 @@
         </is>
       </c>
       <c s="12" r="G89">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C90">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D90">
         <v>45976</v>
       </c>
       <c s="11" r="E90">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G90">
@@ -3082,63 +3082,63 @@
     <row r="91" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C91">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D91">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E91">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G91">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D92">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E92">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G92">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="0">
@@ -3149,7 +3149,7 @@
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
@@ -3161,7 +3161,7 @@
         <v>45949</v>
       </c>
       <c s="11" r="E93">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
@@ -3175,12 +3175,12 @@
     <row r="94" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
@@ -3189,41 +3189,41 @@
         </is>
       </c>
       <c s="10" r="D94">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E94">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G94">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C95">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D95">
-        <v>45874</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E95">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
@@ -3231,18 +3231,18 @@
         </is>
       </c>
       <c s="12" r="G95">
-        <v>45867</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C96">
@@ -3251,49 +3251,49 @@
         </is>
       </c>
       <c s="10" r="D96">
-        <v>45920</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E96">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G96">
-        <v>45854</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C97">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D97">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E97">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G97">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="0">
@@ -3304,19 +3304,19 @@
       </c>
       <c s="9" t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D98">
         <v>45912</v>
       </c>
       <c s="11" r="E98">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
@@ -3330,63 +3330,63 @@
     <row r="99" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D99">
         <v>45912</v>
       </c>
       <c s="11" r="E99">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G99">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C100">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D100">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E100">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G100">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="0">
@@ -3397,19 +3397,19 @@
       </c>
       <c s="9" t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C101">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D101">
         <v>45853</v>
       </c>
       <c s="11" r="E101">
-        <v>1544</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
@@ -3440,7 +3440,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E102">
-        <v>174</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
@@ -3471,7 +3471,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E103">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
@@ -3485,86 +3485,86 @@
     <row r="104" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D104">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E104">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G104">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D105">
-        <v>45901</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E105">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G105">
-        <v>45839</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D106">
-        <v>45982</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E106">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c s="12" r="G106">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="0">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c s="10" r="D107">
-        <v>45968</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E107">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c s="10" r="D108">
-        <v>45894</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E108">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
@@ -3640,24 +3640,24 @@
     <row r="109" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D109">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E109">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
@@ -3665,30 +3665,30 @@
         </is>
       </c>
       <c s="12" r="G109">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D110">
         <v>45838</v>
       </c>
       <c s="11" r="E110">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
@@ -3702,94 +3702,94 @@
     <row r="111" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D111">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E111">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G111">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D112">
-        <v>45807</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E112">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G112">
-        <v>45804</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D113">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E113">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G113">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="0">
@@ -3800,19 +3800,19 @@
       </c>
       <c s="9" t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C114">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D114">
         <v>45866</v>
       </c>
       <c s="11" r="E114">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
@@ -3826,55 +3826,55 @@
     <row r="115" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C115">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D115">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E115">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G115">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D116">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E116">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
@@ -3882,85 +3882,85 @@
         </is>
       </c>
       <c s="12" r="G116">
-        <v>45778</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D117">
-        <v>45769</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E117">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G117">
-        <v>45769</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D118">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E118">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G118">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D119">
@@ -3971,69 +3971,69 @@
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G119">
-        <v>45763</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D120">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E120">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G120">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D121">
-        <v>45810</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E121">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G121">
@@ -4043,43 +4043,43 @@
     <row r="122" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D122">
-        <v>45808</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E122">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G122">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
@@ -4088,103 +4088,103 @@
         </is>
       </c>
       <c s="10" r="D123">
-        <v>45834</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E123">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G123">
-        <v>45774</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D124">
-        <v>45838</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E124">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G124">
-        <v>45744</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D125">
-        <v>45706</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E125">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G125">
-        <v>45706</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C126">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D126">
-        <v>45734</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E126">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
@@ -4192,38 +4192,38 @@
         </is>
       </c>
       <c s="12" r="G126">
-        <v>45666</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D127">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E127">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G127">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="0">
@@ -4234,19 +4234,19 @@
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D128">
         <v>45707</v>
       </c>
       <c s="11" r="E128">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
@@ -4260,63 +4260,63 @@
     <row r="129" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D129">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E129">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G129">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D130">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E130">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G130">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="0">
@@ -4327,19 +4327,19 @@
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D131">
         <v>45696</v>
       </c>
       <c s="11" r="E131">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F131">
         <is>
@@ -4353,86 +4353,86 @@
     <row r="132" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D132">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E132">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F132">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G132">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D133">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E133">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F133">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G133">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D134">
         <v>45931</v>
       </c>
       <c s="11" r="E134">
-        <v>221</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F134">
         <is>
@@ -4446,43 +4446,43 @@
     <row r="135" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D135">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E135">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G135">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
@@ -4491,18 +4491,18 @@
         </is>
       </c>
       <c s="10" r="D136">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E136">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G136">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="0">
@@ -4513,19 +4513,19 @@
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D137">
         <v>45726</v>
       </c>
       <c s="11" r="E137">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
@@ -4544,19 +4544,19 @@
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D138">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E138">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
@@ -4575,19 +4575,19 @@
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D139">
         <v>45725</v>
       </c>
       <c s="11" r="E139">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
@@ -4606,19 +4606,19 @@
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D140">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E140">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
@@ -4637,12 +4637,12 @@
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D141">
@@ -4668,12 +4668,12 @@
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D142">
@@ -4699,19 +4699,19 @@
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D143">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E143">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F143">
         <is>
@@ -4730,19 +4730,19 @@
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D144">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E144">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
@@ -4761,7 +4761,7 @@
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c s="10" r="D145">
-        <v>45703</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E145">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
@@ -4792,19 +4792,19 @@
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D146">
-        <v>45690</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E146">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
@@ -4818,12 +4818,12 @@
     <row r="147" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
@@ -4832,72 +4832,72 @@
         </is>
       </c>
       <c s="10" r="D147">
-        <v>45657</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E147">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G147">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D148">
-        <v>45640</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E148">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F148">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G148">
-        <v>45580</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D149">
-        <v>45657</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E149">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F149">
         <is>
@@ -4905,100 +4905,100 @@
         </is>
       </c>
       <c s="12" r="G149">
-        <v>45595</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D150">
-        <v>45584</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E150">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F150">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G150">
-        <v>45584</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D151">
-        <v>45664</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E151">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F151">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G151">
-        <v>45582</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C152">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D152">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E152">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F152">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G152">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="0">
@@ -5009,19 +5009,19 @@
       </c>
       <c s="9" t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C153">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D153">
         <v>45611</v>
       </c>
       <c s="11" r="E153">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
@@ -5040,7 +5040,7 @@
       </c>
       <c s="9" t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C154">
@@ -5052,7 +5052,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E154">
-        <v>124</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F154">
         <is>
@@ -5071,7 +5071,7 @@
       </c>
       <c s="9" t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C155">
@@ -5083,7 +5083,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E155">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
@@ -5097,28 +5097,28 @@
     <row r="156" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C156">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D156">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E156">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G156">
@@ -5128,24 +5128,24 @@
     <row r="157" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C157">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D157">
-        <v>45621</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E157">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
@@ -5153,38 +5153,38 @@
         </is>
       </c>
       <c s="12" r="G157">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D158">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E158">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G158">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="0">
@@ -5195,23 +5195,23 @@
       </c>
       <c s="9" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D159">
         <v>45544</v>
       </c>
       <c s="11" r="E159">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F159">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G159">
@@ -5221,55 +5221,55 @@
     <row r="160" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C160">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D160">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E160">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F160">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G160">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C161">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D161">
-        <v>45654</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E161">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F161">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c s="12" r="G161">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="0">
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c s="10" r="D162">
-        <v>45612</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E162">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5328,14 +5328,14 @@
         </is>
       </c>
       <c s="10" r="D163">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E163">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G163">
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c s="10" r="D164">
-        <v>45569</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
@@ -5390,14 +5390,14 @@
         </is>
       </c>
       <c s="10" r="D165">
-        <v>45555</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E165">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G165">
@@ -5407,24 +5407,24 @@
     <row r="166" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C166">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D166">
-        <v>45653</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E166">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c s="12" r="G166">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="0">
@@ -5452,14 +5452,14 @@
         </is>
       </c>
       <c s="10" r="D167">
-        <v>45505</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E167">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G167">
@@ -5469,24 +5469,24 @@
     <row r="168" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C168">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D168">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E168">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
@@ -5494,13 +5494,13 @@
         </is>
       </c>
       <c s="12" r="G168">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B169">
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c s="10" r="D169">
-        <v>45513</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E169">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
@@ -5525,18 +5525,18 @@
         </is>
       </c>
       <c s="12" r="G169">
-        <v>45450</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C170">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c s="10" r="D170">
-        <v>45504</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E170">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
@@ -5556,30 +5556,30 @@
         </is>
       </c>
       <c s="12" r="G170">
-        <v>45441</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C171">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D171">
-        <v>46229</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E171">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c s="12" r="G171">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="0">
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c s="10" r="D172">
-        <v>45688</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E172">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c s="10" r="D173">
-        <v>45506</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E173">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
@@ -5655,32 +5655,32 @@
     <row r="174" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C174">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D174">
-        <v>45483</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E174">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G174">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="0">
@@ -5700,10 +5700,10 @@
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45401</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E175">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45366</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
@@ -5748,43 +5748,43 @@
     <row r="177" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C177">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D177">
-        <v>45473</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E177">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G177">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C178">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c s="10" r="D178">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E178">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
@@ -5804,111 +5804,111 @@
         </is>
       </c>
       <c s="12" r="G178">
-        <v>45404</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C179">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D179">
         <v>45471</v>
       </c>
       <c s="11" r="E179">
-        <v>740</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G179">
-        <v>45401</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C180">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D180">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E180">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G180">
-        <v>45384</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C181">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D181">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E181">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G181">
-        <v>45380</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C182">
@@ -5917,134 +5917,134 @@
         </is>
       </c>
       <c s="10" r="D182">
-        <v>45439</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E182">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G182">
-        <v>45379</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C183">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D183">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E183">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G183">
-        <v>45372</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C184">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D184">
-        <v>45433</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E184">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G184">
-        <v>45373</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C185">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D185">
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E185">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F185">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G185">
-        <v>45358</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C186">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D186">
-        <v>45352</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E186">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F186">
         <is>
@@ -6052,18 +6052,18 @@
         </is>
       </c>
       <c s="12" r="G186">
-        <v>45345</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C187">
@@ -6072,41 +6072,41 @@
         </is>
       </c>
       <c s="10" r="D187">
-        <v>45401</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E187">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F187">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G187">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C188">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D188">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E188">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c s="12" r="G188">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="0">
@@ -6125,7 +6125,7 @@
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
@@ -6137,7 +6137,7 @@
         <v>45337</v>
       </c>
       <c s="11" r="E189">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
@@ -6151,24 +6151,24 @@
     <row r="190" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C190">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D190">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E190">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
@@ -6176,34 +6176,34 @@
         </is>
       </c>
       <c s="12" r="G190">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C191">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D191">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E191">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G191">
@@ -6218,19 +6218,19 @@
       </c>
       <c s="9" t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C192">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D192">
         <v>45382</v>
       </c>
       <c s="11" r="E192">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
@@ -6249,19 +6249,19 @@
       </c>
       <c s="9" t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C193">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D193">
         <v>45382</v>
       </c>
       <c s="11" r="E193">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
@@ -6280,7 +6280,7 @@
       </c>
       <c s="9" t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C194">
@@ -6292,7 +6292,7 @@
         <v>45382</v>
       </c>
       <c s="11" r="E194">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
@@ -6311,12 +6311,12 @@
       </c>
       <c s="9" t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C195">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D195">
@@ -6337,32 +6337,32 @@
     <row r="196" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C196">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D196">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E196">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F196">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G196">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="0">
@@ -6373,23 +6373,23 @@
       </c>
       <c s="9" t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C197">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D197">
         <v>45366</v>
       </c>
       <c s="11" r="E197">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G197">
@@ -6399,55 +6399,55 @@
     <row r="198" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C198">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D198">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E198">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G198">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C199">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D199">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E199">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c s="12" r="G199">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="0">
@@ -6466,19 +6466,19 @@
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D200">
         <v>45275</v>
       </c>
       <c s="11" r="E200">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
@@ -6497,19 +6497,19 @@
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D201">
         <v>45275</v>
       </c>
       <c s="11" r="E201">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
@@ -6528,19 +6528,19 @@
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D202">
         <v>45275</v>
       </c>
       <c s="11" r="E202">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F202">
         <is>
@@ -6554,24 +6554,24 @@
     <row r="203" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D203">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E203">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F203">
         <is>
@@ -6579,30 +6579,30 @@
         </is>
       </c>
       <c s="12" r="G203">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D204">
-        <v>45294</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E204">
-        <v>136</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F204">
         <is>
@@ -6610,30 +6610,30 @@
         </is>
       </c>
       <c s="12" r="G204">
-        <v>45217</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C205">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D205">
-        <v>45473</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E205">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F205">
         <is>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c s="12" r="G205">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="0">
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c s="10" r="D206">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E206">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F206">
         <is>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c s="10" r="D207">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E207">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F207">
         <is>
@@ -6709,24 +6709,24 @@
     <row r="208" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C208">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D208">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E208">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F208">
         <is>
@@ -6734,18 +6734,18 @@
         </is>
       </c>
       <c s="12" r="G208">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
@@ -6757,7 +6757,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E209">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F209">
         <is>
@@ -6771,12 +6771,12 @@
     <row r="210" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C210">
@@ -6788,7 +6788,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E210">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F210">
         <is>
@@ -6802,24 +6802,24 @@
     <row r="211" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C211">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D211">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E211">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F211">
         <is>
@@ -6827,61 +6827,61 @@
         </is>
       </c>
       <c s="12" r="G211">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C212">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D212">
-        <v>45237</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E212">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F212">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G212">
-        <v>45176</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C213">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D213">
-        <v>45387</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E213">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F213">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c s="12" r="G213">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="0">
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c s="10" r="D214">
-        <v>45317</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E214">
         <v>2</v>
@@ -6940,14 +6940,14 @@
         </is>
       </c>
       <c s="10" r="D215">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E215">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F215">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G215">
@@ -6962,7 +6962,7 @@
       </c>
       <c s="9" t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C216">
@@ -6974,11 +6974,11 @@
         <v>45303</v>
       </c>
       <c s="11" r="E216">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G216">
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c s="10" r="D217">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E217">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
@@ -7024,7 +7024,7 @@
       </c>
       <c s="9" t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C218">
@@ -7036,7 +7036,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E218">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c s="10" r="D219">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E219">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c s="10" r="D220">
-        <v>45247</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E220">
         <v>1</v>
@@ -7126,14 +7126,14 @@
         </is>
       </c>
       <c s="10" r="D221">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E221">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F221">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G221">
@@ -7148,7 +7148,7 @@
       </c>
       <c s="9" t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C222">
@@ -7160,7 +7160,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E222">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F222">
         <is>
@@ -7174,86 +7174,86 @@
     <row r="223" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C223">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D223">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E223">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F223">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G223">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C224">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D224">
-        <v>45199</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E224">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G224">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C225">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D225">
-        <v>45213</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E225">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
@@ -7267,24 +7267,24 @@
     <row r="226" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C226">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D226">
-        <v>45283</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E226">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c s="12" r="G226">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="0">
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c s="10" r="D227">
-        <v>45192</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E227">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
@@ -7329,24 +7329,24 @@
     <row r="228" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C228">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D228">
-        <v>45137</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E228">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F228">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c s="12" r="G228">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="0">
@@ -7365,19 +7365,19 @@
       </c>
       <c s="9" t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C229">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D229">
-        <v>45107</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E229">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F229">
         <is>
@@ -7391,32 +7391,32 @@
     <row r="230" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D230">
-        <v>45233</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E230">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G230">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="0">
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c s="10" r="D231">
-        <v>45205</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E231">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
@@ -7453,24 +7453,24 @@
     <row r="232" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C232">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D232">
-        <v>45175</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E232">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F232">
         <is>
@@ -7478,30 +7478,30 @@
         </is>
       </c>
       <c s="12" r="G232">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D233">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E233">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F233">
         <is>
@@ -7509,123 +7509,123 @@
         </is>
       </c>
       <c s="12" r="G233">
-        <v>45091</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C234">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D234">
-        <v>45128</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E234">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F234">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G234">
-        <v>45090</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C235">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D235">
-        <v>45170</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E235">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F235">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G235">
-        <v>45085</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C236">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D236">
-        <v>45106</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E236">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F236">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G236">
-        <v>45083</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D237">
-        <v>45107</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E237">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F237">
         <is>
@@ -7633,30 +7633,30 @@
         </is>
       </c>
       <c s="12" r="G237">
-        <v>45070</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C238">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45115</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E238">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F238">
         <is>
@@ -7664,61 +7664,61 @@
         </is>
       </c>
       <c s="12" r="G238">
-        <v>45055</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45105</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E239">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F239">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G239">
-        <v>45044</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D240">
-        <v>45135</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E240">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
@@ -7726,30 +7726,30 @@
         </is>
       </c>
       <c s="12" r="G240">
-        <v>45041</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D241">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E241">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c s="12" r="G241">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="0">
@@ -7768,12 +7768,12 @@
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D242">
@@ -7799,12 +7799,12 @@
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D243">
@@ -7830,12 +7830,12 @@
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D244">
@@ -7861,12 +7861,12 @@
       </c>
       <c s="9" t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C245">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D245">
@@ -7887,86 +7887,86 @@
     <row r="246" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C246">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D246">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E246">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F246">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G246">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E247">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G247">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D248">
-        <v>45058</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E248">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
@@ -7980,24 +7980,24 @@
     <row r="249" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C249">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D249">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E249">
-        <v>379</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F249">
         <is>
@@ -8005,30 +8005,30 @@
         </is>
       </c>
       <c s="12" r="G249">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C250">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D250">
         <v>45079</v>
       </c>
       <c s="11" r="E250">
-        <v>201</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F250">
         <is>
@@ -8042,12 +8042,12 @@
     <row r="251" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
@@ -8056,103 +8056,103 @@
         </is>
       </c>
       <c s="10" r="D251">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E251">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F251">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G251">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C252">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D252">
-        <v>44939</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E252">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F252">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G252">
-        <v>44937</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C253">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D253">
-        <v>44890</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E253">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F253">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G253">
-        <v>44827</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C254">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D254">
-        <v>44907</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E254">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F254">
         <is>
@@ -8160,30 +8160,30 @@
         </is>
       </c>
       <c s="12" r="G254">
-        <v>44846</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D255">
-        <v>44911</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E255">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F255">
         <is>
@@ -8191,80 +8191,80 @@
         </is>
       </c>
       <c s="12" r="G255">
-        <v>44845</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D256">
-        <v>44869</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E256">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G256">
-        <v>44812</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C257">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D257">
-        <v>44866</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E257">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G257">
-        <v>44803</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C258">
@@ -8273,41 +8273,41 @@
         </is>
       </c>
       <c s="10" r="D258">
-        <v>44856</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E258">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G258">
-        <v>44795</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C259">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D259">
-        <v>44815</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E259">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
@@ -8315,30 +8315,30 @@
         </is>
       </c>
       <c s="12" r="G259">
-        <v>44755</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D260">
-        <v>44802</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E260">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F260">
         <is>
@@ -8346,30 +8346,30 @@
         </is>
       </c>
       <c s="12" r="G260">
-        <v>44741</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C261">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D261">
-        <v>44865</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E261">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F261">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c s="12" r="G261">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="0">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c s="10" r="D262">
-        <v>44805</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E262">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F262">
         <is>
@@ -8414,74 +8414,74 @@
     <row r="263" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C263">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D263">
-        <v>44712</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E263">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F263">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G263">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C264">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D264">
-        <v>44600</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E264">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F264">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G264">
-        <v>44600</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C265">
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c s="10" r="D265">
-        <v>44652</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E265">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
@@ -8501,30 +8501,30 @@
         </is>
       </c>
       <c s="12" r="G265">
-        <v>44578</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C266">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D266">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E266">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c s="12" r="G266">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="0">
@@ -8555,7 +8555,7 @@
         <v>44620</v>
       </c>
       <c s="11" r="E267">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
@@ -8569,24 +8569,24 @@
     <row r="268" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C268">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D268">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E268">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8594,30 +8594,30 @@
         </is>
       </c>
       <c s="12" r="G268">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C269">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D269">
-        <v>44531</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E269">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
@@ -8625,30 +8625,30 @@
         </is>
       </c>
       <c s="12" r="G269">
-        <v>44470</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C270">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D270">
-        <v>44799</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E270">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c s="12" r="G270">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="0">
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c s="10" r="D271">
-        <v>44743</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E271">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c s="10" r="D272">
-        <v>44680</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E272">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44652</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E273">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
@@ -8769,10 +8769,10 @@
         </is>
       </c>
       <c s="10" r="D274">
-        <v>44575</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E274">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c s="10" r="D275">
-        <v>44512</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E275">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
@@ -8817,12 +8817,12 @@
     <row r="276" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C276">
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c s="10" r="D276">
-        <v>44469</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E276">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
@@ -8842,30 +8842,30 @@
         </is>
       </c>
       <c s="12" r="G276">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C277">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44482</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E277">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
@@ -8873,30 +8873,30 @@
         </is>
       </c>
       <c s="12" r="G277">
-        <v>44421</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C278">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E278">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c s="12" r="G278">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="0">
@@ -8915,7 +8915,7 @@
       </c>
       <c s="9" t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C279">
@@ -8927,7 +8927,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E279">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
@@ -8946,19 +8946,19 @@
       </c>
       <c s="9" t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C280">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D280">
         <v>44469</v>
       </c>
       <c s="11" r="E280">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8972,24 +8972,24 @@
     <row r="281" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C281">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D281">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E281">
-        <v>402</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
@@ -8997,30 +8997,30 @@
         </is>
       </c>
       <c s="12" r="G281">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C282">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D282">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E282">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
@@ -9028,18 +9028,18 @@
         </is>
       </c>
       <c s="12" r="G282">
-        <v>44383</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C283">
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c s="10" r="D283">
-        <v>44348</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E283">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
@@ -9059,18 +9059,18 @@
         </is>
       </c>
       <c s="12" r="G283">
-        <v>44308</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C284">
@@ -9079,49 +9079,49 @@
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44347</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E284">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G284">
-        <v>44291</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C285">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D285">
-        <v>44311</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E285">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G285">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="0">
@@ -9141,10 +9141,10 @@
         </is>
       </c>
       <c s="10" r="D286">
-        <v>44256</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E286">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
@@ -9158,32 +9158,32 @@
     <row r="287" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C287">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D287">
-        <v>44358</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E287">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G287">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="0">
@@ -9203,10 +9203,10 @@
         </is>
       </c>
       <c s="10" r="D288">
-        <v>44330</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E288">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c s="10" r="D289">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E289">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c s="10" r="D290">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E290">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
@@ -9282,12 +9282,12 @@
     <row r="291" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C291">
@@ -9299,7 +9299,7 @@
         <v>44288</v>
       </c>
       <c s="11" r="E291">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
@@ -9313,24 +9313,24 @@
     <row r="292" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C292">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D292">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E292">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F292">
         <is>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c s="12" r="G292">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="0">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44264</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E293">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F293">
         <is>
@@ -9375,24 +9375,24 @@
     <row r="294" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C294">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D294">
-        <v>44242</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E294">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F294">
         <is>
@@ -9400,100 +9400,100 @@
         </is>
       </c>
       <c s="12" r="G294">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C295">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D295">
-        <v>44270</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E295">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G295">
-        <v>44168</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C296">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D296">
-        <v>44214</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E296">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G296">
-        <v>44160</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C297">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D297">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E297">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G297">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="0">
@@ -9516,11 +9516,11 @@
         <v>44211</v>
       </c>
       <c s="11" r="E298">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G298">
@@ -9530,12 +9530,12 @@
     <row r="299" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C299">
@@ -9544,29 +9544,29 @@
         </is>
       </c>
       <c s="10" r="D299">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E299">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F299">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G299">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C300">
@@ -9575,69 +9575,69 @@
         </is>
       </c>
       <c s="10" r="D300">
-        <v>44214</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E300">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F300">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G300">
-        <v>44151</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C301">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D301">
-        <v>44186</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E301">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F301">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G301">
-        <v>44127</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C302">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D302">
-        <v>44104</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E302">
         <v>59</v>
@@ -9648,100 +9648,100 @@
         </is>
       </c>
       <c s="12" r="G302">
-        <v>44104</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C303">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D303">
-        <v>44197</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E303">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F303">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G303">
-        <v>44151</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">7241</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">SP+</t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C304">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Elgin</t>
         </is>
       </c>
       <c s="10" r="D304">
-        <v>43914</v>
+        <v>44197</v>
       </c>
       <c s="11" r="E304">
-        <v>89</v>
+        <v>229</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G304">
-        <v>44099</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">7218</t>
+          <t xml:space="preserve">7241</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
+          <t xml:space="preserve">SP+</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C305">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D305">
-        <v>43903</v>
+        <v>43914</v>
       </c>
       <c s="11" r="E305">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G305">
-        <v>44091</v>
+        <v>44099</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="0">
@@ -9752,19 +9752,19 @@
       </c>
       <c s="9" t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
+          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C306">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D306">
         <v>43903</v>
       </c>
       <c s="11" r="E306">
-        <v>358</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F306">
         <is>
@@ -9783,19 +9783,19 @@
       </c>
       <c s="9" t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">Sodexo - Medford SD</t>
+          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C307">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D307">
         <v>43903</v>
       </c>
       <c s="11" r="E307">
-        <v>111</v>
+        <v>358</v>
       </c>
       <c s="9" t="inlineStr" r="F307">
         <is>
@@ -9809,32 +9809,32 @@
     <row r="308" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">7217</t>
+          <t xml:space="preserve">7218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">PF Chang's</t>
+          <t xml:space="preserve">Sodexo - Medford SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C308">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D308">
-        <v>44092</v>
+        <v>43903</v>
       </c>
       <c s="11" r="E308">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F308">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G308">
-        <v>44092</v>
+        <v>44091</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="0">
@@ -9845,12 +9845,12 @@
       </c>
       <c s="9" t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">PF Chang's - Eugene</t>
+          <t xml:space="preserve">PF Chang's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C309">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D309">
@@ -9871,32 +9871,32 @@
     <row r="310" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">7215</t>
+          <t xml:space="preserve">7217</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Salem</t>
+          <t xml:space="preserve">PF Chang's - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D310">
-        <v>44137</v>
+        <v>44092</v>
       </c>
       <c s="11" r="E310">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F310">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G310">
-        <v>44077</v>
+        <v>44092</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="0">
@@ -9907,19 +9907,19 @@
       </c>
       <c s="9" t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Portland</t>
+          <t xml:space="preserve">LAGS Medical Center - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C311">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D311">
         <v>44137</v>
       </c>
       <c s="11" r="E311">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F311">
         <is>
@@ -9933,12 +9933,12 @@
     <row r="312" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">7211</t>
+          <t xml:space="preserve">7215</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">Bon Appetit</t>
+          <t xml:space="preserve">LAGS Medical Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C312">
@@ -9947,18 +9947,18 @@
         </is>
       </c>
       <c s="10" r="D312">
-        <v>44104</v>
+        <v>44137</v>
       </c>
       <c s="11" r="E312">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G312">
-        <v>44075</v>
+        <v>44077</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="0">
@@ -9981,11 +9981,11 @@
         <v>44104</v>
       </c>
       <c s="11" r="E313">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G313">
@@ -9995,24 +9995,24 @@
     <row r="314" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">7209</t>
+          <t xml:space="preserve">7211</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">Dave &amp; Buster's</t>
+          <t xml:space="preserve">Bon Appetit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D314">
-        <v>44143</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E314">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F314">
         <is>
@@ -10020,123 +10020,123 @@
         </is>
       </c>
       <c s="12" r="G314">
-        <v>44082</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">7207</t>
+          <t xml:space="preserve">7209</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">PGE - Boardman</t>
+          <t xml:space="preserve">Dave &amp; Buster's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
         <is>
-          <t xml:space="preserve">Boardman</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D315">
-        <v>44140</v>
+        <v>44143</v>
       </c>
       <c s="11" r="E315">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c s="9" t="inlineStr" r="F315">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G315">
-        <v>44075</v>
+        <v>44082</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">7199</t>
+          <t xml:space="preserve">7207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">LAIKA</t>
+          <t xml:space="preserve">PGE - Boardman</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C316">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Boardman</t>
         </is>
       </c>
       <c s="10" r="D316">
+        <v>44140</v>
+      </c>
+      <c s="11" r="E316">
+        <v>22</v>
+      </c>
+      <c s="9" t="inlineStr" r="F316">
+        <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G316">
         <v>44075</v>
-      </c>
-      <c s="11" r="E316">
-        <v>50</v>
-      </c>
-      <c s="9" t="inlineStr" r="F316">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G316">
-        <v>44057</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">7192</t>
+          <t xml:space="preserve">7199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">HMSHost</t>
+          <t xml:space="preserve">LAIKA</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C317">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D317">
-        <v>44119</v>
+        <v>44075</v>
       </c>
       <c s="11" r="E317">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F317">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G317">
-        <v>44054</v>
+        <v>44057</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">7186</t>
+          <t xml:space="preserve">7192</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">HMSHost</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C318">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D318">
-        <v>44124</v>
+        <v>44119</v>
       </c>
       <c s="11" r="E318">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F318">
         <is>
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c s="12" r="G318">
-        <v>44032</v>
+        <v>44054</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="0">
@@ -10155,19 +10155,19 @@
       </c>
       <c s="9" t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C319">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D319">
-        <v>44099</v>
+        <v>44124</v>
       </c>
       <c s="11" r="E319">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F319">
         <is>
@@ -10186,19 +10186,19 @@
       </c>
       <c s="9" t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C320">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D320">
         <v>44099</v>
       </c>
       <c s="11" r="E320">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F320">
         <is>
@@ -10212,24 +10212,24 @@
     <row r="321" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">7185</t>
+          <t xml:space="preserve">7186</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C321">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D321">
-        <v>44105</v>
+        <v>44099</v>
       </c>
       <c s="11" r="E321">
-        <v>277</v>
+        <v>355</v>
       </c>
       <c s="9" t="inlineStr" r="F321">
         <is>
@@ -10237,18 +10237,18 @@
         </is>
       </c>
       <c s="12" r="G321">
-        <v>44041</v>
+        <v>44032</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">7184</t>
+          <t xml:space="preserve">7185</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
+          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C322">
@@ -10257,29 +10257,29 @@
         </is>
       </c>
       <c s="10" r="D322">
-        <v>43910</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E322">
-        <v>70</v>
+        <v>277</v>
       </c>
       <c s="9" t="inlineStr" r="F322">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G322">
-        <v>44043</v>
+        <v>44041</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">7171</t>
+          <t xml:space="preserve">7184</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
+          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C323">
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c s="10" r="D323">
-        <v>44105</v>
+        <v>43910</v>
       </c>
       <c s="11" r="E323">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F323">
         <is>
@@ -10305,122 +10305,152 @@
     <row r="324" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7171</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C324">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D324"/>
-      <c s="13" t="str" r="E324"/>
+          <t xml:space="preserve">Portland</t>
+        </is>
+      </c>
+      <c s="10" r="D324">
+        <v>44105</v>
+      </c>
+      <c s="11" r="E324">
+        <v>193</v>
+      </c>
       <c s="9" t="inlineStr" r="F324">
         <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G324">
-        <v>44909</v>
+        <v>44043</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C325">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D325"/>
       <c s="13" t="str" r="E325"/>
       <c s="9" t="inlineStr" r="F325">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G325">
-        <v>45125</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C326">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">Mesa, AZ</t>
         </is>
       </c>
       <c s="9" t="str" r="D326"/>
       <c s="13" t="str" r="E326"/>
       <c s="9" t="inlineStr" r="F326">
         <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G326">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="327" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A327">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B327">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C327">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D327"/>
+      <c s="13" t="str" r="E327"/>
+      <c s="9" t="inlineStr" r="F327">
+        <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
-      <c s="12" r="G326">
+      <c s="12" r="G327">
         <v>45887</v>
       </c>
     </row>
-    <row r="327" ht="3.55" customHeight="0">
-      <c s="14" t="inlineStr" r="A327">
+    <row r="328" ht="3.6" customHeight="0">
+      <c s="14" t="inlineStr" r="A328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B327">
+      <c s="14" t="inlineStr" r="B328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C327">
+      <c s="14" t="inlineStr" r="C328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D327">
+      <c s="14" t="inlineStr" r="D328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E327">
+      <c s="14" t="inlineStr" r="E328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F327">
+      <c s="14" t="inlineStr" r="F328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G327">
+      <c s="14" t="inlineStr" r="G328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="328" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:A2"/>
@@ -10430,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/25/2026 5:48:16 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/25/2026 6:02:04 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/25/2016 to 8/25/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/26/2016 to 8/26/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/25/2026 6:02:04 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/26/2026 5:52:32 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/26/2026 5:52:32 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/26/2026 1:37:39 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/26/2026 1:37:39 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/26/2026 11:01:17 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/26/2016 to 8/26/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/27/2016 to 8/27/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/26/2026 11:01:17 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/27/2026 2:47:47 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/27/2016 to 8/27/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/28/2016 to 8/28/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/27/2026 2:47:47 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/28/2026 12:55:06 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/28/2026 12:55:06 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/28/2026 3:04:18 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/28/2026 3:04:18 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/28/2026 10:02:08 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/28/2016 to 8/28/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/29/2016 to 8/29/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/28/2026 10:02:08 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/29/2026 9:28:22 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/29/2026 9:28:22 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/29/2026 7:35:12 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/29/2016 to 8/29/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/30/2016 to 8/30/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/29/2026 7:35:12 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/30/2026 9:04:37 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/30/2026 9:04:37 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/30/2026 7:31:42 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/30/2016 to 8/30/2026</t>
+          <t xml:space="preserve">WARNs Received: 8/31/2016 to 8/31/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/30/2026 7:31:42 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/31/2026 11:46:46 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -385,63 +385,63 @@
     <row r="4" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">9588</t>
+          <t xml:space="preserve">9590</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
+          <t xml:space="preserve">J.R. Johnson, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D4">
-        <v>46314</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E4">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c s="9" t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G4">
-        <v>46254</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">9556</t>
+          <t xml:space="preserve">9588</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">JeniusBank</t>
+          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">New York, NY</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D5">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c s="11" r="E5">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c s="9" t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G5">
-        <v>46244</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="0">
@@ -452,19 +452,19 @@
       </c>
       <c s="9" t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">JeniusBank</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">New York, NY</t>
         </is>
       </c>
       <c s="10" r="D6">
         <v>46304</v>
       </c>
       <c s="11" r="E6">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F6">
         <is>
@@ -478,21 +478,21 @@
     <row r="7" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">9555</t>
+          <t xml:space="preserve">9556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">Bowtech, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D7">
-        <v>46446</v>
+        <v>46304</v>
       </c>
       <c s="11" r="E7">
         <v>1</v>
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c s="12" r="G7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="0">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c s="10" r="D8">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c s="11" r="E8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F8">
         <is>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c s="10" r="D9">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E9">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F9">
         <is>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c s="10" r="D10">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F10">
         <is>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c s="10" r="D11">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E11">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F11">
         <is>
@@ -633,24 +633,24 @@
     <row r="12" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">9553</t>
+          <t xml:space="preserve">9555</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
+          <t xml:space="preserve">Bowtech, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D12">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E12">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F12">
         <is>
@@ -658,34 +658,34 @@
         </is>
       </c>
       <c s="12" r="G12">
-        <v>46237</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9553</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">Avamere Health Services, LLC</t>
+          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">Tigard</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D13">
-        <v>46266</v>
+        <v>46298</v>
       </c>
       <c s="11" r="E13">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F13">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G13">
@@ -695,94 +695,94 @@
     <row r="14" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">9549</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
+          <t xml:space="preserve">Avamere Health Services, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tigard</t>
         </is>
       </c>
       <c s="10" r="D14">
-        <v>46325</v>
+        <v>46266</v>
       </c>
       <c s="11" r="E14">
-        <v>387</v>
+        <v>129</v>
       </c>
       <c s="9" t="inlineStr" r="F14">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G14">
-        <v>46233</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">9534</t>
+          <t xml:space="preserve">9549</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
+          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D15">
-        <v>46262</v>
+        <v>46325</v>
       </c>
       <c s="11" r="E15">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c s="9" t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G15">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">Adventist Health Tillamook</t>
+          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D16">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c s="11" r="E16">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c s="9" t="inlineStr" r="F16">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G16">
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="0">
@@ -793,19 +793,19 @@
       </c>
       <c s="9" t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">Adventist Health Portland</t>
+          <t xml:space="preserve">Adventist Health Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C17">
         <is>
-          <t xml:space="preserve">Portland, </t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D17">
         <v>46206</v>
       </c>
       <c s="11" r="E17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F17">
         <is>
@@ -824,19 +824,19 @@
       </c>
       <c s="9" t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
+          <t xml:space="preserve">Adventist Health Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">The Dalles</t>
+          <t xml:space="preserve">Portland, </t>
         </is>
       </c>
       <c s="10" r="D18">
         <v>46206</v>
       </c>
       <c s="11" r="E18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F18">
         <is>
@@ -850,32 +850,32 @@
     <row r="19" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">PacificSource</t>
+          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">The Dalles</t>
         </is>
       </c>
       <c s="10" r="D19">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E19">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G19">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="0">
@@ -886,23 +886,23 @@
       </c>
       <c s="9" t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">PacificSource - Bend</t>
+          <t xml:space="preserve">PacificSource</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D20">
         <v>46234</v>
       </c>
       <c s="11" r="E20">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G20">
@@ -917,19 +917,19 @@
       </c>
       <c s="9" t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">PacificSource - Portland</t>
+          <t xml:space="preserve">PacificSource - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D21">
         <v>46234</v>
       </c>
       <c s="11" r="E21">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F21">
         <is>
@@ -948,12 +948,12 @@
       </c>
       <c s="9" t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">PacificSource - Salem</t>
+          <t xml:space="preserve">PacificSource - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D22">
@@ -979,19 +979,19 @@
       </c>
       <c s="9" t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">PacificSource Hood River</t>
+          <t xml:space="preserve">PacificSource - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D23">
         <v>46234</v>
       </c>
       <c s="11" r="E23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F23">
         <is>
@@ -1005,63 +1005,63 @@
     <row r="24" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">9511</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
+          <t xml:space="preserve">PacificSource Hood River</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D24">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E24">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G24">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9511</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D25">
-        <v>46234</v>
+        <v>46228</v>
       </c>
       <c s="11" r="E25">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G25">
-        <v>46160</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="0">
@@ -1072,19 +1072,19 @@
       </c>
       <c s="9" t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D26">
         <v>46234</v>
       </c>
       <c s="11" r="E26">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F26">
         <is>
@@ -1103,19 +1103,19 @@
       </c>
       <c s="9" t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D27">
         <v>46234</v>
       </c>
       <c s="11" r="E27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F27">
         <is>
@@ -1134,19 +1134,19 @@
       </c>
       <c s="9" t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D28">
         <v>46234</v>
       </c>
       <c s="11" r="E28">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F28">
         <is>
@@ -1165,19 +1165,19 @@
       </c>
       <c s="9" t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D29">
         <v>46234</v>
       </c>
       <c s="11" r="E29">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c s="9" t="inlineStr" r="F29">
         <is>
@@ -1191,86 +1191,86 @@
     <row r="30" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D30">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E30">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G30">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D31">
-        <v>46201</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E31">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G31">
-        <v>46141</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D32">
-        <v>46295</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E32">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F32">
         <is>
@@ -1278,49 +1278,49 @@
         </is>
       </c>
       <c s="12" r="G32">
-        <v>46114</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D33">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E33">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G33">
-        <v>46108</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
@@ -1329,18 +1329,18 @@
         </is>
       </c>
       <c s="10" r="D34">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E34">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F34">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G34">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="0">
@@ -1351,7 +1351,7 @@
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
@@ -1377,24 +1377,24 @@
     <row r="36" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D36">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E36">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F36">
         <is>
@@ -1402,38 +1402,38 @@
         </is>
       </c>
       <c s="12" r="G36">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D37">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E37">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F37">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G37">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="0">
@@ -1444,19 +1444,19 @@
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D38">
         <v>46131</v>
       </c>
       <c s="11" r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F38">
         <is>
@@ -1470,63 +1470,63 @@
     <row r="39" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D39">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E39">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G39">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D40">
         <v>46117</v>
       </c>
       <c s="11" r="E40">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F40">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G40">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="0">
@@ -1537,19 +1537,19 @@
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D41">
         <v>46117</v>
       </c>
       <c s="11" r="E41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F41">
         <is>
@@ -1568,12 +1568,12 @@
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D42">
@@ -1599,12 +1599,12 @@
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D43">
@@ -1630,12 +1630,12 @@
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D44">
@@ -1661,12 +1661,12 @@
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D45">
@@ -1692,12 +1692,12 @@
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D46">
@@ -1723,12 +1723,12 @@
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D47">
@@ -1754,7 +1754,7 @@
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
@@ -1785,7 +1785,7 @@
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
@@ -1816,12 +1816,12 @@
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D50">
@@ -1847,12 +1847,12 @@
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D51">
@@ -1878,12 +1878,12 @@
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D52">
@@ -1909,7 +1909,7 @@
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
@@ -1940,19 +1940,19 @@
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D54">
         <v>46117</v>
       </c>
       <c s="11" r="E54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F54">
         <is>
@@ -1971,19 +1971,19 @@
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D55">
         <v>46117</v>
       </c>
       <c s="11" r="E55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F55">
         <is>
@@ -2002,19 +2002,19 @@
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D56">
         <v>46117</v>
       </c>
       <c s="11" r="E56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F56">
         <is>
@@ -2033,12 +2033,12 @@
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D57">
@@ -2064,12 +2064,12 @@
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D58">
@@ -2090,24 +2090,24 @@
     <row r="59" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D59">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E59">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F59">
         <is>
@@ -2126,19 +2126,19 @@
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D60">
         <v>46112</v>
       </c>
       <c s="11" r="E60">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F60">
         <is>
@@ -2157,19 +2157,19 @@
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D61">
         <v>46112</v>
       </c>
       <c s="11" r="E61">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F61">
         <is>
@@ -2183,24 +2183,24 @@
     <row r="62" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D62">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E62">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F62">
         <is>
@@ -2208,30 +2208,30 @@
         </is>
       </c>
       <c s="12" r="G62">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D63">
-        <v>46142</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E63">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F63">
         <is>
@@ -2239,30 +2239,30 @@
         </is>
       </c>
       <c s="12" r="G63">
-        <v>46020</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D64">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E64">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F64">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c s="12" r="G64">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="0">
@@ -2281,7 +2281,7 @@
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
@@ -2293,7 +2293,7 @@
         <v>46014</v>
       </c>
       <c s="11" r="E65">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F65">
         <is>
@@ -2312,19 +2312,19 @@
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D66">
         <v>46014</v>
       </c>
       <c s="11" r="E66">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F66">
         <is>
@@ -2338,43 +2338,43 @@
     <row r="67" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D67">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E67">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F67">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G67">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
@@ -2383,29 +2383,29 @@
         </is>
       </c>
       <c s="10" r="D68">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E68">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F68">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G68">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c s="10" r="D69">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E69">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F69">
         <is>
@@ -2431,63 +2431,63 @@
     <row r="70" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D70">
         <v>46054</v>
       </c>
       <c s="11" r="E70">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F70">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G70">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D71">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E71">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F71">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G71">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="0">
@@ -2498,19 +2498,19 @@
       </c>
       <c s="9" t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C72">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D72">
         <v>45916</v>
       </c>
       <c s="11" r="E72">
-        <v>510</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c s="9" t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C73">
@@ -2541,7 +2541,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E73">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c s="9" t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C74">
@@ -2572,7 +2572,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E74">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F74">
         <is>
@@ -2586,24 +2586,24 @@
     <row r="75" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D75">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E75">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F75">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c s="12" r="G75">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="0">
@@ -2622,23 +2622,23 @@
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D76">
         <v>46022</v>
       </c>
       <c s="11" r="E76">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F76">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G76">
@@ -2653,19 +2653,19 @@
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D77">
         <v>46022</v>
       </c>
       <c s="11" r="E77">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
@@ -2684,19 +2684,19 @@
       </c>
       <c s="9" t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C78">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D78">
         <v>46022</v>
       </c>
       <c s="11" r="E78">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
@@ -2715,19 +2715,19 @@
       </c>
       <c s="9" t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C79">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D79">
         <v>46022</v>
       </c>
       <c s="11" r="E79">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
@@ -2741,55 +2741,55 @@
     <row r="80" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C80">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D80">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E80">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G80">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D81">
         <v>46017</v>
       </c>
       <c s="11" r="E81">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
@@ -2803,28 +2803,28 @@
     <row r="82" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C82">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D82">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E82">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G82">
@@ -2848,14 +2848,14 @@
         </is>
       </c>
       <c s="10" r="D83">
-        <v>46017</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E83">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G83">
@@ -2865,86 +2865,86 @@
     <row r="84" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D84">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E84">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G84">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D85">
-        <v>46022</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E85">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G85">
-        <v>45917</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D86">
-        <v>45978</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E86">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
@@ -2952,18 +2952,18 @@
         </is>
       </c>
       <c s="12" r="G86">
-        <v>45943</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c s="10" r="D87">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E87">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
@@ -2983,38 +2983,38 @@
         </is>
       </c>
       <c s="12" r="G87">
-        <v>45930</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D88">
-        <v>45940</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E88">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G88">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="0">
@@ -3034,14 +3034,14 @@
         </is>
       </c>
       <c s="10" r="D89">
-        <v>45925</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E89">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G89">
@@ -3051,24 +3051,24 @@
     <row r="90" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C90">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D90">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E90">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
@@ -3076,34 +3076,34 @@
         </is>
       </c>
       <c s="12" r="G90">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C91">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D91">
         <v>45976</v>
       </c>
       <c s="11" r="E91">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G91">
@@ -3113,63 +3113,63 @@
     <row r="92" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D92">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E92">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G92">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D93">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E93">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G93">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="0">
@@ -3180,7 +3180,7 @@
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
@@ -3192,7 +3192,7 @@
         <v>45949</v>
       </c>
       <c s="11" r="E94">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
@@ -3206,12 +3206,12 @@
     <row r="95" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C95">
@@ -3220,41 +3220,41 @@
         </is>
       </c>
       <c s="10" r="D95">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E95">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G95">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D96">
-        <v>45874</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E96">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
@@ -3262,18 +3262,18 @@
         </is>
       </c>
       <c s="12" r="G96">
-        <v>45867</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C97">
@@ -3282,49 +3282,49 @@
         </is>
       </c>
       <c s="10" r="D97">
-        <v>45920</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E97">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G97">
-        <v>45854</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D98">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E98">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G98">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="0">
@@ -3335,19 +3335,19 @@
       </c>
       <c s="9" t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D99">
         <v>45912</v>
       </c>
       <c s="11" r="E99">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
@@ -3361,63 +3361,63 @@
     <row r="100" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C100">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D100">
         <v>45912</v>
       </c>
       <c s="11" r="E100">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G100">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C101">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D101">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E101">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G101">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="0">
@@ -3428,19 +3428,19 @@
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D102">
         <v>45853</v>
       </c>
       <c s="11" r="E102">
-        <v>1544</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
@@ -3471,7 +3471,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E103">
-        <v>174</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
@@ -3490,7 +3490,7 @@
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
@@ -3502,7 +3502,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E104">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
@@ -3516,86 +3516,86 @@
     <row r="105" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D105">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E105">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G105">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D106">
-        <v>45901</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E106">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G106">
-        <v>45839</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D107">
-        <v>45982</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E107">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c s="12" r="G107">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="0">
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c s="10" r="D108">
-        <v>45968</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E108">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c s="10" r="D109">
-        <v>45894</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E109">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
@@ -3671,24 +3671,24 @@
     <row r="110" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D110">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E110">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
@@ -3696,30 +3696,30 @@
         </is>
       </c>
       <c s="12" r="G110">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D111">
         <v>45838</v>
       </c>
       <c s="11" r="E111">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
@@ -3733,94 +3733,94 @@
     <row r="112" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D112">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E112">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G112">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D113">
-        <v>45807</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E113">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G113">
-        <v>45804</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C114">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D114">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E114">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G114">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="0">
@@ -3831,19 +3831,19 @@
       </c>
       <c s="9" t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C115">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D115">
         <v>45866</v>
       </c>
       <c s="11" r="E115">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
@@ -3857,55 +3857,55 @@
     <row r="116" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D116">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E116">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G116">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D117">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E117">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
@@ -3913,85 +3913,85 @@
         </is>
       </c>
       <c s="12" r="G117">
-        <v>45778</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D118">
-        <v>45769</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E118">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G118">
-        <v>45769</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D119">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E119">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G119">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D120">
@@ -4002,69 +4002,69 @@
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G120">
-        <v>45763</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D121">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E121">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G121">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D122">
-        <v>45810</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E122">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G122">
@@ -4074,43 +4074,43 @@
     <row r="123" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D123">
-        <v>45808</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E123">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G123">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
@@ -4119,103 +4119,103 @@
         </is>
       </c>
       <c s="10" r="D124">
-        <v>45834</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E124">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G124">
-        <v>45774</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D125">
-        <v>45838</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E125">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G125">
-        <v>45744</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C126">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D126">
-        <v>45706</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E126">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G126">
-        <v>45706</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D127">
-        <v>45734</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E127">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
@@ -4223,38 +4223,38 @@
         </is>
       </c>
       <c s="12" r="G127">
-        <v>45666</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D128">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E128">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G128">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="0">
@@ -4265,19 +4265,19 @@
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D129">
         <v>45707</v>
       </c>
       <c s="11" r="E129">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
@@ -4291,63 +4291,63 @@
     <row r="130" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D130">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E130">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G130">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D131">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E131">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F131">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G131">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="0">
@@ -4358,19 +4358,19 @@
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D132">
         <v>45696</v>
       </c>
       <c s="11" r="E132">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F132">
         <is>
@@ -4384,86 +4384,86 @@
     <row r="133" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D133">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E133">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F133">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G133">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D134">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E134">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F134">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G134">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D135">
         <v>45931</v>
       </c>
       <c s="11" r="E135">
-        <v>221</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
@@ -4477,43 +4477,43 @@
     <row r="136" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D136">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E136">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G136">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
@@ -4522,18 +4522,18 @@
         </is>
       </c>
       <c s="10" r="D137">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E137">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G137">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="0">
@@ -4544,19 +4544,19 @@
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D138">
         <v>45726</v>
       </c>
       <c s="11" r="E138">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
@@ -4575,19 +4575,19 @@
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D139">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E139">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
@@ -4606,19 +4606,19 @@
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D140">
         <v>45725</v>
       </c>
       <c s="11" r="E140">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
@@ -4637,19 +4637,19 @@
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D141">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E141">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F141">
         <is>
@@ -4668,12 +4668,12 @@
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D142">
@@ -4699,12 +4699,12 @@
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D143">
@@ -4730,19 +4730,19 @@
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D144">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E144">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
@@ -4761,19 +4761,19 @@
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D145">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E145">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c s="10" r="D146">
-        <v>45703</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E146">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
@@ -4823,19 +4823,19 @@
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D147">
-        <v>45690</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E147">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
@@ -4849,12 +4849,12 @@
     <row r="148" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
@@ -4863,72 +4863,72 @@
         </is>
       </c>
       <c s="10" r="D148">
-        <v>45657</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E148">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F148">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G148">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D149">
-        <v>45640</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E149">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F149">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G149">
-        <v>45580</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D150">
-        <v>45657</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E150">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F150">
         <is>
@@ -4936,100 +4936,100 @@
         </is>
       </c>
       <c s="12" r="G150">
-        <v>45595</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D151">
-        <v>45584</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E151">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F151">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G151">
-        <v>45584</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C152">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D152">
-        <v>45664</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E152">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F152">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G152">
-        <v>45582</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C153">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D153">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E153">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G153">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="0">
@@ -5040,19 +5040,19 @@
       </c>
       <c s="9" t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C154">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D154">
         <v>45611</v>
       </c>
       <c s="11" r="E154">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F154">
         <is>
@@ -5071,7 +5071,7 @@
       </c>
       <c s="9" t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C155">
@@ -5083,7 +5083,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E155">
-        <v>124</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
@@ -5102,7 +5102,7 @@
       </c>
       <c s="9" t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C156">
@@ -5114,7 +5114,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E156">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
@@ -5128,28 +5128,28 @@
     <row r="157" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C157">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D157">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E157">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G157">
@@ -5159,24 +5159,24 @@
     <row r="158" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D158">
-        <v>45621</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E158">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
@@ -5184,38 +5184,38 @@
         </is>
       </c>
       <c s="12" r="G158">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D159">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E159">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F159">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G159">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="0">
@@ -5226,23 +5226,23 @@
       </c>
       <c s="9" t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C160">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D160">
         <v>45544</v>
       </c>
       <c s="11" r="E160">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F160">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G160">
@@ -5252,55 +5252,55 @@
     <row r="161" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C161">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D161">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E161">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F161">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G161">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C162">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D162">
-        <v>45654</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E162">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c s="12" r="G162">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="0">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c s="10" r="D163">
-        <v>45612</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E163">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
@@ -5359,14 +5359,14 @@
         </is>
       </c>
       <c s="10" r="D164">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E164">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G164">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c s="10" r="D165">
-        <v>45569</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E165">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
@@ -5421,14 +5421,14 @@
         </is>
       </c>
       <c s="10" r="D166">
-        <v>45555</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E166">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G166">
@@ -5438,24 +5438,24 @@
     <row r="167" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C167">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D167">
-        <v>45653</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E167">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c s="12" r="G167">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="0">
@@ -5483,14 +5483,14 @@
         </is>
       </c>
       <c s="10" r="D168">
-        <v>45505</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E168">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G168">
@@ -5500,24 +5500,24 @@
     <row r="169" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C169">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D169">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E169">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c s="12" r="G169">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B170">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c s="10" r="D170">
-        <v>45513</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E170">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
@@ -5556,18 +5556,18 @@
         </is>
       </c>
       <c s="12" r="G170">
-        <v>45450</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C171">
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c s="10" r="D171">
-        <v>45504</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E171">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
@@ -5587,30 +5587,30 @@
         </is>
       </c>
       <c s="12" r="G171">
-        <v>45441</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C172">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D172">
-        <v>46229</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E172">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c s="12" r="G172">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="0">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c s="10" r="D173">
-        <v>45688</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E173">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c s="10" r="D174">
-        <v>45506</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E174">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
@@ -5686,32 +5686,32 @@
     <row r="175" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C175">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45483</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E175">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G175">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="0">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45401</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E176">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c s="10" r="D177">
-        <v>45366</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
@@ -5779,43 +5779,43 @@
     <row r="178" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C178">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D178">
-        <v>45473</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E178">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G178">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C179">
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c s="10" r="D179">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E179">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
@@ -5835,111 +5835,111 @@
         </is>
       </c>
       <c s="12" r="G179">
-        <v>45404</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C180">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D180">
         <v>45471</v>
       </c>
       <c s="11" r="E180">
-        <v>740</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G180">
-        <v>45401</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C181">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D181">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E181">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G181">
-        <v>45384</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C182">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D182">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E182">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G182">
-        <v>45380</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C183">
@@ -5948,134 +5948,134 @@
         </is>
       </c>
       <c s="10" r="D183">
-        <v>45439</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E183">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G183">
-        <v>45379</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C184">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D184">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E184">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G184">
-        <v>45372</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C185">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D185">
-        <v>45433</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E185">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F185">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G185">
-        <v>45373</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C186">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D186">
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E186">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F186">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G186">
-        <v>45358</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C187">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D187">
-        <v>45352</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E187">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F187">
         <is>
@@ -6083,18 +6083,18 @@
         </is>
       </c>
       <c s="12" r="G187">
-        <v>45345</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C188">
@@ -6103,41 +6103,41 @@
         </is>
       </c>
       <c s="10" r="D188">
-        <v>45401</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E188">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G188">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D189">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E189">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c s="12" r="G189">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="0">
@@ -6156,7 +6156,7 @@
       </c>
       <c s="9" t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C190">
@@ -6168,7 +6168,7 @@
         <v>45337</v>
       </c>
       <c s="11" r="E190">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
@@ -6182,24 +6182,24 @@
     <row r="191" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C191">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D191">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E191">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
@@ -6207,34 +6207,34 @@
         </is>
       </c>
       <c s="12" r="G191">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C192">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D192">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E192">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G192">
@@ -6249,19 +6249,19 @@
       </c>
       <c s="9" t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C193">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D193">
         <v>45382</v>
       </c>
       <c s="11" r="E193">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
@@ -6280,19 +6280,19 @@
       </c>
       <c s="9" t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C194">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D194">
         <v>45382</v>
       </c>
       <c s="11" r="E194">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
@@ -6311,7 +6311,7 @@
       </c>
       <c s="9" t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C195">
@@ -6323,7 +6323,7 @@
         <v>45382</v>
       </c>
       <c s="11" r="E195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F195">
         <is>
@@ -6342,12 +6342,12 @@
       </c>
       <c s="9" t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C196">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D196">
@@ -6368,32 +6368,32 @@
     <row r="197" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C197">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D197">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E197">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G197">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="0">
@@ -6404,23 +6404,23 @@
       </c>
       <c s="9" t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C198">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D198">
         <v>45366</v>
       </c>
       <c s="11" r="E198">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G198">
@@ -6430,55 +6430,55 @@
     <row r="199" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C199">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D199">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E199">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G199">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D200">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E200">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c s="12" r="G200">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="0">
@@ -6497,19 +6497,19 @@
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D201">
         <v>45275</v>
       </c>
       <c s="11" r="E201">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
@@ -6528,19 +6528,19 @@
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D202">
         <v>45275</v>
       </c>
       <c s="11" r="E202">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F202">
         <is>
@@ -6559,19 +6559,19 @@
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D203">
         <v>45275</v>
       </c>
       <c s="11" r="E203">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F203">
         <is>
@@ -6585,24 +6585,24 @@
     <row r="204" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D204">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E204">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F204">
         <is>
@@ -6610,30 +6610,30 @@
         </is>
       </c>
       <c s="12" r="G204">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C205">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D205">
-        <v>45294</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E205">
-        <v>136</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F205">
         <is>
@@ -6641,30 +6641,30 @@
         </is>
       </c>
       <c s="12" r="G205">
-        <v>45217</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C206">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D206">
-        <v>45473</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E206">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F206">
         <is>
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c s="12" r="G206">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="0">
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c s="10" r="D207">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E207">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F207">
         <is>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c s="10" r="D208">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E208">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F208">
         <is>
@@ -6740,24 +6740,24 @@
     <row r="209" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D209">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E209">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F209">
         <is>
@@ -6765,18 +6765,18 @@
         </is>
       </c>
       <c s="12" r="G209">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C210">
@@ -6788,7 +6788,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E210">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F210">
         <is>
@@ -6802,12 +6802,12 @@
     <row r="211" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C211">
@@ -6819,7 +6819,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E211">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F211">
         <is>
@@ -6833,24 +6833,24 @@
     <row r="212" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C212">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D212">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E212">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F212">
         <is>
@@ -6858,61 +6858,61 @@
         </is>
       </c>
       <c s="12" r="G212">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C213">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D213">
-        <v>45237</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E213">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F213">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G213">
-        <v>45176</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C214">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D214">
-        <v>45387</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E214">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F214">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c s="12" r="G214">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="0">
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c s="10" r="D215">
-        <v>45317</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E215">
         <v>2</v>
@@ -6971,14 +6971,14 @@
         </is>
       </c>
       <c s="10" r="D216">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E216">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G216">
@@ -6993,7 +6993,7 @@
       </c>
       <c s="9" t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C217">
@@ -7005,11 +7005,11 @@
         <v>45303</v>
       </c>
       <c s="11" r="E217">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G217">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c s="10" r="D218">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E218">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7055,7 +7055,7 @@
       </c>
       <c s="9" t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C219">
@@ -7067,7 +7067,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E219">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
@@ -7095,10 +7095,10 @@
         </is>
       </c>
       <c s="10" r="D220">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E220">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F220">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c s="10" r="D221">
-        <v>45247</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E221">
         <v>1</v>
@@ -7157,14 +7157,14 @@
         </is>
       </c>
       <c s="10" r="D222">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E222">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F222">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G222">
@@ -7179,7 +7179,7 @@
       </c>
       <c s="9" t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C223">
@@ -7191,7 +7191,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E223">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F223">
         <is>
@@ -7205,86 +7205,86 @@
     <row r="224" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C224">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D224">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E224">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G224">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C225">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D225">
-        <v>45199</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E225">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G225">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C226">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D226">
-        <v>45213</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E226">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
@@ -7298,24 +7298,24 @@
     <row r="227" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C227">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D227">
-        <v>45283</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E227">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
@@ -7323,7 +7323,7 @@
         </is>
       </c>
       <c s="12" r="G227">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="0">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c s="10" r="D228">
-        <v>45192</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E228">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F228">
         <is>
@@ -7360,24 +7360,24 @@
     <row r="229" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C229">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D229">
-        <v>45137</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E229">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F229">
         <is>
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c s="12" r="G229">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="0">
@@ -7396,19 +7396,19 @@
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D230">
-        <v>45107</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E230">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
@@ -7422,32 +7422,32 @@
     <row r="231" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D231">
-        <v>45233</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E231">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G231">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="0">
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c s="10" r="D232">
-        <v>45205</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E232">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F232">
         <is>
@@ -7484,24 +7484,24 @@
     <row r="233" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D233">
-        <v>45175</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E233">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F233">
         <is>
@@ -7509,30 +7509,30 @@
         </is>
       </c>
       <c s="12" r="G233">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C234">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D234">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E234">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F234">
         <is>
@@ -7540,123 +7540,123 @@
         </is>
       </c>
       <c s="12" r="G234">
-        <v>45091</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C235">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D235">
-        <v>45128</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E235">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F235">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G235">
-        <v>45090</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C236">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D236">
-        <v>45170</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E236">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F236">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G236">
-        <v>45085</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D237">
-        <v>45106</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E237">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F237">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G237">
-        <v>45083</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C238">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45107</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E238">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F238">
         <is>
@@ -7664,30 +7664,30 @@
         </is>
       </c>
       <c s="12" r="G238">
-        <v>45070</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45115</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E239">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F239">
         <is>
@@ -7695,61 +7695,61 @@
         </is>
       </c>
       <c s="12" r="G239">
-        <v>45055</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D240">
-        <v>45105</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E240">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G240">
-        <v>45044</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D241">
-        <v>45135</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E241">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
@@ -7757,30 +7757,30 @@
         </is>
       </c>
       <c s="12" r="G241">
-        <v>45041</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D242">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E242">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F242">
         <is>
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c s="12" r="G242">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="0">
@@ -7799,12 +7799,12 @@
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D243">
@@ -7830,12 +7830,12 @@
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D244">
@@ -7861,12 +7861,12 @@
       </c>
       <c s="9" t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C245">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D245">
@@ -7892,12 +7892,12 @@
       </c>
       <c s="9" t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C246">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D246">
@@ -7918,86 +7918,86 @@
     <row r="247" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E247">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G247">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D248">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E248">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G248">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C249">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D249">
-        <v>45058</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E249">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F249">
         <is>
@@ -8011,24 +8011,24 @@
     <row r="250" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C250">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D250">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E250">
-        <v>379</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F250">
         <is>
@@ -8036,30 +8036,30 @@
         </is>
       </c>
       <c s="12" r="G250">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D251">
         <v>45079</v>
       </c>
       <c s="11" r="E251">
-        <v>201</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F251">
         <is>
@@ -8073,12 +8073,12 @@
     <row r="252" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C252">
@@ -8087,103 +8087,103 @@
         </is>
       </c>
       <c s="10" r="D252">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E252">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F252">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G252">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C253">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D253">
-        <v>44939</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E253">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F253">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G253">
-        <v>44937</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C254">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D254">
-        <v>44890</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E254">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F254">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G254">
-        <v>44827</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D255">
-        <v>44907</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E255">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F255">
         <is>
@@ -8191,30 +8191,30 @@
         </is>
       </c>
       <c s="12" r="G255">
-        <v>44846</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D256">
-        <v>44911</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E256">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
@@ -8222,80 +8222,80 @@
         </is>
       </c>
       <c s="12" r="G256">
-        <v>44845</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C257">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D257">
-        <v>44869</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E257">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G257">
-        <v>44812</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C258">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D258">
-        <v>44866</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E258">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G258">
-        <v>44803</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C259">
@@ -8304,41 +8304,41 @@
         </is>
       </c>
       <c s="10" r="D259">
-        <v>44856</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E259">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G259">
-        <v>44795</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D260">
-        <v>44815</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E260">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F260">
         <is>
@@ -8346,30 +8346,30 @@
         </is>
       </c>
       <c s="12" r="G260">
-        <v>44755</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C261">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D261">
-        <v>44802</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E261">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F261">
         <is>
@@ -8377,30 +8377,30 @@
         </is>
       </c>
       <c s="12" r="G261">
-        <v>44741</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C262">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D262">
-        <v>44865</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E262">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F262">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c s="12" r="G262">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="0">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c s="10" r="D263">
-        <v>44805</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E263">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F263">
         <is>
@@ -8445,74 +8445,74 @@
     <row r="264" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C264">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D264">
-        <v>44712</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E264">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F264">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G264">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C265">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D265">
-        <v>44600</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E265">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G265">
-        <v>44600</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C266">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c s="10" r="D266">
-        <v>44652</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E266">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
@@ -8532,30 +8532,30 @@
         </is>
       </c>
       <c s="12" r="G266">
-        <v>44578</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C267">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D267">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E267">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c s="12" r="G267">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="0">
@@ -8586,7 +8586,7 @@
         <v>44620</v>
       </c>
       <c s="11" r="E268">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8600,24 +8600,24 @@
     <row r="269" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C269">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D269">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E269">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
@@ -8625,30 +8625,30 @@
         </is>
       </c>
       <c s="12" r="G269">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C270">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D270">
-        <v>44531</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E270">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
@@ -8656,30 +8656,30 @@
         </is>
       </c>
       <c s="12" r="G270">
-        <v>44470</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C271">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D271">
-        <v>44799</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E271">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c s="12" r="G271">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="0">
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c s="10" r="D272">
-        <v>44743</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E272">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44680</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E273">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
@@ -8769,10 +8769,10 @@
         </is>
       </c>
       <c s="10" r="D274">
-        <v>44652</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E274">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c s="10" r="D275">
-        <v>44575</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E275">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c s="10" r="D276">
-        <v>44512</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E276">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
@@ -8848,12 +8848,12 @@
     <row r="277" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C277">
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44469</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E277">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
@@ -8873,30 +8873,30 @@
         </is>
       </c>
       <c s="12" r="G277">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C278">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44482</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E278">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
@@ -8904,30 +8904,30 @@
         </is>
       </c>
       <c s="12" r="G278">
-        <v>44421</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C279">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D279">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E279">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c s="12" r="G279">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="0">
@@ -8946,7 +8946,7 @@
       </c>
       <c s="9" t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C280">
@@ -8958,7 +8958,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E280">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8977,19 +8977,19 @@
       </c>
       <c s="9" t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C281">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D281">
         <v>44469</v>
       </c>
       <c s="11" r="E281">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
@@ -9003,24 +9003,24 @@
     <row r="282" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C282">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D282">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E282">
-        <v>402</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
@@ -9028,30 +9028,30 @@
         </is>
       </c>
       <c s="12" r="G282">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C283">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D283">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E283">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
@@ -9059,18 +9059,18 @@
         </is>
       </c>
       <c s="12" r="G283">
-        <v>44383</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C284">
@@ -9079,10 +9079,10 @@
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44348</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E284">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
@@ -9090,18 +9090,18 @@
         </is>
       </c>
       <c s="12" r="G284">
-        <v>44308</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C285">
@@ -9110,49 +9110,49 @@
         </is>
       </c>
       <c s="10" r="D285">
-        <v>44347</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E285">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G285">
-        <v>44291</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C286">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D286">
-        <v>44311</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E286">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G286">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="0">
@@ -9172,10 +9172,10 @@
         </is>
       </c>
       <c s="10" r="D287">
-        <v>44256</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E287">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
@@ -9189,32 +9189,32 @@
     <row r="288" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C288">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D288">
-        <v>44358</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E288">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G288">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="0">
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c s="10" r="D289">
-        <v>44330</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E289">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c s="10" r="D290">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E290">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c s="10" r="D291">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E291">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
@@ -9313,12 +9313,12 @@
     <row r="292" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C292">
@@ -9330,7 +9330,7 @@
         <v>44288</v>
       </c>
       <c s="11" r="E292">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F292">
         <is>
@@ -9344,24 +9344,24 @@
     <row r="293" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C293">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E293">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F293">
         <is>
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c s="12" r="G293">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="0">
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c s="10" r="D294">
-        <v>44264</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E294">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F294">
         <is>
@@ -9406,24 +9406,24 @@
     <row r="295" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C295">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D295">
-        <v>44242</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E295">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
@@ -9431,100 +9431,100 @@
         </is>
       </c>
       <c s="12" r="G295">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C296">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D296">
-        <v>44270</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E296">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G296">
-        <v>44168</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C297">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D297">
-        <v>44214</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E297">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G297">
-        <v>44160</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C298">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D298">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E298">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G298">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="0">
@@ -9547,11 +9547,11 @@
         <v>44211</v>
       </c>
       <c s="11" r="E299">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F299">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G299">
@@ -9561,12 +9561,12 @@
     <row r="300" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C300">
@@ -9575,29 +9575,29 @@
         </is>
       </c>
       <c s="10" r="D300">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E300">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F300">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G300">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C301">
@@ -9606,69 +9606,69 @@
         </is>
       </c>
       <c s="10" r="D301">
-        <v>44214</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E301">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F301">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G301">
-        <v>44151</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C302">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D302">
-        <v>44186</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E302">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F302">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G302">
-        <v>44127</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C303">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D303">
-        <v>44104</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E303">
         <v>59</v>
@@ -9679,100 +9679,100 @@
         </is>
       </c>
       <c s="12" r="G303">
-        <v>44104</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C304">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D304">
-        <v>44197</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E304">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G304">
-        <v>44151</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">7241</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">SP+</t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C305">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Elgin</t>
         </is>
       </c>
       <c s="10" r="D305">
-        <v>43914</v>
+        <v>44197</v>
       </c>
       <c s="11" r="E305">
-        <v>89</v>
+        <v>229</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G305">
-        <v>44099</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">7218</t>
+          <t xml:space="preserve">7241</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
+          <t xml:space="preserve">SP+</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C306">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D306">
-        <v>43903</v>
+        <v>43914</v>
       </c>
       <c s="11" r="E306">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F306">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G306">
-        <v>44091</v>
+        <v>44099</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="0">
@@ -9783,19 +9783,19 @@
       </c>
       <c s="9" t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
+          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C307">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D307">
         <v>43903</v>
       </c>
       <c s="11" r="E307">
-        <v>358</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F307">
         <is>
@@ -9814,19 +9814,19 @@
       </c>
       <c s="9" t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">Sodexo - Medford SD</t>
+          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C308">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D308">
         <v>43903</v>
       </c>
       <c s="11" r="E308">
-        <v>111</v>
+        <v>358</v>
       </c>
       <c s="9" t="inlineStr" r="F308">
         <is>
@@ -9840,32 +9840,32 @@
     <row r="309" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">7217</t>
+          <t xml:space="preserve">7218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">PF Chang's</t>
+          <t xml:space="preserve">Sodexo - Medford SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C309">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D309">
-        <v>44092</v>
+        <v>43903</v>
       </c>
       <c s="11" r="E309">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F309">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G309">
-        <v>44092</v>
+        <v>44091</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="0">
@@ -9876,12 +9876,12 @@
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">PF Chang's - Eugene</t>
+          <t xml:space="preserve">PF Chang's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D310">
@@ -9902,32 +9902,32 @@
     <row r="311" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">7215</t>
+          <t xml:space="preserve">7217</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Salem</t>
+          <t xml:space="preserve">PF Chang's - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C311">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D311">
-        <v>44137</v>
+        <v>44092</v>
       </c>
       <c s="11" r="E311">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F311">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G311">
-        <v>44077</v>
+        <v>44092</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="0">
@@ -9938,19 +9938,19 @@
       </c>
       <c s="9" t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Portland</t>
+          <t xml:space="preserve">LAGS Medical Center - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C312">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D312">
         <v>44137</v>
       </c>
       <c s="11" r="E312">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
@@ -9964,12 +9964,12 @@
     <row r="313" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">7211</t>
+          <t xml:space="preserve">7215</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">Bon Appetit</t>
+          <t xml:space="preserve">LAGS Medical Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
@@ -9978,18 +9978,18 @@
         </is>
       </c>
       <c s="10" r="D313">
-        <v>44104</v>
+        <v>44137</v>
       </c>
       <c s="11" r="E313">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G313">
-        <v>44075</v>
+        <v>44077</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="0">
@@ -10012,11 +10012,11 @@
         <v>44104</v>
       </c>
       <c s="11" r="E314">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c s="9" t="inlineStr" r="F314">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G314">
@@ -10026,24 +10026,24 @@
     <row r="315" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">7209</t>
+          <t xml:space="preserve">7211</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">Dave &amp; Buster's</t>
+          <t xml:space="preserve">Bon Appetit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D315">
-        <v>44143</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E315">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F315">
         <is>
@@ -10051,123 +10051,123 @@
         </is>
       </c>
       <c s="12" r="G315">
-        <v>44082</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">7207</t>
+          <t xml:space="preserve">7209</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">PGE - Boardman</t>
+          <t xml:space="preserve">Dave &amp; Buster's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C316">
         <is>
-          <t xml:space="preserve">Boardman</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D316">
-        <v>44140</v>
+        <v>44143</v>
       </c>
       <c s="11" r="E316">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c s="9" t="inlineStr" r="F316">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G316">
-        <v>44075</v>
+        <v>44082</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">7199</t>
+          <t xml:space="preserve">7207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">LAIKA</t>
+          <t xml:space="preserve">PGE - Boardman</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C317">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Boardman</t>
         </is>
       </c>
       <c s="10" r="D317">
+        <v>44140</v>
+      </c>
+      <c s="11" r="E317">
+        <v>22</v>
+      </c>
+      <c s="9" t="inlineStr" r="F317">
+        <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G317">
         <v>44075</v>
-      </c>
-      <c s="11" r="E317">
-        <v>50</v>
-      </c>
-      <c s="9" t="inlineStr" r="F317">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G317">
-        <v>44057</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">7192</t>
+          <t xml:space="preserve">7199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">HMSHost</t>
+          <t xml:space="preserve">LAIKA</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C318">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D318">
-        <v>44119</v>
+        <v>44075</v>
       </c>
       <c s="11" r="E318">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F318">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G318">
-        <v>44054</v>
+        <v>44057</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">7186</t>
+          <t xml:space="preserve">7192</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">HMSHost</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C319">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D319">
-        <v>44124</v>
+        <v>44119</v>
       </c>
       <c s="11" r="E319">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F319">
         <is>
@@ -10175,7 +10175,7 @@
         </is>
       </c>
       <c s="12" r="G319">
-        <v>44032</v>
+        <v>44054</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="0">
@@ -10186,19 +10186,19 @@
       </c>
       <c s="9" t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C320">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D320">
-        <v>44099</v>
+        <v>44124</v>
       </c>
       <c s="11" r="E320">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F320">
         <is>
@@ -10217,19 +10217,19 @@
       </c>
       <c s="9" t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C321">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D321">
         <v>44099</v>
       </c>
       <c s="11" r="E321">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F321">
         <is>
@@ -10243,24 +10243,24 @@
     <row r="322" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">7185</t>
+          <t xml:space="preserve">7186</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
+          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C322">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D322">
-        <v>44105</v>
+        <v>44099</v>
       </c>
       <c s="11" r="E322">
-        <v>277</v>
+        <v>355</v>
       </c>
       <c s="9" t="inlineStr" r="F322">
         <is>
@@ -10268,18 +10268,18 @@
         </is>
       </c>
       <c s="12" r="G322">
-        <v>44041</v>
+        <v>44032</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">7184</t>
+          <t xml:space="preserve">7185</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
+          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C323">
@@ -10288,29 +10288,29 @@
         </is>
       </c>
       <c s="10" r="D323">
-        <v>43910</v>
+        <v>44105</v>
       </c>
       <c s="11" r="E323">
-        <v>70</v>
+        <v>277</v>
       </c>
       <c s="9" t="inlineStr" r="F323">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G323">
-        <v>44043</v>
+        <v>44041</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">7171</t>
+          <t xml:space="preserve">7184</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
+          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C324">
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c s="10" r="D324">
-        <v>44105</v>
+        <v>43910</v>
       </c>
       <c s="11" r="E324">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F324">
         <is>
@@ -10336,116 +10336,147 @@
     <row r="325" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7171</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C325">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D325"/>
-      <c s="13" t="str" r="E325"/>
+          <t xml:space="preserve">Portland</t>
+        </is>
+      </c>
+      <c s="10" r="D325">
+        <v>44105</v>
+      </c>
+      <c s="11" r="E325">
+        <v>193</v>
+      </c>
       <c s="9" t="inlineStr" r="F325">
         <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G325">
-        <v>44909</v>
+        <v>44043</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C326">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D326"/>
       <c s="13" t="str" r="E326"/>
       <c s="9" t="inlineStr" r="F326">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G326">
-        <v>45125</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C327">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">Mesa, AZ</t>
         </is>
       </c>
       <c s="9" t="str" r="D327"/>
       <c s="13" t="str" r="E327"/>
       <c s="9" t="inlineStr" r="F327">
         <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G327">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="328" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A328">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B328">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C328">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D328"/>
+      <c s="13" t="str" r="E328"/>
+      <c s="9" t="inlineStr" r="F328">
+        <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
-      <c s="12" r="G327">
+      <c s="12" r="G328">
         <v>45887</v>
       </c>
     </row>
-    <row r="328" ht="3.6" customHeight="0">
-      <c s="14" t="inlineStr" r="A328">
+    <row r="329" ht="3.6" customHeight="0">
+      <c s="14" t="inlineStr" r="A329">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B328">
+      <c s="14" t="inlineStr" r="B329">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C328">
+      <c s="14" t="inlineStr" r="C329">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D328">
+      <c s="14" t="inlineStr" r="D329">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E328">
+      <c s="14" t="inlineStr" r="E329">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F328">
+      <c s="14" t="inlineStr" r="F329">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G328">
+      <c s="14" t="inlineStr" r="G329">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -10460,7 +10491,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/31/2026 11:46:46 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/31/2026 7:53:31 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 8/31/2016 to 8/31/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/1/2016 to 9/1/2026</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 8/31/2026 7:53:31 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/1/2026 9:11:35 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/1/2016 to 9/1/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/2/2016 to 9/2/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/1/2026 7:11:58 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/2/2026 9:04:01 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/2/2026 9:04:01 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/2/2026 7:19:21 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/2/2016 to 9/2/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/3/2016 to 9/3/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/2/2026 7:19:21 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/3/2026 8:49:24 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/3/2026 8:49:24 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/3/2026 7:11:39 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/3/2016 to 9/3/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/4/2016 to 9/4/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/3/2026 7:11:39 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/4/2026 8:44:09 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/4/2026 8:44:09 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/4/2026 7:18:08 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/4/2016 to 9/4/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/5/2016 to 9/5/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/4/2026 7:18:08 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/5/2026 7:31:01 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/5/2026 7:31:01 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/5/2026 7:10:28 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/5/2016 to 9/5/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/6/2016 to 9/6/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/5/2026 7:10:28 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/6/2026 7:56:06 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/6/2026 7:56:06 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/6/2026 7:06:16 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/6/2016 to 9/6/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/7/2016 to 9/7/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/6/2026 7:06:16 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/7/2026 10:14:56 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/7/2026 10:14:56 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/7/2026 7:24:09 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/7/2016 to 9/7/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/8/2016 to 9/8/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/7/2026 7:24:09 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/8/2026 9:00:00 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/8/2026 9:00:00 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/8/2026 7:25:59 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/8/2016 to 9/8/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/9/2016 to 9/9/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/8/2026 7:25:59 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/9/2026 8:52:32 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/9/2026 8:52:32 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/9/2026 7:26:52 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/9/2016 to 9/9/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/10/2016 to 9/10/2026</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/9/2026 7:26:52 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/10/2026 8:51:03 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10274,364 +10274,116 @@
     <row r="323" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">7199</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">LAIKA</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C323">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
-        </is>
-      </c>
-      <c s="10" r="D323">
-        <v>44075</v>
-      </c>
-      <c s="11" r="E323">
-        <v>50</v>
-      </c>
+          <t xml:space="preserve">ELGIN                         </t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D323"/>
+      <c s="13" t="str" r="E323"/>
       <c s="9" t="inlineStr" r="F323">
         <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G323">
-        <v>44057</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">7192</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">HMSHost</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C324">
         <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D324">
-        <v>44119</v>
-      </c>
-      <c s="11" r="E324">
-        <v>51</v>
-      </c>
+          <t xml:space="preserve">Mesa, AZ</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D324"/>
+      <c s="13" t="str" r="E324"/>
       <c s="9" t="inlineStr" r="F324">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G324">
-        <v>44054</v>
+        <v>45125</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">7186</t>
+          <t xml:space="preserve">9324</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C325">
         <is>
-          <t xml:space="preserve">Beaverton</t>
-        </is>
-      </c>
-      <c s="10" r="D325">
-        <v>44124</v>
-      </c>
-      <c s="11" r="E325">
-        <v>66</v>
-      </c>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D325"/>
+      <c s="13" t="str" r="E325"/>
       <c s="9" t="inlineStr" r="F325">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G325">
-        <v>44032</v>
-      </c>
-    </row>
-    <row r="326" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A326">
-        <is>
-          <t xml:space="preserve">7186</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B326">
-        <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Hillsboro</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C326">
-        <is>
-          <t xml:space="preserve">Hillsboro</t>
-        </is>
-      </c>
-      <c s="10" r="D326">
-        <v>44099</v>
-      </c>
-      <c s="11" r="E326">
-        <v>23</v>
-      </c>
-      <c s="9" t="inlineStr" r="F326">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G326">
-        <v>44032</v>
-      </c>
-    </row>
-    <row r="327" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A327">
-        <is>
-          <t xml:space="preserve">7186</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B327">
-        <is>
-          <t xml:space="preserve">Nike (Lifeworks) - Beaverton</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C327">
-        <is>
-          <t xml:space="preserve">Beaverton</t>
-        </is>
-      </c>
-      <c s="10" r="D327">
-        <v>44099</v>
-      </c>
-      <c s="11" r="E327">
-        <v>355</v>
-      </c>
-      <c s="9" t="inlineStr" r="F327">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G327">
-        <v>44032</v>
-      </c>
-    </row>
-    <row r="328" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A328">
-        <is>
-          <t xml:space="preserve">7185</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B328">
-        <is>
-          <t xml:space="preserve">Alaska Airlines - Portland Internationa</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C328">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D328">
-        <v>44105</v>
-      </c>
-      <c s="11" r="E328">
-        <v>277</v>
-      </c>
-      <c s="9" t="inlineStr" r="F328">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G328">
-        <v>44041</v>
-      </c>
-    </row>
-    <row r="329" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A329">
-        <is>
-          <t xml:space="preserve">7184</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B329">
-        <is>
-          <t xml:space="preserve">Embassy Suites Portland-Downtown</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C329">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D329">
-        <v>43910</v>
-      </c>
-      <c s="11" r="E329">
-        <v>70</v>
-      </c>
-      <c s="9" t="inlineStr" r="F329">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G329">
-        <v>44043</v>
-      </c>
-    </row>
-    <row r="330" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A330">
-        <is>
-          <t xml:space="preserve">7171</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B330">
-        <is>
-          <t xml:space="preserve">LSG Group - Sky Chefs, Inc</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C330">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D330">
-        <v>44105</v>
-      </c>
-      <c s="11" r="E330">
-        <v>193</v>
-      </c>
-      <c s="9" t="inlineStr" r="F330">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G330">
-        <v>44043</v>
-      </c>
-    </row>
-    <row r="331" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A331">
-        <is>
-          <t xml:space="preserve">8470</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B331">
-        <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C331">
-        <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D331"/>
-      <c s="13" t="str" r="E331"/>
-      <c s="9" t="inlineStr" r="F331">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G331">
-        <v>44909</v>
-      </c>
-    </row>
-    <row r="332" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A332">
-        <is>
-          <t xml:space="preserve">8592</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B332">
-        <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C332">
-        <is>
-          <t xml:space="preserve">Mesa, AZ</t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D332"/>
-      <c s="13" t="str" r="E332"/>
-      <c s="9" t="inlineStr" r="F332">
-        <is>
-          <t xml:space="preserve">Permanent closure</t>
-        </is>
-      </c>
-      <c s="12" r="G332">
-        <v>45125</v>
-      </c>
-    </row>
-    <row r="333" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A333">
-        <is>
-          <t xml:space="preserve">9324</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B333">
-        <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C333">
-        <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D333"/>
-      <c s="13" t="str" r="E333"/>
-      <c s="9" t="inlineStr" r="F333">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G333">
         <v>45887</v>
       </c>
     </row>
-    <row r="334" ht="3.6" customHeight="0">
-      <c s="14" t="inlineStr" r="A334">
+    <row r="326" ht="3.6" customHeight="0">
+      <c s="14" t="inlineStr" r="A326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B334">
+      <c s="14" t="inlineStr" r="B326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C334">
+      <c s="14" t="inlineStr" r="C326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D334">
+      <c s="14" t="inlineStr" r="D326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E334">
+      <c s="14" t="inlineStr" r="E326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F334">
+      <c s="14" t="inlineStr" r="F326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G334">
+      <c s="14" t="inlineStr" r="G326">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -10646,7 +10398,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/10/2026 8:51:03 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/10/2026 7:24:40 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/10/2016 to 9/10/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/11/2016 to 9/11/2026</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/10/2026 7:24:40 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/11/2026 8:51:43 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -1227,23 +1227,23 @@
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D31">
-        <v>46234</v>
+        <v>46333</v>
       </c>
       <c s="11" r="E31">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G31">
@@ -1258,19 +1258,19 @@
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D32">
         <v>46234</v>
       </c>
       <c s="11" r="E32">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F32">
         <is>
@@ -1289,12 +1289,12 @@
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D33">
@@ -1320,19 +1320,19 @@
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D34">
         <v>46234</v>
       </c>
       <c s="11" r="E34">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F34">
         <is>
@@ -1351,19 +1351,19 @@
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D35">
         <v>46234</v>
       </c>
       <c s="11" r="E35">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F35">
         <is>
@@ -1377,86 +1377,86 @@
     <row r="36" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D36">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E36">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G36">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D37">
-        <v>46201</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E37">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F37">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G37">
-        <v>46141</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D38">
-        <v>46295</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E38">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F38">
         <is>
@@ -1464,49 +1464,49 @@
         </is>
       </c>
       <c s="12" r="G38">
-        <v>46114</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D39">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E39">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G39">
-        <v>46108</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
@@ -1515,18 +1515,18 @@
         </is>
       </c>
       <c s="10" r="D40">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E40">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F40">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G40">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="0">
@@ -1537,7 +1537,7 @@
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
@@ -1563,24 +1563,24 @@
     <row r="42" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D42">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E42">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F42">
         <is>
@@ -1588,38 +1588,38 @@
         </is>
       </c>
       <c s="12" r="G42">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D43">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E43">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F43">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G43">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="0">
@@ -1630,19 +1630,19 @@
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D44">
         <v>46131</v>
       </c>
       <c s="11" r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F44">
         <is>
@@ -1656,63 +1656,63 @@
     <row r="45" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D45">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E45">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F45">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G45">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D46">
         <v>46117</v>
       </c>
       <c s="11" r="E46">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F46">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G46">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="0">
@@ -1723,19 +1723,19 @@
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D47">
         <v>46117</v>
       </c>
       <c s="11" r="E47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F47">
         <is>
@@ -1754,12 +1754,12 @@
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D48">
@@ -1785,12 +1785,12 @@
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D49">
@@ -1816,12 +1816,12 @@
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D50">
@@ -1847,12 +1847,12 @@
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D51">
@@ -1878,12 +1878,12 @@
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D52">
@@ -1909,12 +1909,12 @@
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D53">
@@ -1940,7 +1940,7 @@
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
@@ -1971,7 +1971,7 @@
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
@@ -2002,12 +2002,12 @@
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D56">
@@ -2033,12 +2033,12 @@
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D57">
@@ -2064,12 +2064,12 @@
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D58">
@@ -2095,7 +2095,7 @@
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
@@ -2126,19 +2126,19 @@
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D60">
         <v>46117</v>
       </c>
       <c s="11" r="E60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F60">
         <is>
@@ -2157,19 +2157,19 @@
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D61">
         <v>46117</v>
       </c>
       <c s="11" r="E61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F61">
         <is>
@@ -2188,19 +2188,19 @@
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D62">
         <v>46117</v>
       </c>
       <c s="11" r="E62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F62">
         <is>
@@ -2219,12 +2219,12 @@
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D63">
@@ -2250,12 +2250,12 @@
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D64">
@@ -2276,24 +2276,24 @@
     <row r="65" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D65">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E65">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F65">
         <is>
@@ -2312,19 +2312,19 @@
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D66">
         <v>46112</v>
       </c>
       <c s="11" r="E66">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F66">
         <is>
@@ -2343,19 +2343,19 @@
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D67">
         <v>46112</v>
       </c>
       <c s="11" r="E67">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F67">
         <is>
@@ -2369,24 +2369,24 @@
     <row r="68" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D68">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E68">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F68">
         <is>
@@ -2394,30 +2394,30 @@
         </is>
       </c>
       <c s="12" r="G68">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D69">
-        <v>46142</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E69">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F69">
         <is>
@@ -2425,30 +2425,30 @@
         </is>
       </c>
       <c s="12" r="G69">
-        <v>46020</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D70">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E70">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F70">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c s="12" r="G70">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="0">
@@ -2467,7 +2467,7 @@
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
@@ -2479,7 +2479,7 @@
         <v>46014</v>
       </c>
       <c s="11" r="E71">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F71">
         <is>
@@ -2498,19 +2498,19 @@
       </c>
       <c s="9" t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C72">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D72">
         <v>46014</v>
       </c>
       <c s="11" r="E72">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
@@ -2524,43 +2524,43 @@
     <row r="73" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C73">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D73">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E73">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G73">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C74">
@@ -2569,29 +2569,29 @@
         </is>
       </c>
       <c s="10" r="D74">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E74">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F74">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G74">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c s="10" r="D75">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E75">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F75">
         <is>
@@ -2617,63 +2617,63 @@
     <row r="76" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D76">
         <v>46054</v>
       </c>
       <c s="11" r="E76">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F76">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G76">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D77">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E77">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G77">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="0">
@@ -2684,19 +2684,19 @@
       </c>
       <c s="9" t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C78">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D78">
         <v>45916</v>
       </c>
       <c s="11" r="E78">
-        <v>510</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c s="9" t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C79">
@@ -2727,7 +2727,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E79">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
@@ -2746,7 +2746,7 @@
       </c>
       <c s="9" t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C80">
@@ -2758,7 +2758,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E80">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
@@ -2772,24 +2772,24 @@
     <row r="81" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D81">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E81">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c s="12" r="G81">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="0">
@@ -2808,23 +2808,23 @@
       </c>
       <c s="9" t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C82">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D82">
         <v>46022</v>
       </c>
       <c s="11" r="E82">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G82">
@@ -2839,19 +2839,19 @@
       </c>
       <c s="9" t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C83">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D83">
         <v>46022</v>
       </c>
       <c s="11" r="E83">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
@@ -2870,19 +2870,19 @@
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D84">
         <v>46022</v>
       </c>
       <c s="11" r="E84">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
@@ -2901,19 +2901,19 @@
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D85">
         <v>46022</v>
       </c>
       <c s="11" r="E85">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
@@ -2927,55 +2927,55 @@
     <row r="86" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D86">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E86">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G86">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D87">
         <v>46017</v>
       </c>
       <c s="11" r="E87">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
@@ -2989,28 +2989,28 @@
     <row r="88" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D88">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E88">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G88">
@@ -3034,14 +3034,14 @@
         </is>
       </c>
       <c s="10" r="D89">
-        <v>46017</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E89">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G89">
@@ -3051,86 +3051,86 @@
     <row r="90" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C90">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D90">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E90">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G90">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C91">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D91">
-        <v>46022</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E91">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G91">
-        <v>45917</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D92">
-        <v>45978</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E92">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
@@ -3138,18 +3138,18 @@
         </is>
       </c>
       <c s="12" r="G92">
-        <v>45943</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c s="10" r="D93">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E93">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
@@ -3169,38 +3169,38 @@
         </is>
       </c>
       <c s="12" r="G93">
-        <v>45930</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D94">
-        <v>45940</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E94">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G94">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="0">
@@ -3220,14 +3220,14 @@
         </is>
       </c>
       <c s="10" r="D95">
-        <v>45925</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E95">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G95">
@@ -3237,24 +3237,24 @@
     <row r="96" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D96">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E96">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
@@ -3262,34 +3262,34 @@
         </is>
       </c>
       <c s="12" r="G96">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C97">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D97">
         <v>45976</v>
       </c>
       <c s="11" r="E97">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G97">
@@ -3299,63 +3299,63 @@
     <row r="98" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D98">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E98">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G98">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D99">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E99">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G99">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="0">
@@ -3366,7 +3366,7 @@
       </c>
       <c s="9" t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C100">
@@ -3378,7 +3378,7 @@
         <v>45949</v>
       </c>
       <c s="11" r="E100">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
@@ -3392,12 +3392,12 @@
     <row r="101" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C101">
@@ -3406,41 +3406,41 @@
         </is>
       </c>
       <c s="10" r="D101">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E101">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G101">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D102">
-        <v>45874</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E102">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
@@ -3448,18 +3448,18 @@
         </is>
       </c>
       <c s="12" r="G102">
-        <v>45867</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
@@ -3468,49 +3468,49 @@
         </is>
       </c>
       <c s="10" r="D103">
-        <v>45920</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E103">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G103">
-        <v>45854</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D104">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E104">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G104">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="0">
@@ -3521,19 +3521,19 @@
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D105">
         <v>45912</v>
       </c>
       <c s="11" r="E105">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
@@ -3547,63 +3547,63 @@
     <row r="106" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D106">
         <v>45912</v>
       </c>
       <c s="11" r="E106">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G106">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D107">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E107">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G107">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="0">
@@ -3614,19 +3614,19 @@
       </c>
       <c s="9" t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D108">
         <v>45853</v>
       </c>
       <c s="11" r="E108">
-        <v>1544</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
@@ -3645,7 +3645,7 @@
       </c>
       <c s="9" t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C109">
@@ -3657,7 +3657,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E109">
-        <v>174</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
@@ -3676,7 +3676,7 @@
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
@@ -3688,7 +3688,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E110">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
@@ -3702,86 +3702,86 @@
     <row r="111" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D111">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E111">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G111">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D112">
-        <v>45901</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E112">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G112">
-        <v>45839</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D113">
-        <v>45982</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E113">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c s="12" r="G113">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="0">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c s="10" r="D114">
-        <v>45968</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E114">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c s="10" r="D115">
-        <v>45894</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E115">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
@@ -3857,24 +3857,24 @@
     <row r="116" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D116">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E116">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
@@ -3882,30 +3882,30 @@
         </is>
       </c>
       <c s="12" r="G116">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D117">
         <v>45838</v>
       </c>
       <c s="11" r="E117">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
@@ -3919,94 +3919,94 @@
     <row r="118" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D118">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E118">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G118">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D119">
-        <v>45807</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E119">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G119">
-        <v>45804</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D120">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E120">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G120">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="0">
@@ -4017,19 +4017,19 @@
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D121">
         <v>45866</v>
       </c>
       <c s="11" r="E121">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
@@ -4043,55 +4043,55 @@
     <row r="122" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D122">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E122">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G122">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D123">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E123">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
@@ -4099,85 +4099,85 @@
         </is>
       </c>
       <c s="12" r="G123">
-        <v>45778</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D124">
-        <v>45769</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E124">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G124">
-        <v>45769</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D125">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E125">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G125">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C126">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D126">
@@ -4188,69 +4188,69 @@
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G126">
-        <v>45763</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D127">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E127">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G127">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D128">
-        <v>45810</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E128">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G128">
@@ -4260,43 +4260,43 @@
     <row r="129" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D129">
-        <v>45808</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E129">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G129">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
@@ -4305,103 +4305,103 @@
         </is>
       </c>
       <c s="10" r="D130">
-        <v>45834</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E130">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G130">
-        <v>45774</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D131">
-        <v>45838</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E131">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F131">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G131">
-        <v>45744</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D132">
-        <v>45706</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E132">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F132">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G132">
-        <v>45706</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D133">
-        <v>45734</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E133">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F133">
         <is>
@@ -4409,38 +4409,38 @@
         </is>
       </c>
       <c s="12" r="G133">
-        <v>45666</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D134">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E134">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F134">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G134">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="0">
@@ -4451,19 +4451,19 @@
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D135">
         <v>45707</v>
       </c>
       <c s="11" r="E135">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
@@ -4477,63 +4477,63 @@
     <row r="136" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D136">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E136">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G136">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D137">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E137">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G137">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="0">
@@ -4544,19 +4544,19 @@
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D138">
         <v>45696</v>
       </c>
       <c s="11" r="E138">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
@@ -4570,86 +4570,86 @@
     <row r="139" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D139">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E139">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G139">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D140">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E140">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G140">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D141">
         <v>45931</v>
       </c>
       <c s="11" r="E141">
-        <v>221</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F141">
         <is>
@@ -4663,43 +4663,43 @@
     <row r="142" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D142">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E142">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F142">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G142">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
@@ -4708,18 +4708,18 @@
         </is>
       </c>
       <c s="10" r="D143">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E143">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F143">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G143">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="0">
@@ -4730,19 +4730,19 @@
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D144">
         <v>45726</v>
       </c>
       <c s="11" r="E144">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
@@ -4761,19 +4761,19 @@
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D145">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E145">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
@@ -4792,19 +4792,19 @@
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D146">
         <v>45725</v>
       </c>
       <c s="11" r="E146">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
@@ -4823,19 +4823,19 @@
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D147">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E147">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
@@ -4854,12 +4854,12 @@
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D148">
@@ -4885,12 +4885,12 @@
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D149">
@@ -4916,19 +4916,19 @@
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D150">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E150">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F150">
         <is>
@@ -4947,19 +4947,19 @@
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D151">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E151">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F151">
         <is>
@@ -4978,7 +4978,7 @@
       </c>
       <c s="9" t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C152">
@@ -4987,10 +4987,10 @@
         </is>
       </c>
       <c s="10" r="D152">
-        <v>45703</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E152">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F152">
         <is>
@@ -5009,19 +5009,19 @@
       </c>
       <c s="9" t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C153">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D153">
-        <v>45690</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E153">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
@@ -5035,12 +5035,12 @@
     <row r="154" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C154">
@@ -5049,72 +5049,72 @@
         </is>
       </c>
       <c s="10" r="D154">
-        <v>45657</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E154">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F154">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G154">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C155">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D155">
-        <v>45640</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E155">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G155">
-        <v>45580</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C156">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D156">
-        <v>45657</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E156">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
@@ -5122,100 +5122,100 @@
         </is>
       </c>
       <c s="12" r="G156">
-        <v>45595</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C157">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D157">
-        <v>45584</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E157">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G157">
-        <v>45584</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D158">
-        <v>45664</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E158">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G158">
-        <v>45582</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D159">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E159">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F159">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G159">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="0">
@@ -5226,19 +5226,19 @@
       </c>
       <c s="9" t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C160">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D160">
         <v>45611</v>
       </c>
       <c s="11" r="E160">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F160">
         <is>
@@ -5257,7 +5257,7 @@
       </c>
       <c s="9" t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C161">
@@ -5269,7 +5269,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E161">
-        <v>124</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F161">
         <is>
@@ -5288,7 +5288,7 @@
       </c>
       <c s="9" t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C162">
@@ -5300,7 +5300,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E162">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5314,28 +5314,28 @@
     <row r="163" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C163">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D163">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E163">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G163">
@@ -5345,24 +5345,24 @@
     <row r="164" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C164">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D164">
-        <v>45621</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E164">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
@@ -5370,38 +5370,38 @@
         </is>
       </c>
       <c s="12" r="G164">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C165">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D165">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E165">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G165">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="0">
@@ -5412,23 +5412,23 @@
       </c>
       <c s="9" t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C166">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D166">
         <v>45544</v>
       </c>
       <c s="11" r="E166">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G166">
@@ -5438,55 +5438,55 @@
     <row r="167" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C167">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D167">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E167">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G167">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C168">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D168">
-        <v>45654</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E168">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c s="12" r="G168">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="0">
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c s="10" r="D169">
-        <v>45612</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E169">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
@@ -5545,14 +5545,14 @@
         </is>
       </c>
       <c s="10" r="D170">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E170">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G170">
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c s="10" r="D171">
-        <v>45569</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E171">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
@@ -5607,14 +5607,14 @@
         </is>
       </c>
       <c s="10" r="D172">
-        <v>45555</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E172">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G172">
@@ -5624,24 +5624,24 @@
     <row r="173" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C173">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D173">
-        <v>45653</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E173">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c s="12" r="G173">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="0">
@@ -5669,14 +5669,14 @@
         </is>
       </c>
       <c s="10" r="D174">
-        <v>45505</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E174">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G174">
@@ -5686,24 +5686,24 @@
     <row r="175" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C175">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E175">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
@@ -5711,13 +5711,13 @@
         </is>
       </c>
       <c s="12" r="G175">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B176">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45513</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E176">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
@@ -5742,18 +5742,18 @@
         </is>
       </c>
       <c s="12" r="G176">
-        <v>45450</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C177">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c s="10" r="D177">
-        <v>45504</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E177">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
@@ -5773,30 +5773,30 @@
         </is>
       </c>
       <c s="12" r="G177">
-        <v>45441</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C178">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D178">
-        <v>46229</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E178">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c s="12" r="G178">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="0">
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c s="10" r="D179">
-        <v>45688</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E179">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c s="10" r="D180">
-        <v>45506</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E180">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
@@ -5872,32 +5872,32 @@
     <row r="181" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C181">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D181">
-        <v>45483</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E181">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G181">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="0">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c s="10" r="D182">
-        <v>45401</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E182">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c s="10" r="D183">
-        <v>45366</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E183">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
@@ -5965,43 +5965,43 @@
     <row r="184" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C184">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D184">
-        <v>45473</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E184">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G184">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C185">
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c s="10" r="D185">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E185">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F185">
         <is>
@@ -6021,111 +6021,111 @@
         </is>
       </c>
       <c s="12" r="G185">
-        <v>45404</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C186">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D186">
         <v>45471</v>
       </c>
       <c s="11" r="E186">
-        <v>740</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F186">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G186">
-        <v>45401</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C187">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D187">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E187">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F187">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G187">
-        <v>45384</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C188">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D188">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E188">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G188">
-        <v>45380</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
@@ -6134,134 +6134,134 @@
         </is>
       </c>
       <c s="10" r="D189">
-        <v>45439</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E189">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G189">
-        <v>45379</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C190">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D190">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E190">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G190">
-        <v>45372</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C191">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D191">
-        <v>45433</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E191">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G191">
-        <v>45373</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C192">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D192">
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E192">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G192">
-        <v>45358</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C193">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D193">
-        <v>45352</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E193">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
@@ -6269,18 +6269,18 @@
         </is>
       </c>
       <c s="12" r="G193">
-        <v>45345</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C194">
@@ -6289,41 +6289,41 @@
         </is>
       </c>
       <c s="10" r="D194">
-        <v>45401</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E194">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G194">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C195">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D195">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E195">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F195">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c s="12" r="G195">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="0">
@@ -6342,7 +6342,7 @@
       </c>
       <c s="9" t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C196">
@@ -6354,7 +6354,7 @@
         <v>45337</v>
       </c>
       <c s="11" r="E196">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F196">
         <is>
@@ -6368,24 +6368,24 @@
     <row r="197" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C197">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D197">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E197">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
@@ -6393,34 +6393,34 @@
         </is>
       </c>
       <c s="12" r="G197">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C198">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D198">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E198">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G198">
@@ -6435,19 +6435,19 @@
       </c>
       <c s="9" t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C199">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D199">
         <v>45382</v>
       </c>
       <c s="11" r="E199">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
@@ -6466,19 +6466,19 @@
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D200">
         <v>45382</v>
       </c>
       <c s="11" r="E200">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
@@ -6497,7 +6497,7 @@
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
@@ -6509,7 +6509,7 @@
         <v>45382</v>
       </c>
       <c s="11" r="E201">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
@@ -6528,12 +6528,12 @@
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D202">
@@ -6554,32 +6554,32 @@
     <row r="203" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D203">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E203">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F203">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G203">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="0">
@@ -6590,23 +6590,23 @@
       </c>
       <c s="9" t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D204">
         <v>45366</v>
       </c>
       <c s="11" r="E204">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F204">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G204">
@@ -6616,55 +6616,55 @@
     <row r="205" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C205">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D205">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E205">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F205">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G205">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C206">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D206">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E206">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F206">
         <is>
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c s="12" r="G206">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="0">
@@ -6683,19 +6683,19 @@
       </c>
       <c s="9" t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C207">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D207">
         <v>45275</v>
       </c>
       <c s="11" r="E207">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F207">
         <is>
@@ -6714,19 +6714,19 @@
       </c>
       <c s="9" t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C208">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D208">
         <v>45275</v>
       </c>
       <c s="11" r="E208">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F208">
         <is>
@@ -6745,19 +6745,19 @@
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D209">
         <v>45275</v>
       </c>
       <c s="11" r="E209">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F209">
         <is>
@@ -6771,24 +6771,24 @@
     <row r="210" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C210">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D210">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E210">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F210">
         <is>
@@ -6796,30 +6796,30 @@
         </is>
       </c>
       <c s="12" r="G210">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C211">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D211">
-        <v>45294</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E211">
-        <v>136</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F211">
         <is>
@@ -6827,30 +6827,30 @@
         </is>
       </c>
       <c s="12" r="G211">
-        <v>45217</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C212">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D212">
-        <v>45473</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E212">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F212">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c s="12" r="G212">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="0">
@@ -6878,10 +6878,10 @@
         </is>
       </c>
       <c s="10" r="D213">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E213">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F213">
         <is>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c s="10" r="D214">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E214">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F214">
         <is>
@@ -6926,24 +6926,24 @@
     <row r="215" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C215">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D215">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E215">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F215">
         <is>
@@ -6951,18 +6951,18 @@
         </is>
       </c>
       <c s="12" r="G215">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C216">
@@ -6974,7 +6974,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E216">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
@@ -6988,12 +6988,12 @@
     <row r="217" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C217">
@@ -7005,7 +7005,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E217">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
@@ -7019,24 +7019,24 @@
     <row r="218" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C218">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D218">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E218">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7044,61 +7044,61 @@
         </is>
       </c>
       <c s="12" r="G218">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C219">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D219">
-        <v>45237</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E219">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G219">
-        <v>45176</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C220">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D220">
-        <v>45387</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E220">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F220">
         <is>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c s="12" r="G220">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="0">
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c s="10" r="D221">
-        <v>45317</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E221">
         <v>2</v>
@@ -7157,14 +7157,14 @@
         </is>
       </c>
       <c s="10" r="D222">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E222">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F222">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G222">
@@ -7179,7 +7179,7 @@
       </c>
       <c s="9" t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C223">
@@ -7191,11 +7191,11 @@
         <v>45303</v>
       </c>
       <c s="11" r="E223">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F223">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G223">
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c s="10" r="D224">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E224">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
@@ -7241,7 +7241,7 @@
       </c>
       <c s="9" t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C225">
@@ -7253,7 +7253,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E225">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c s="10" r="D226">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E226">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c s="10" r="D227">
-        <v>45247</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E227">
         <v>1</v>
@@ -7343,14 +7343,14 @@
         </is>
       </c>
       <c s="10" r="D228">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E228">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F228">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G228">
@@ -7365,7 +7365,7 @@
       </c>
       <c s="9" t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C229">
@@ -7377,7 +7377,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E229">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F229">
         <is>
@@ -7391,86 +7391,86 @@
     <row r="230" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D230">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E230">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G230">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D231">
-        <v>45199</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E231">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G231">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C232">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D232">
-        <v>45213</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E232">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F232">
         <is>
@@ -7484,24 +7484,24 @@
     <row r="233" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D233">
-        <v>45283</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E233">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F233">
         <is>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c s="12" r="G233">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="0">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c s="10" r="D234">
-        <v>45192</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E234">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F234">
         <is>
@@ -7546,24 +7546,24 @@
     <row r="235" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C235">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D235">
-        <v>45137</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E235">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F235">
         <is>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c s="12" r="G235">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="0">
@@ -7582,19 +7582,19 @@
       </c>
       <c s="9" t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C236">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D236">
-        <v>45107</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E236">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F236">
         <is>
@@ -7608,32 +7608,32 @@
     <row r="237" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D237">
-        <v>45233</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E237">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F237">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G237">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="0">
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45205</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E238">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F238">
         <is>
@@ -7670,24 +7670,24 @@
     <row r="239" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45175</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E239">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F239">
         <is>
@@ -7695,30 +7695,30 @@
         </is>
       </c>
       <c s="12" r="G239">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D240">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E240">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
@@ -7726,123 +7726,123 @@
         </is>
       </c>
       <c s="12" r="G240">
-        <v>45091</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D241">
-        <v>45128</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E241">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G241">
-        <v>45090</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D242">
-        <v>45170</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E242">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F242">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G242">
-        <v>45085</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D243">
-        <v>45106</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E243">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F243">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G243">
-        <v>45083</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D244">
-        <v>45107</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E244">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F244">
         <is>
@@ -7850,30 +7850,30 @@
         </is>
       </c>
       <c s="12" r="G244">
-        <v>45070</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C245">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D245">
-        <v>45115</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E245">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F245">
         <is>
@@ -7881,61 +7881,61 @@
         </is>
       </c>
       <c s="12" r="G245">
-        <v>45055</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C246">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D246">
-        <v>45105</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E246">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F246">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G246">
-        <v>45044</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>45135</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E247">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
@@ -7943,30 +7943,30 @@
         </is>
       </c>
       <c s="12" r="G247">
-        <v>45041</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D248">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E248">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c s="12" r="G248">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="0">
@@ -7985,12 +7985,12 @@
       </c>
       <c s="9" t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C249">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D249">
@@ -8016,12 +8016,12 @@
       </c>
       <c s="9" t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C250">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D250">
@@ -8047,12 +8047,12 @@
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D251">
@@ -8078,12 +8078,12 @@
       </c>
       <c s="9" t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C252">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D252">
@@ -8104,86 +8104,86 @@
     <row r="253" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C253">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D253">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E253">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F253">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G253">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C254">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D254">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E254">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F254">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G254">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D255">
-        <v>45058</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E255">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F255">
         <is>
@@ -8197,24 +8197,24 @@
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D256">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E256">
-        <v>379</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
@@ -8222,30 +8222,30 @@
         </is>
       </c>
       <c s="12" r="G256">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C257">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D257">
         <v>45079</v>
       </c>
       <c s="11" r="E257">
-        <v>201</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
@@ -8259,12 +8259,12 @@
     <row r="258" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C258">
@@ -8273,103 +8273,103 @@
         </is>
       </c>
       <c s="10" r="D258">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E258">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G258">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C259">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D259">
-        <v>44939</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E259">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G259">
-        <v>44937</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D260">
-        <v>44890</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E260">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F260">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G260">
-        <v>44827</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C261">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D261">
-        <v>44907</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E261">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F261">
         <is>
@@ -8377,30 +8377,30 @@
         </is>
       </c>
       <c s="12" r="G261">
-        <v>44846</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C262">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D262">
-        <v>44911</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E262">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F262">
         <is>
@@ -8408,80 +8408,80 @@
         </is>
       </c>
       <c s="12" r="G262">
-        <v>44845</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C263">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D263">
-        <v>44869</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E263">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F263">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G263">
-        <v>44812</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C264">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D264">
-        <v>44866</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E264">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F264">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G264">
-        <v>44803</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C265">
@@ -8490,41 +8490,41 @@
         </is>
       </c>
       <c s="10" r="D265">
-        <v>44856</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E265">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G265">
-        <v>44795</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C266">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D266">
-        <v>44815</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E266">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
@@ -8532,30 +8532,30 @@
         </is>
       </c>
       <c s="12" r="G266">
-        <v>44755</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C267">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D267">
-        <v>44802</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E267">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
@@ -8563,30 +8563,30 @@
         </is>
       </c>
       <c s="12" r="G267">
-        <v>44741</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C268">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D268">
-        <v>44865</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E268">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c s="12" r="G268">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="0">
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c s="10" r="D269">
-        <v>44805</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E269">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
@@ -8631,74 +8631,74 @@
     <row r="270" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C270">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D270">
-        <v>44712</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E270">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G270">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C271">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D271">
-        <v>44600</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E271">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G271">
-        <v>44600</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C272">
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c s="10" r="D272">
-        <v>44652</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E272">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
@@ -8718,30 +8718,30 @@
         </is>
       </c>
       <c s="12" r="G272">
-        <v>44578</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C273">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E273">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
@@ -8749,7 +8749,7 @@
         </is>
       </c>
       <c s="12" r="G273">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="0">
@@ -8772,7 +8772,7 @@
         <v>44620</v>
       </c>
       <c s="11" r="E274">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
@@ -8786,24 +8786,24 @@
     <row r="275" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C275">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D275">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E275">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
@@ -8811,30 +8811,30 @@
         </is>
       </c>
       <c s="12" r="G275">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C276">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D276">
-        <v>44531</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E276">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
@@ -8842,30 +8842,30 @@
         </is>
       </c>
       <c s="12" r="G276">
-        <v>44470</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C277">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44799</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E277">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c s="12" r="G277">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="0">
@@ -8893,10 +8893,10 @@
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44743</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E278">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c s="10" r="D279">
-        <v>44680</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E279">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c s="10" r="D280">
-        <v>44652</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E280">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8986,10 +8986,10 @@
         </is>
       </c>
       <c s="10" r="D281">
-        <v>44575</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E281">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c s="10" r="D282">
-        <v>44512</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E282">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
@@ -9034,12 +9034,12 @@
     <row r="283" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C283">
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c s="10" r="D283">
-        <v>44469</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E283">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
@@ -9059,30 +9059,30 @@
         </is>
       </c>
       <c s="12" r="G283">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C284">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44482</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E284">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
@@ -9090,30 +9090,30 @@
         </is>
       </c>
       <c s="12" r="G284">
-        <v>44421</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C285">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D285">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E285">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c s="12" r="G285">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="0">
@@ -9132,7 +9132,7 @@
       </c>
       <c s="9" t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C286">
@@ -9144,7 +9144,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E286">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
@@ -9163,19 +9163,19 @@
       </c>
       <c s="9" t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C287">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D287">
         <v>44469</v>
       </c>
       <c s="11" r="E287">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
@@ -9189,24 +9189,24 @@
     <row r="288" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C288">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D288">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E288">
-        <v>402</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
@@ -9214,30 +9214,30 @@
         </is>
       </c>
       <c s="12" r="G288">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C289">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D289">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E289">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
@@ -9245,18 +9245,18 @@
         </is>
       </c>
       <c s="12" r="G289">
-        <v>44383</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C290">
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c s="10" r="D290">
-        <v>44348</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E290">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
@@ -9276,18 +9276,18 @@
         </is>
       </c>
       <c s="12" r="G290">
-        <v>44308</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C291">
@@ -9296,49 +9296,49 @@
         </is>
       </c>
       <c s="10" r="D291">
-        <v>44347</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E291">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G291">
-        <v>44291</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C292">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D292">
-        <v>44311</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E292">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F292">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G292">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="0">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44256</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E293">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F293">
         <is>
@@ -9375,32 +9375,32 @@
     <row r="294" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C294">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D294">
-        <v>44358</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E294">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F294">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G294">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="0">
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c s="10" r="D295">
-        <v>44330</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E295">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
@@ -9451,10 +9451,10 @@
         </is>
       </c>
       <c s="10" r="D296">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E296">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c s="10" r="D297">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E297">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
@@ -9499,12 +9499,12 @@
     <row r="298" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C298">
@@ -9516,7 +9516,7 @@
         <v>44288</v>
       </c>
       <c s="11" r="E298">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
@@ -9530,24 +9530,24 @@
     <row r="299" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C299">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D299">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E299">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F299">
         <is>
@@ -9555,7 +9555,7 @@
         </is>
       </c>
       <c s="12" r="G299">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="0">
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c s="10" r="D300">
-        <v>44264</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E300">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F300">
         <is>
@@ -9592,24 +9592,24 @@
     <row r="301" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C301">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D301">
-        <v>44242</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E301">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F301">
         <is>
@@ -9617,100 +9617,100 @@
         </is>
       </c>
       <c s="12" r="G301">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C302">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D302">
-        <v>44270</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E302">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F302">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G302">
-        <v>44168</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C303">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D303">
-        <v>44214</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E303">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F303">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G303">
-        <v>44160</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C304">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D304">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E304">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G304">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="0">
@@ -9733,11 +9733,11 @@
         <v>44211</v>
       </c>
       <c s="11" r="E305">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G305">
@@ -9747,12 +9747,12 @@
     <row r="306" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C306">
@@ -9761,29 +9761,29 @@
         </is>
       </c>
       <c s="10" r="D306">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E306">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F306">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G306">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C307">
@@ -9792,69 +9792,69 @@
         </is>
       </c>
       <c s="10" r="D307">
-        <v>44214</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E307">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F307">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G307">
-        <v>44151</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C308">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D308">
-        <v>44186</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E308">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F308">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G308">
-        <v>44127</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C309">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D309">
-        <v>44104</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E309">
         <v>59</v>
@@ -9865,100 +9865,100 @@
         </is>
       </c>
       <c s="12" r="G309">
-        <v>44104</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D310">
-        <v>44197</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E310">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F310">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G310">
-        <v>44151</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">7241</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">SP+</t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C311">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Elgin</t>
         </is>
       </c>
       <c s="10" r="D311">
-        <v>43914</v>
+        <v>44197</v>
       </c>
       <c s="11" r="E311">
-        <v>89</v>
+        <v>229</v>
       </c>
       <c s="9" t="inlineStr" r="F311">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G311">
-        <v>44099</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">7218</t>
+          <t xml:space="preserve">7241</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
+          <t xml:space="preserve">SP+</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C312">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D312">
-        <v>43903</v>
+        <v>43914</v>
       </c>
       <c s="11" r="E312">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G312">
-        <v>44091</v>
+        <v>44099</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="0">
@@ -9969,19 +9969,19 @@
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
+          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D313">
         <v>43903</v>
       </c>
       <c s="11" r="E313">
-        <v>358</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
@@ -10000,19 +10000,19 @@
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">Sodexo - Medford SD</t>
+          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D314">
         <v>43903</v>
       </c>
       <c s="11" r="E314">
-        <v>111</v>
+        <v>358</v>
       </c>
       <c s="9" t="inlineStr" r="F314">
         <is>
@@ -10026,32 +10026,32 @@
     <row r="315" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">7217</t>
+          <t xml:space="preserve">7218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">PF Chang's</t>
+          <t xml:space="preserve">Sodexo - Medford SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D315">
-        <v>44092</v>
+        <v>43903</v>
       </c>
       <c s="11" r="E315">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F315">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G315">
-        <v>44092</v>
+        <v>44091</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="0">
@@ -10062,12 +10062,12 @@
       </c>
       <c s="9" t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">PF Chang's - Eugene</t>
+          <t xml:space="preserve">PF Chang's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C316">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D316">
@@ -10088,32 +10088,32 @@
     <row r="317" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">7215</t>
+          <t xml:space="preserve">7217</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Salem</t>
+          <t xml:space="preserve">PF Chang's - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C317">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D317">
-        <v>44137</v>
+        <v>44092</v>
       </c>
       <c s="11" r="E317">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F317">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G317">
-        <v>44077</v>
+        <v>44092</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="0">
@@ -10124,19 +10124,19 @@
       </c>
       <c s="9" t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Portland</t>
+          <t xml:space="preserve">LAGS Medical Center - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C318">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D318">
         <v>44137</v>
       </c>
       <c s="11" r="E318">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F318">
         <is>
@@ -10150,12 +10150,12 @@
     <row r="319" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">7211</t>
+          <t xml:space="preserve">7215</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">Bon Appetit</t>
+          <t xml:space="preserve">LAGS Medical Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C319">
@@ -10164,18 +10164,18 @@
         </is>
       </c>
       <c s="10" r="D319">
-        <v>44104</v>
+        <v>44137</v>
       </c>
       <c s="11" r="E319">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F319">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G319">
-        <v>44075</v>
+        <v>44077</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="0">
@@ -10198,11 +10198,11 @@
         <v>44104</v>
       </c>
       <c s="11" r="E320">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c s="9" t="inlineStr" r="F320">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G320">
@@ -10212,24 +10212,24 @@
     <row r="321" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">7209</t>
+          <t xml:space="preserve">7211</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">Dave &amp; Buster's</t>
+          <t xml:space="preserve">Bon Appetit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C321">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D321">
-        <v>44143</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E321">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F321">
         <is>
@@ -10237,158 +10237,190 @@
         </is>
       </c>
       <c s="12" r="G321">
-        <v>44082</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">7207</t>
+          <t xml:space="preserve">7209</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">PGE - Boardman</t>
+          <t xml:space="preserve">Dave &amp; Buster's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C322">
         <is>
-          <t xml:space="preserve">Boardman</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D322">
-        <v>44140</v>
+        <v>44143</v>
       </c>
       <c s="11" r="E322">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c s="9" t="inlineStr" r="F322">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G322">
-        <v>44075</v>
+        <v>44082</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">PGE - Boardman</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C323">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D323"/>
-      <c s="13" t="str" r="E323"/>
+          <t xml:space="preserve">Boardman</t>
+        </is>
+      </c>
+      <c s="10" r="D323">
+        <v>44140</v>
+      </c>
+      <c s="11" r="E323">
+        <v>22</v>
+      </c>
       <c s="9" t="inlineStr" r="F323">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G323">
-        <v>44909</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C324">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D324"/>
       <c s="13" t="str" r="E324"/>
       <c s="9" t="inlineStr" r="F324">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G324">
-        <v>45125</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C325">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">Mesa, AZ</t>
         </is>
       </c>
       <c s="9" t="str" r="D325"/>
       <c s="13" t="str" r="E325"/>
       <c s="9" t="inlineStr" r="F325">
         <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G325">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="326" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A326">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B326">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C326">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D326"/>
+      <c s="13" t="str" r="E326"/>
+      <c s="9" t="inlineStr" r="F326">
+        <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
-      <c s="12" r="G325">
+      <c s="12" r="G326">
         <v>45887</v>
       </c>
     </row>
-    <row r="326" ht="3.6" customHeight="0">
-      <c s="14" t="inlineStr" r="A326">
+    <row r="327" ht="3.55" customHeight="0">
+      <c s="14" t="inlineStr" r="A327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B326">
+      <c s="14" t="inlineStr" r="B327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C326">
+      <c s="14" t="inlineStr" r="C327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D326">
+      <c s="14" t="inlineStr" r="D327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E326">
+      <c s="14" t="inlineStr" r="E327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F326">
+      <c s="14" t="inlineStr" r="F327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G326">
+      <c s="14" t="inlineStr" r="G327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
+    <row r="328" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:A2"/>
@@ -10398,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/11/2026 8:51:43 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/11/2026 7:28:34 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/11/2016 to 9/11/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/12/2016 to 9/12/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/11/2026 7:28:34 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/12/2026 7:57:00 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>
